--- a/research/traditional_assets/database/data/spain/spain_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_chemical_specialty.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bme_kom" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,17 +589,38 @@
           <t>Chemical (Specialty)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.156</v>
+      </c>
+      <c r="F2">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="G2">
+        <v>-0.01935820895522388</v>
+      </c>
+      <c r="H2">
+        <v>-0.02701492537313432</v>
+      </c>
+      <c r="I2">
+        <v>-0.06420895522388061</v>
+      </c>
+      <c r="J2">
+        <v>-0.06420895522388061</v>
+      </c>
       <c r="K2">
-        <v>-4.65</v>
+        <v>-5.539</v>
+      </c>
+      <c r="L2">
+        <v>-0.08267164179104478</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.663003663003664e-05</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.001083228019498104</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,76 +632,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.006</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>9.48</v>
+        <v>12.59</v>
       </c>
       <c r="V2">
-        <v>0.03974842767295598</v>
+        <v>0.07686202686202687</v>
       </c>
       <c r="W2">
-        <v>-0.04978586723768737</v>
+        <v>-0.03832475164245607</v>
       </c>
       <c r="X2">
-        <v>0.07310102647612564</v>
+        <v>0.1817065037496087</v>
       </c>
       <c r="Y2">
-        <v>-0.122886893713813</v>
+        <v>-0.2200312553920648</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.568760611205433</v>
       </c>
       <c r="AA2">
-        <v>-0.04171195652173913</v>
+        <v>-0.01963356793145656</v>
       </c>
       <c r="AB2">
-        <v>0.07310102647612564</v>
+        <v>0.1242361703898218</v>
       </c>
       <c r="AC2">
-        <v>-0.1148129829978648</v>
+        <v>-0.1438697383212783</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="AG2">
-        <v>-9.48</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.143646408839779</v>
       </c>
       <c r="AJ2">
-        <v>-0.04139376473670422</v>
+        <v>0.03311492828050292</v>
       </c>
       <c r="AK2">
-        <v>-0.1113721804511278</v>
+        <v>0.04916308824818157</v>
       </c>
       <c r="AL2">
-        <v>0.032</v>
+        <v>1.329</v>
       </c>
       <c r="AM2">
-        <v>0.032</v>
+        <v>1.327</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-8.198198198198199</v>
       </c>
       <c r="AO2">
-        <v>-95.9375</v>
+        <v>-3.237020316027088</v>
       </c>
       <c r="AP2">
-        <v>3.118421052631579</v>
+        <v>-2.527027027027027</v>
       </c>
       <c r="AQ2">
-        <v>-95.9375</v>
+        <v>-3.241899020346647</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Highfield Resources Limited (ASX:HFR)</t>
+          <t>Plásticos Compuestos, S.A. (BME:KOM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -697,17 +723,38 @@
           <t>Chemical (Specialty)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.156</v>
+      </c>
+      <c r="F3">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.04735820895522388</v>
+      </c>
+      <c r="H3">
+        <v>0.03970149253731343</v>
+      </c>
+      <c r="I3">
+        <v>0.008925373134328358</v>
+      </c>
+      <c r="J3">
+        <v>0.008925373134328358</v>
+      </c>
       <c r="K3">
-        <v>-4.65</v>
+        <v>-0.419</v>
+      </c>
+      <c r="L3">
+        <v>-0.006253731343283581</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.006</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0005357142857142857</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.01431980906921241</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -719,76 +766,8890 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.006</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>9.48</v>
+        <v>3.86</v>
       </c>
       <c r="V3">
-        <v>0.03974842767295598</v>
+        <v>0.3446428571428571</v>
       </c>
       <c r="W3">
-        <v>-0.04978586723768737</v>
+        <v>-0.02252688172043011</v>
       </c>
       <c r="X3">
-        <v>0.07310102647612564</v>
+        <v>0.2358167333247033</v>
       </c>
       <c r="Y3">
-        <v>-0.122886893713813</v>
+        <v>-0.2583436150451334</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.050183598531212</v>
       </c>
       <c r="AA3">
-        <v>-0.04171195652173913</v>
+        <v>0.01829865361077111</v>
       </c>
       <c r="AB3">
-        <v>0.07310102647612564</v>
+        <v>0.1208760666051294</v>
       </c>
       <c r="AC3">
-        <v>-0.1148129829978648</v>
+        <v>-0.1025774129943583</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="AG3">
-        <v>-9.48</v>
+        <v>14.34</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AJ3">
-        <v>-0.04139376473670422</v>
+        <v>0.5614722004698512</v>
       </c>
       <c r="AK3">
-        <v>-0.1113721804511278</v>
+        <v>0.4605009633911368</v>
       </c>
       <c r="AL3">
-        <v>0.032</v>
+        <v>1.32</v>
       </c>
       <c r="AM3">
-        <v>0.032</v>
+        <v>1.318</v>
       </c>
       <c r="AN3">
+        <v>6.842105263157894</v>
+      </c>
+      <c r="AO3">
+        <v>0.453030303030303</v>
+      </c>
+      <c r="AP3">
+        <v>5.390977443609022</v>
+      </c>
+      <c r="AQ3">
+        <v>0.4537177541729893</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Highfield Resources Limited (ASX:HFR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chemical (Specialty)</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-5.12</v>
+      </c>
+      <c r="M4">
         <v>-0</v>
       </c>
-      <c r="AO3">
-        <v>-95.9375</v>
-      </c>
-      <c r="AP3">
-        <v>3.118421052631579</v>
-      </c>
-      <c r="AQ3">
-        <v>-95.9375</v>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>8.73</v>
+      </c>
+      <c r="V4">
+        <v>0.0572083879423329</v>
+      </c>
+      <c r="W4">
+        <v>-0.05412262156448203</v>
+      </c>
+      <c r="X4">
+        <v>0.1275962741745141</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1817188957389962</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-0.05756578947368422</v>
+      </c>
+      <c r="AB4">
+        <v>0.1275962741745141</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1851620636481984</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-8.73</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.06067978035726698</v>
+      </c>
+      <c r="AK4">
+        <v>-0.1052187537664216</v>
+      </c>
+      <c r="AL4">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AM4">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AO4">
+        <v>-544.4444444444446</v>
+      </c>
+      <c r="AP4">
+        <v>1.788934426229508</v>
+      </c>
+      <c r="AQ4">
+        <v>-544.4444444444446</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Plásticos Compuestos, S.A. (BME:KOM)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BME:KOM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chemical (Specialty)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.619047619047619</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>11.2</v>
+      </c>
+      <c r="H2">
+        <v>25.47108447024</v>
+      </c>
+      <c r="I2">
+        <v>25.54</v>
+      </c>
+      <c r="J2">
+        <v>21.90508447024</v>
+      </c>
+      <c r="K2">
+        <v>18.2</v>
+      </c>
+      <c r="L2">
+        <v>0.294</v>
+      </c>
+      <c r="M2">
+        <v>0.120876066605129</v>
+      </c>
+      <c r="N2">
+        <v>0.134495715939507</v>
+      </c>
+      <c r="O2">
+        <v>0.0501433486238532</v>
+      </c>
+      <c r="P2">
+        <v>0.595942857142857</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.235816733324703</v>
+      </c>
+      <c r="T2">
+        <v>0.12983463370513</v>
+      </c>
+      <c r="U2">
+        <v>2.27158079195605</v>
+      </c>
+      <c r="V2">
+        <v>1.04961909497562</v>
+      </c>
+      <c r="W2">
+        <v>-5.982292414453218</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>11.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.06685779816513762</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>2.66</v>
+      </c>
+      <c r="AH2">
+        <v>3.08</v>
+      </c>
+      <c r="AI2">
+        <v>1.71</v>
+      </c>
+      <c r="AJ2">
+        <v>18.2</v>
+      </c>
+      <c r="AK2">
+        <v>18.2</v>
+      </c>
+      <c r="AL2">
+        <v>1.32</v>
+      </c>
+      <c r="AM2">
+        <v>18.2</v>
+      </c>
+      <c r="AN2">
+        <v>3.86</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-18.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.86</v>
+      </c>
+      <c r="H2">
+        <v>11.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.66</v>
+      </c>
+      <c r="K2">
+        <v>3.08</v>
+      </c>
+      <c r="L2">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="O2">
+        <v>-0.105</v>
+      </c>
+      <c r="P2">
+        <v>-0.3149999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>2.765</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1344957159395075</v>
+      </c>
+      <c r="C3">
+        <v>25.47108447024002</v>
+      </c>
+      <c r="D3">
+        <v>21.90508447024002</v>
+      </c>
+      <c r="E3">
+        <v>-17.906</v>
+      </c>
+      <c r="F3">
+        <v>0.294</v>
+      </c>
+      <c r="G3">
+        <v>3.86</v>
+      </c>
+      <c r="H3">
+        <v>11.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.66</v>
+      </c>
+      <c r="K3">
+        <v>3.08</v>
+      </c>
+      <c r="L3">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.0702072</v>
+      </c>
+      <c r="N3">
+        <v>-0.4902072</v>
+      </c>
+      <c r="O3">
+        <v>-0.1225518</v>
+      </c>
+      <c r="P3">
+        <v>-0.3676554</v>
+      </c>
+      <c r="Q3">
+        <v>2.7123446</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1298346337051302</v>
+      </c>
+      <c r="T3">
+        <v>1.049619094975622</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-1.495573103613304</v>
+      </c>
+      <c r="W3">
+        <v>0.5959428571428571</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-5.982292414453218</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1364957159395075</v>
+      </c>
+      <c r="C4">
+        <v>24.72864956683436</v>
+      </c>
+      <c r="D4">
+        <v>21.45664956683436</v>
+      </c>
+      <c r="E4">
+        <v>-17.612</v>
+      </c>
+      <c r="F4">
+        <v>0.588</v>
+      </c>
+      <c r="G4">
+        <v>3.86</v>
+      </c>
+      <c r="H4">
+        <v>11.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.66</v>
+      </c>
+      <c r="K4">
+        <v>3.08</v>
+      </c>
+      <c r="L4">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.1404144</v>
+      </c>
+      <c r="N4">
+        <v>-0.5604144</v>
+      </c>
+      <c r="O4">
+        <v>-0.1401036</v>
+      </c>
+      <c r="P4">
+        <v>-0.4203108</v>
+      </c>
+      <c r="Q4">
+        <v>2.6596892</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.130763558538856</v>
+      </c>
+      <c r="T4">
+        <v>1.060329493903945</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-0.7477865518066522</v>
+      </c>
+      <c r="W4">
+        <v>0.4173714285714286</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-2.991146207226609</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1384957159395075</v>
+      </c>
+      <c r="C5">
+        <v>24.00420680678931</v>
+      </c>
+      <c r="D5">
+        <v>21.02620680678931</v>
+      </c>
+      <c r="E5">
+        <v>-17.318</v>
+      </c>
+      <c r="F5">
+        <v>0.8819999999999999</v>
+      </c>
+      <c r="G5">
+        <v>3.86</v>
+      </c>
+      <c r="H5">
+        <v>11.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.66</v>
+      </c>
+      <c r="K5">
+        <v>3.08</v>
+      </c>
+      <c r="L5">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.2106216</v>
+      </c>
+      <c r="N5">
+        <v>-0.6306215999999999</v>
+      </c>
+      <c r="O5">
+        <v>-0.1576554</v>
+      </c>
+      <c r="P5">
+        <v>-0.4729661999999999</v>
+      </c>
+      <c r="Q5">
+        <v>2.6070338</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.131711636461937</v>
+      </c>
+      <c r="T5">
+        <v>1.071260725799862</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.4985243678711015</v>
+      </c>
+      <c r="W5">
+        <v>0.3578476190476191</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-1.994097471484406</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1404957159395075</v>
+      </c>
+      <c r="C6">
+        <v>23.29669466200444</v>
+      </c>
+      <c r="D6">
+        <v>20.61269466200444</v>
+      </c>
+      <c r="E6">
+        <v>-17.024</v>
+      </c>
+      <c r="F6">
+        <v>1.176</v>
+      </c>
+      <c r="G6">
+        <v>3.86</v>
+      </c>
+      <c r="H6">
+        <v>11.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.66</v>
+      </c>
+      <c r="K6">
+        <v>3.08</v>
+      </c>
+      <c r="L6">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.2808288</v>
+      </c>
+      <c r="N6">
+        <v>-0.7008287999999999</v>
+      </c>
+      <c r="O6">
+        <v>-0.1752072</v>
+      </c>
+      <c r="P6">
+        <v>-0.5256215999999999</v>
+      </c>
+      <c r="Q6">
+        <v>2.5543784</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1326794660084155</v>
+      </c>
+      <c r="T6">
+        <v>1.08241969169361</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.3738932759033261</v>
+      </c>
+      <c r="W6">
+        <v>0.3280857142857143</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-1.495573103613304</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1424957159395074</v>
+      </c>
+      <c r="C7">
+        <v>22.60513349999792</v>
+      </c>
+      <c r="D7">
+        <v>20.21513349999792</v>
+      </c>
+      <c r="E7">
+        <v>-16.73</v>
+      </c>
+      <c r="F7">
+        <v>1.47</v>
+      </c>
+      <c r="G7">
+        <v>3.86</v>
+      </c>
+      <c r="H7">
+        <v>11.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.66</v>
+      </c>
+      <c r="K7">
+        <v>3.08</v>
+      </c>
+      <c r="L7">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.351036</v>
+      </c>
+      <c r="N7">
+        <v>-0.7710359999999999</v>
+      </c>
+      <c r="O7">
+        <v>-0.192759</v>
+      </c>
+      <c r="P7">
+        <v>-0.5782769999999999</v>
+      </c>
+      <c r="Q7">
+        <v>2.501723</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1336676709137672</v>
+      </c>
+      <c r="T7">
+        <v>1.093813583185122</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.2991146207226609</v>
+      </c>
+      <c r="W7">
+        <v>0.3102285714285715</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-1.196458482890643</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1444957159395075</v>
+      </c>
+      <c r="C8">
+        <v>21.92861783566261</v>
+      </c>
+      <c r="D8">
+        <v>19.83261783566261</v>
+      </c>
+      <c r="E8">
+        <v>-16.436</v>
+      </c>
+      <c r="F8">
+        <v>1.764</v>
+      </c>
+      <c r="G8">
+        <v>3.86</v>
+      </c>
+      <c r="H8">
+        <v>11.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.66</v>
+      </c>
+      <c r="K8">
+        <v>3.08</v>
+      </c>
+      <c r="L8">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.4212432</v>
+      </c>
+      <c r="N8">
+        <v>-0.8412431999999999</v>
+      </c>
+      <c r="O8">
+        <v>-0.2103108</v>
+      </c>
+      <c r="P8">
+        <v>-0.6309323999999998</v>
+      </c>
+      <c r="Q8">
+        <v>2.4490676</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1346769014554031</v>
+      </c>
+      <c r="T8">
+        <v>1.105449897899857</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.2492621839355507</v>
+      </c>
+      <c r="W8">
+        <v>0.2983238095238095</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-0.9970487357422029</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1464957159395075</v>
+      </c>
+      <c r="C9">
+        <v>21.26630944637065</v>
+      </c>
+      <c r="D9">
+        <v>19.46430944637065</v>
+      </c>
+      <c r="E9">
+        <v>-16.142</v>
+      </c>
+      <c r="F9">
+        <v>2.058</v>
+      </c>
+      <c r="G9">
+        <v>3.86</v>
+      </c>
+      <c r="H9">
+        <v>11.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.66</v>
+      </c>
+      <c r="K9">
+        <v>3.08</v>
+      </c>
+      <c r="L9">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.4914504000000001</v>
+      </c>
+      <c r="N9">
+        <v>-0.9114504</v>
+      </c>
+      <c r="O9">
+        <v>-0.2278626</v>
+      </c>
+      <c r="P9">
+        <v>-0.6835878</v>
+      </c>
+      <c r="Q9">
+        <v>2.3964122</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1357078358796547</v>
+      </c>
+      <c r="T9">
+        <v>1.117336455941791</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.2136533005161863</v>
+      </c>
+      <c r="W9">
+        <v>0.2898204081632653</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-0.8546132020647452</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1484957159395075</v>
+      </c>
+      <c r="C10">
+        <v>20.6174312402408</v>
+      </c>
+      <c r="D10">
+        <v>19.10943124024081</v>
+      </c>
+      <c r="E10">
+        <v>-15.848</v>
+      </c>
+      <c r="F10">
+        <v>2.352</v>
+      </c>
+      <c r="G10">
+        <v>3.86</v>
+      </c>
+      <c r="H10">
+        <v>11.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.66</v>
+      </c>
+      <c r="K10">
+        <v>3.08</v>
+      </c>
+      <c r="L10">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.5616576</v>
+      </c>
+      <c r="N10">
+        <v>-0.9816575999999999</v>
+      </c>
+      <c r="O10">
+        <v>-0.2454144</v>
+      </c>
+      <c r="P10">
+        <v>-0.7362431999999999</v>
+      </c>
+      <c r="Q10">
+        <v>2.3437568</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1367611819218249</v>
+      </c>
+      <c r="T10">
+        <v>1.129481417419419</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.1869466379516631</v>
+      </c>
+      <c r="W10">
+        <v>0.2834428571428572</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-0.7477865518066522</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1504957159395075</v>
+      </c>
+      <c r="C11">
+        <v>19.98126178316708</v>
+      </c>
+      <c r="D11">
+        <v>18.76726178316708</v>
+      </c>
+      <c r="E11">
+        <v>-15.554</v>
+      </c>
+      <c r="F11">
+        <v>2.646</v>
+      </c>
+      <c r="G11">
+        <v>3.86</v>
+      </c>
+      <c r="H11">
+        <v>11.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.66</v>
+      </c>
+      <c r="K11">
+        <v>3.08</v>
+      </c>
+      <c r="L11">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.6318648</v>
+      </c>
+      <c r="N11">
+        <v>-1.0518648</v>
+      </c>
+      <c r="O11">
+        <v>-0.2629662</v>
+      </c>
+      <c r="P11">
+        <v>-0.7888986</v>
+      </c>
+      <c r="Q11">
+        <v>2.2911014</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1378376784264604</v>
+      </c>
+      <c r="T11">
+        <v>1.141893301127325</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.1661747892903672</v>
+      </c>
+      <c r="W11">
+        <v>0.2784825396825397</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-0.6646991571614687</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1524957159395075</v>
+      </c>
+      <c r="C12">
+        <v>19.35713040349131</v>
+      </c>
+      <c r="D12">
+        <v>18.43713040349131</v>
+      </c>
+      <c r="E12">
+        <v>-15.26</v>
+      </c>
+      <c r="F12">
+        <v>2.94</v>
+      </c>
+      <c r="G12">
+        <v>3.86</v>
+      </c>
+      <c r="H12">
+        <v>11.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.66</v>
+      </c>
+      <c r="K12">
+        <v>3.08</v>
+      </c>
+      <c r="L12">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M12">
+        <v>0.702072</v>
+      </c>
+      <c r="N12">
+        <v>-1.122072</v>
+      </c>
+      <c r="O12">
+        <v>-0.280518</v>
+      </c>
+      <c r="P12">
+        <v>-0.8415539999999999</v>
+      </c>
+      <c r="Q12">
+        <v>2.238446</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1389380970756432</v>
+      </c>
+      <c r="T12">
+        <v>1.154581004473184</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.1495573103613304</v>
+      </c>
+      <c r="W12">
+        <v>0.2745142857142857</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-0.5982292414453216</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1544957159395075</v>
+      </c>
+      <c r="C13">
+        <v>18.74441280442081</v>
+      </c>
+      <c r="D13">
+        <v>18.11841280442081</v>
+      </c>
+      <c r="E13">
+        <v>-14.966</v>
+      </c>
+      <c r="F13">
+        <v>3.234</v>
+      </c>
+      <c r="G13">
+        <v>3.86</v>
+      </c>
+      <c r="H13">
+        <v>11.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.66</v>
+      </c>
+      <c r="K13">
+        <v>3.08</v>
+      </c>
+      <c r="L13">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M13">
+        <v>0.7722792000000001</v>
+      </c>
+      <c r="N13">
+        <v>-1.1922792</v>
+      </c>
+      <c r="O13">
+        <v>-0.2980698</v>
+      </c>
+      <c r="P13">
+        <v>-0.8942094</v>
+      </c>
+      <c r="Q13">
+        <v>2.1857906</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1400632442337965</v>
+      </c>
+      <c r="T13">
+        <v>1.167553824748164</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.1359611912375731</v>
+      </c>
+      <c r="W13">
+        <v>0.2712675324675325</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-0.5438447649502924</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1564957159395075</v>
+      </c>
+      <c r="C14">
+        <v>18.14252712379446</v>
+      </c>
+      <c r="D14">
+        <v>17.81052712379446</v>
+      </c>
+      <c r="E14">
+        <v>-14.672</v>
+      </c>
+      <c r="F14">
+        <v>3.528</v>
+      </c>
+      <c r="G14">
+        <v>3.86</v>
+      </c>
+      <c r="H14">
+        <v>11.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.66</v>
+      </c>
+      <c r="K14">
+        <v>3.08</v>
+      </c>
+      <c r="L14">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M14">
+        <v>0.8424864</v>
+      </c>
+      <c r="N14">
+        <v>-1.2624864</v>
+      </c>
+      <c r="O14">
+        <v>-0.3156215999999999</v>
+      </c>
+      <c r="P14">
+        <v>-0.9468647999999998</v>
+      </c>
+      <c r="Q14">
+        <v>2.1331352</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1412139629182715</v>
+      </c>
+      <c r="T14">
+        <v>1.180821481847575</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.1246310919677754</v>
+      </c>
+      <c r="W14">
+        <v>0.2685619047619048</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.4985243678711013</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1584957159395075</v>
+      </c>
+      <c r="C15">
+        <v>17.55093038887379</v>
+      </c>
+      <c r="D15">
+        <v>17.51293038887379</v>
+      </c>
+      <c r="E15">
+        <v>-14.378</v>
+      </c>
+      <c r="F15">
+        <v>3.822</v>
+      </c>
+      <c r="G15">
+        <v>3.86</v>
+      </c>
+      <c r="H15">
+        <v>11.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.66</v>
+      </c>
+      <c r="K15">
+        <v>3.08</v>
+      </c>
+      <c r="L15">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M15">
+        <v>0.9126936000000001</v>
+      </c>
+      <c r="N15">
+        <v>-1.3326936</v>
+      </c>
+      <c r="O15">
+        <v>-0.3331734</v>
+      </c>
+      <c r="P15">
+        <v>-0.9995202000000001</v>
+      </c>
+      <c r="Q15">
+        <v>2.0804798</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1423911349058378</v>
+      </c>
+      <c r="T15">
+        <v>1.194394142558467</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.1150440848933311</v>
+      </c>
+      <c r="W15">
+        <v>0.2662725274725275</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.4601763395733243</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1604957159395075</v>
+      </c>
+      <c r="C16">
+        <v>16.96911532071512</v>
+      </c>
+      <c r="D16">
+        <v>17.22511532071512</v>
+      </c>
+      <c r="E16">
+        <v>-14.084</v>
+      </c>
+      <c r="F16">
+        <v>4.116000000000001</v>
+      </c>
+      <c r="G16">
+        <v>3.86</v>
+      </c>
+      <c r="H16">
+        <v>11.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.66</v>
+      </c>
+      <c r="K16">
+        <v>3.08</v>
+      </c>
+      <c r="L16">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M16">
+        <v>0.9829008000000001</v>
+      </c>
+      <c r="N16">
+        <v>-1.4029008</v>
+      </c>
+      <c r="O16">
+        <v>-0.3507252</v>
+      </c>
+      <c r="P16">
+        <v>-1.0521756</v>
+      </c>
+      <c r="Q16">
+        <v>2.0278244</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1435956829861383</v>
+      </c>
+      <c r="T16">
+        <v>1.208282446541705</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.1068266502580932</v>
+      </c>
+      <c r="W16">
+        <v>0.2643102040816327</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.4273066010323727</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1624957159395075</v>
+      </c>
+      <c r="C17">
+        <v>16.39660744855666</v>
+      </c>
+      <c r="D17">
+        <v>16.94660744855666</v>
+      </c>
+      <c r="E17">
+        <v>-13.79</v>
+      </c>
+      <c r="F17">
+        <v>4.409999999999999</v>
+      </c>
+      <c r="G17">
+        <v>3.86</v>
+      </c>
+      <c r="H17">
+        <v>11.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.66</v>
+      </c>
+      <c r="K17">
+        <v>3.08</v>
+      </c>
+      <c r="L17">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M17">
+        <v>1.053108</v>
+      </c>
+      <c r="N17">
+        <v>-1.473108</v>
+      </c>
+      <c r="O17">
+        <v>-0.368277</v>
+      </c>
+      <c r="P17">
+        <v>-1.104831</v>
+      </c>
+      <c r="Q17">
+        <v>1.975169</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1448285733742105</v>
+      </c>
+      <c r="T17">
+        <v>1.222497534148077</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.0997048735742203</v>
+      </c>
+      <c r="W17">
+        <v>0.2626095238095238</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.3988194942968812</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1644957159395075</v>
+      </c>
+      <c r="C18">
+        <v>15.83296249969121</v>
+      </c>
+      <c r="D18">
+        <v>16.67696249969121</v>
+      </c>
+      <c r="E18">
+        <v>-13.496</v>
+      </c>
+      <c r="F18">
+        <v>4.704</v>
+      </c>
+      <c r="G18">
+        <v>3.86</v>
+      </c>
+      <c r="H18">
+        <v>11.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.66</v>
+      </c>
+      <c r="K18">
+        <v>3.08</v>
+      </c>
+      <c r="L18">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M18">
+        <v>1.1233152</v>
+      </c>
+      <c r="N18">
+        <v>-1.5433152</v>
+      </c>
+      <c r="O18">
+        <v>-0.3858288</v>
+      </c>
+      <c r="P18">
+        <v>-1.1574864</v>
+      </c>
+      <c r="Q18">
+        <v>1.9225136</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.146090818295332</v>
+      </c>
+      <c r="T18">
+        <v>1.237051076221269</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.09347331897583153</v>
+      </c>
+      <c r="W18">
+        <v>0.2611214285714286</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.373893275903326</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1664957159395075</v>
+      </c>
+      <c r="C19">
+        <v>15.27776403462146</v>
+      </c>
+      <c r="D19">
+        <v>16.41576403462146</v>
+      </c>
+      <c r="E19">
+        <v>-13.202</v>
+      </c>
+      <c r="F19">
+        <v>4.998</v>
+      </c>
+      <c r="G19">
+        <v>3.86</v>
+      </c>
+      <c r="H19">
+        <v>11.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.66</v>
+      </c>
+      <c r="K19">
+        <v>3.08</v>
+      </c>
+      <c r="L19">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M19">
+        <v>1.1935224</v>
+      </c>
+      <c r="N19">
+        <v>-1.6135224</v>
+      </c>
+      <c r="O19">
+        <v>-0.4033806</v>
+      </c>
+      <c r="P19">
+        <v>-1.2101418</v>
+      </c>
+      <c r="Q19">
+        <v>1.8698582</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1473834787567216</v>
+      </c>
+      <c r="T19">
+        <v>1.25195530605526</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.08797488844784142</v>
+      </c>
+      <c r="W19">
+        <v>0.2598084033613446</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.3518995537913656</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1684957159395075</v>
+      </c>
+      <c r="C20">
+        <v>14.73062130102064</v>
+      </c>
+      <c r="D20">
+        <v>16.16262130102064</v>
+      </c>
+      <c r="E20">
+        <v>-12.908</v>
+      </c>
+      <c r="F20">
+        <v>5.292</v>
+      </c>
+      <c r="G20">
+        <v>3.86</v>
+      </c>
+      <c r="H20">
+        <v>11.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.66</v>
+      </c>
+      <c r="K20">
+        <v>3.08</v>
+      </c>
+      <c r="L20">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M20">
+        <v>1.2637296</v>
+      </c>
+      <c r="N20">
+        <v>-1.6837296</v>
+      </c>
+      <c r="O20">
+        <v>-0.4209324</v>
+      </c>
+      <c r="P20">
+        <v>-1.2627972</v>
+      </c>
+      <c r="Q20">
+        <v>1.8172028</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1487076675220474</v>
+      </c>
+      <c r="T20">
+        <v>1.26722305369008</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.08308739464518358</v>
+      </c>
+      <c r="W20">
+        <v>0.2586412698412698</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.3323495785807342</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1704957159395075</v>
+      </c>
+      <c r="C21">
+        <v>14.19116728323854</v>
+      </c>
+      <c r="D21">
+        <v>15.91716728323854</v>
+      </c>
+      <c r="E21">
+        <v>-12.614</v>
+      </c>
+      <c r="F21">
+        <v>5.585999999999999</v>
+      </c>
+      <c r="G21">
+        <v>3.86</v>
+      </c>
+      <c r="H21">
+        <v>11.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.66</v>
+      </c>
+      <c r="K21">
+        <v>3.08</v>
+      </c>
+      <c r="L21">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M21">
+        <v>1.3339368</v>
+      </c>
+      <c r="N21">
+        <v>-1.7539368</v>
+      </c>
+      <c r="O21">
+        <v>-0.4384842</v>
+      </c>
+      <c r="P21">
+        <v>-1.3154526</v>
+      </c>
+      <c r="Q21">
+        <v>1.7645474</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1500645523062702</v>
+      </c>
+      <c r="T21">
+        <v>1.282867782747983</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.07871437387438444</v>
+      </c>
+      <c r="W21">
+        <v>0.257596992481203</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.3148574954975378</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1724957159395075</v>
+      </c>
+      <c r="C22">
+        <v>13.65905692687618</v>
+      </c>
+      <c r="D22">
+        <v>15.67905692687618</v>
+      </c>
+      <c r="E22">
+        <v>-12.32</v>
+      </c>
+      <c r="F22">
+        <v>5.88</v>
+      </c>
+      <c r="G22">
+        <v>3.86</v>
+      </c>
+      <c r="H22">
+        <v>11.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.66</v>
+      </c>
+      <c r="K22">
+        <v>3.08</v>
+      </c>
+      <c r="L22">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M22">
+        <v>1.404144</v>
+      </c>
+      <c r="N22">
+        <v>-1.824144</v>
+      </c>
+      <c r="O22">
+        <v>-0.456036</v>
+      </c>
+      <c r="P22">
+        <v>-1.368108</v>
+      </c>
+      <c r="Q22">
+        <v>1.711892</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1514553592100986</v>
+      </c>
+      <c r="T22">
+        <v>1.298903630032332</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.07477865518066522</v>
+      </c>
+      <c r="W22">
+        <v>0.2566571428571429</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.2991146207226609</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1744957159395075</v>
+      </c>
+      <c r="C23">
+        <v>13.13396552036685</v>
+      </c>
+      <c r="D23">
+        <v>15.44796552036684</v>
+      </c>
+      <c r="E23">
+        <v>-12.026</v>
+      </c>
+      <c r="F23">
+        <v>6.173999999999999</v>
+      </c>
+      <c r="G23">
+        <v>3.86</v>
+      </c>
+      <c r="H23">
+        <v>11.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.66</v>
+      </c>
+      <c r="K23">
+        <v>3.08</v>
+      </c>
+      <c r="L23">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M23">
+        <v>1.4743512</v>
+      </c>
+      <c r="N23">
+        <v>-1.8943512</v>
+      </c>
+      <c r="O23">
+        <v>-0.4735877999999999</v>
+      </c>
+      <c r="P23">
+        <v>-1.4207634</v>
+      </c>
+      <c r="Q23">
+        <v>1.6592366</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1528813764152898</v>
+      </c>
+      <c r="T23">
+        <v>1.315345448134007</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.07121776683872878</v>
+      </c>
+      <c r="W23">
+        <v>0.2558068027210885</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.2848710673549151</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1764957159395075</v>
+      </c>
+      <c r="C24">
+        <v>12.61558721760028</v>
+      </c>
+      <c r="D24">
+        <v>15.22358721760028</v>
+      </c>
+      <c r="E24">
+        <v>-11.732</v>
+      </c>
+      <c r="F24">
+        <v>6.468</v>
+      </c>
+      <c r="G24">
+        <v>3.86</v>
+      </c>
+      <c r="H24">
+        <v>11.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.66</v>
+      </c>
+      <c r="K24">
+        <v>3.08</v>
+      </c>
+      <c r="L24">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M24">
+        <v>1.5445584</v>
+      </c>
+      <c r="N24">
+        <v>-1.9645584</v>
+      </c>
+      <c r="O24">
+        <v>-0.4911396</v>
+      </c>
+      <c r="P24">
+        <v>-1.4734188</v>
+      </c>
+      <c r="Q24">
+        <v>1.6065812</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1543439581642037</v>
+      </c>
+      <c r="T24">
+        <v>1.332208851315213</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.06798059561878655</v>
+      </c>
+      <c r="W24">
+        <v>0.2550337662337663</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.2719223824751462</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1784957159395075</v>
+      </c>
+      <c r="C25">
+        <v>12.10363368745491</v>
+      </c>
+      <c r="D25">
+        <v>15.00563368745491</v>
+      </c>
+      <c r="E25">
+        <v>-11.438</v>
+      </c>
+      <c r="F25">
+        <v>6.762</v>
+      </c>
+      <c r="G25">
+        <v>3.86</v>
+      </c>
+      <c r="H25">
+        <v>11.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.66</v>
+      </c>
+      <c r="K25">
+        <v>3.08</v>
+      </c>
+      <c r="L25">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M25">
+        <v>1.6147656</v>
+      </c>
+      <c r="N25">
+        <v>-2.0347656</v>
+      </c>
+      <c r="O25">
+        <v>-0.5086914</v>
+      </c>
+      <c r="P25">
+        <v>-1.5260742</v>
+      </c>
+      <c r="Q25">
+        <v>1.5539258</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1558445290494531</v>
+      </c>
+      <c r="T25">
+        <v>1.349510264968657</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.06502491754840455</v>
+      </c>
+      <c r="W25">
+        <v>0.254327950310559</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.2600996701936182</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1804957159395075</v>
+      </c>
+      <c r="C26">
+        <v>11.59783287769915</v>
+      </c>
+      <c r="D26">
+        <v>14.79383287769915</v>
+      </c>
+      <c r="E26">
+        <v>-11.144</v>
+      </c>
+      <c r="F26">
+        <v>7.055999999999999</v>
+      </c>
+      <c r="G26">
+        <v>3.86</v>
+      </c>
+      <c r="H26">
+        <v>11.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.66</v>
+      </c>
+      <c r="K26">
+        <v>3.08</v>
+      </c>
+      <c r="L26">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M26">
+        <v>1.6849728</v>
+      </c>
+      <c r="N26">
+        <v>-2.1049728</v>
+      </c>
+      <c r="O26">
+        <v>-0.5262431999999999</v>
+      </c>
+      <c r="P26">
+        <v>-1.5787296</v>
+      </c>
+      <c r="Q26">
+        <v>1.5012704</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1573845886422091</v>
+      </c>
+      <c r="T26">
+        <v>1.367266978981402</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.06231554598388769</v>
+      </c>
+      <c r="W26">
+        <v>0.2536809523809524</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.2492621839355507</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1824957159395075</v>
+      </c>
+      <c r="C27">
+        <v>11.09792788211909</v>
+      </c>
+      <c r="D27">
+        <v>14.58792788211909</v>
+      </c>
+      <c r="E27">
+        <v>-10.85</v>
+      </c>
+      <c r="F27">
+        <v>7.35</v>
+      </c>
+      <c r="G27">
+        <v>3.86</v>
+      </c>
+      <c r="H27">
+        <v>11.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.66</v>
+      </c>
+      <c r="K27">
+        <v>3.08</v>
+      </c>
+      <c r="L27">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M27">
+        <v>1.75518</v>
+      </c>
+      <c r="N27">
+        <v>-2.17518</v>
+      </c>
+      <c r="O27">
+        <v>-0.543795</v>
+      </c>
+      <c r="P27">
+        <v>-1.631385</v>
+      </c>
+      <c r="Q27">
+        <v>1.448615</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1589657164907719</v>
+      </c>
+      <c r="T27">
+        <v>1.385497205367821</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.05982292414453218</v>
+      </c>
+      <c r="W27">
+        <v>0.2530857142857143</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.2392916965781289</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1844957159395075</v>
+      </c>
+      <c r="C28">
+        <v>10.60367590095341</v>
+      </c>
+      <c r="D28">
+        <v>14.38767590095341</v>
+      </c>
+      <c r="E28">
+        <v>-10.556</v>
+      </c>
+      <c r="F28">
+        <v>7.644</v>
+      </c>
+      <c r="G28">
+        <v>3.86</v>
+      </c>
+      <c r="H28">
+        <v>11.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.66</v>
+      </c>
+      <c r="K28">
+        <v>3.08</v>
+      </c>
+      <c r="L28">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M28">
+        <v>1.8253872</v>
+      </c>
+      <c r="N28">
+        <v>-2.2453872</v>
+      </c>
+      <c r="O28">
+        <v>-0.5613468</v>
+      </c>
+      <c r="P28">
+        <v>-1.6840404</v>
+      </c>
+      <c r="Q28">
+        <v>1.3959596</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.160589577524431</v>
+      </c>
+      <c r="T28">
+        <v>1.404220140575494</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.05752204244666555</v>
+      </c>
+      <c r="W28">
+        <v>0.2525362637362638</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.2300881697866621</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1864957159395075</v>
+      </c>
+      <c r="C29">
+        <v>10.11484728579106</v>
+      </c>
+      <c r="D29">
+        <v>14.19284728579106</v>
+      </c>
+      <c r="E29">
+        <v>-10.262</v>
+      </c>
+      <c r="F29">
+        <v>7.938</v>
+      </c>
+      <c r="G29">
+        <v>3.86</v>
+      </c>
+      <c r="H29">
+        <v>11.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.66</v>
+      </c>
+      <c r="K29">
+        <v>3.08</v>
+      </c>
+      <c r="L29">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M29">
+        <v>1.8955944</v>
+      </c>
+      <c r="N29">
+        <v>-2.3155944</v>
+      </c>
+      <c r="O29">
+        <v>-0.5788986</v>
+      </c>
+      <c r="P29">
+        <v>-1.7366958</v>
+      </c>
+      <c r="Q29">
+        <v>1.3433042</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.162257927901478</v>
+      </c>
+      <c r="T29">
+        <v>1.423456032912145</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.05539159643012238</v>
+      </c>
+      <c r="W29">
+        <v>0.2520275132275132</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.2215663857204897</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1884957159395075</v>
+      </c>
+      <c r="C30">
+        <v>9.631224661032354</v>
+      </c>
+      <c r="D30">
+        <v>14.00322466103236</v>
+      </c>
+      <c r="E30">
+        <v>-9.967999999999998</v>
+      </c>
+      <c r="F30">
+        <v>8.232000000000001</v>
+      </c>
+      <c r="G30">
+        <v>3.86</v>
+      </c>
+      <c r="H30">
+        <v>11.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.66</v>
+      </c>
+      <c r="K30">
+        <v>3.08</v>
+      </c>
+      <c r="L30">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M30">
+        <v>1.9658016</v>
+      </c>
+      <c r="N30">
+        <v>-2.3858016</v>
+      </c>
+      <c r="O30">
+        <v>-0.5964504</v>
+      </c>
+      <c r="P30">
+        <v>-1.7893512</v>
+      </c>
+      <c r="Q30">
+        <v>1.2906488</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.163972621344554</v>
+      </c>
+      <c r="T30">
+        <v>1.443226255591481</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.05341332512904658</v>
+      </c>
+      <c r="W30">
+        <v>0.2515551020408163</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.2136533005161863</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1904957159395075</v>
+      </c>
+      <c r="C31">
+        <v>9.152602114847642</v>
+      </c>
+      <c r="D31">
+        <v>13.81860211484764</v>
+      </c>
+      <c r="E31">
+        <v>-9.673999999999999</v>
+      </c>
+      <c r="F31">
+        <v>8.526</v>
+      </c>
+      <c r="G31">
+        <v>3.86</v>
+      </c>
+      <c r="H31">
+        <v>11.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.66</v>
+      </c>
+      <c r="K31">
+        <v>3.08</v>
+      </c>
+      <c r="L31">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M31">
+        <v>2.0360088</v>
+      </c>
+      <c r="N31">
+        <v>-2.4560088</v>
+      </c>
+      <c r="O31">
+        <v>-0.6140021999999999</v>
+      </c>
+      <c r="P31">
+        <v>-1.8420066</v>
+      </c>
+      <c r="Q31">
+        <v>1.2379934</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1657356160113787</v>
+      </c>
+      <c r="T31">
+        <v>1.463553385951924</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.05157148633149326</v>
+      </c>
+      <c r="W31">
+        <v>0.2511152709359606</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.2062859453259731</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1924957159395075</v>
+      </c>
+      <c r="C32">
+        <v>8.678784453302852</v>
+      </c>
+      <c r="D32">
+        <v>13.63878445330285</v>
+      </c>
+      <c r="E32">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="F32">
+        <v>8.819999999999999</v>
+      </c>
+      <c r="G32">
+        <v>3.86</v>
+      </c>
+      <c r="H32">
+        <v>11.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.66</v>
+      </c>
+      <c r="K32">
+        <v>3.08</v>
+      </c>
+      <c r="L32">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M32">
+        <v>2.106216</v>
+      </c>
+      <c r="N32">
+        <v>-2.526216</v>
+      </c>
+      <c r="O32">
+        <v>-0.6315539999999999</v>
+      </c>
+      <c r="P32">
+        <v>-1.894662</v>
+      </c>
+      <c r="Q32">
+        <v>1.185338</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1675489819543984</v>
+      </c>
+      <c r="T32">
+        <v>1.484461291465523</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.04985243678711015</v>
+      </c>
+      <c r="W32">
+        <v>0.2507047619047619</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.1994097471484406</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1944957159395075</v>
+      </c>
+      <c r="C33">
+        <v>8.209586511972185</v>
+      </c>
+      <c r="D33">
+        <v>13.46358651197218</v>
+      </c>
+      <c r="E33">
+        <v>-9.086</v>
+      </c>
+      <c r="F33">
+        <v>9.113999999999999</v>
+      </c>
+      <c r="G33">
+        <v>3.86</v>
+      </c>
+      <c r="H33">
+        <v>11.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.66</v>
+      </c>
+      <c r="K33">
+        <v>3.08</v>
+      </c>
+      <c r="L33">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M33">
+        <v>2.1764232</v>
+      </c>
+      <c r="N33">
+        <v>-2.5964232</v>
+      </c>
+      <c r="O33">
+        <v>-0.6491058</v>
+      </c>
+      <c r="P33">
+        <v>-1.9473174</v>
+      </c>
+      <c r="Q33">
+        <v>1.1326826</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1694149092290999</v>
+      </c>
+      <c r="T33">
+        <v>1.505975223225893</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.04824429366494531</v>
+      </c>
+      <c r="W33">
+        <v>0.2503207373271889</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.1929771746597813</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1964957159395075</v>
+      </c>
+      <c r="C34">
+        <v>7.744832519934294</v>
+      </c>
+      <c r="D34">
+        <v>13.29283251993429</v>
+      </c>
+      <c r="E34">
+        <v>-8.792</v>
+      </c>
+      <c r="F34">
+        <v>9.407999999999999</v>
+      </c>
+      <c r="G34">
+        <v>3.86</v>
+      </c>
+      <c r="H34">
+        <v>11.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.66</v>
+      </c>
+      <c r="K34">
+        <v>3.08</v>
+      </c>
+      <c r="L34">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M34">
+        <v>2.2466304</v>
+      </c>
+      <c r="N34">
+        <v>-2.6666304</v>
+      </c>
+      <c r="O34">
+        <v>-0.6666576</v>
+      </c>
+      <c r="P34">
+        <v>-1.9999728</v>
+      </c>
+      <c r="Q34">
+        <v>1.0800272</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1713357167177631</v>
+      </c>
+      <c r="T34">
+        <v>1.528121917685097</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.04673665948791576</v>
+      </c>
+      <c r="W34">
+        <v>0.2499607142857143</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.1869466379516631</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1984957159395075</v>
+      </c>
+      <c r="C35">
+        <v>7.28435551155957</v>
+      </c>
+      <c r="D35">
+        <v>13.12635551155957</v>
+      </c>
+      <c r="E35">
+        <v>-8.497999999999999</v>
+      </c>
+      <c r="F35">
+        <v>9.702</v>
+      </c>
+      <c r="G35">
+        <v>3.86</v>
+      </c>
+      <c r="H35">
+        <v>11.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.66</v>
+      </c>
+      <c r="K35">
+        <v>3.08</v>
+      </c>
+      <c r="L35">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M35">
+        <v>2.3168376</v>
+      </c>
+      <c r="N35">
+        <v>-2.7368376</v>
+      </c>
+      <c r="O35">
+        <v>-0.6842094</v>
+      </c>
+      <c r="P35">
+        <v>-2.0526282</v>
+      </c>
+      <c r="Q35">
+        <v>1.0273718</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1733138617434014</v>
+      </c>
+      <c r="T35">
+        <v>1.550929707501293</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.04532039707919104</v>
+      </c>
+      <c r="W35">
+        <v>0.2496225108225109</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.1812815883167642</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2004957159395075</v>
+      </c>
+      <c r="C36">
+        <v>6.827996781950796</v>
+      </c>
+      <c r="D36">
+        <v>12.9639967819508</v>
+      </c>
+      <c r="E36">
+        <v>-8.203999999999999</v>
+      </c>
+      <c r="F36">
+        <v>9.996</v>
+      </c>
+      <c r="G36">
+        <v>3.86</v>
+      </c>
+      <c r="H36">
+        <v>11.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.66</v>
+      </c>
+      <c r="K36">
+        <v>3.08</v>
+      </c>
+      <c r="L36">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M36">
+        <v>2.3870448</v>
+      </c>
+      <c r="N36">
+        <v>-2.8070448</v>
+      </c>
+      <c r="O36">
+        <v>-0.7017612000000001</v>
+      </c>
+      <c r="P36">
+        <v>-2.1052836</v>
+      </c>
+      <c r="Q36">
+        <v>0.9747163999999997</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1753519505576953</v>
+      </c>
+      <c r="T36">
+        <v>1.574428642463433</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.04398744422392071</v>
+      </c>
+      <c r="W36">
+        <v>0.2493042016806723</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.1759497768956828</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2024957159395075</v>
+      </c>
+      <c r="C37">
+        <v>6.375605382303641</v>
+      </c>
+      <c r="D37">
+        <v>12.80560538230364</v>
+      </c>
+      <c r="E37">
+        <v>-7.909999999999998</v>
+      </c>
+      <c r="F37">
+        <v>10.29</v>
+      </c>
+      <c r="G37">
+        <v>3.86</v>
+      </c>
+      <c r="H37">
+        <v>11.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.66</v>
+      </c>
+      <c r="K37">
+        <v>3.08</v>
+      </c>
+      <c r="L37">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M37">
+        <v>2.457252</v>
+      </c>
+      <c r="N37">
+        <v>-2.877252</v>
+      </c>
+      <c r="O37">
+        <v>-0.7193130000000001</v>
+      </c>
+      <c r="P37">
+        <v>-2.157939</v>
+      </c>
+      <c r="Q37">
+        <v>0.9220609999999998</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1774527497970445</v>
+      </c>
+      <c r="T37">
+        <v>1.598650621578255</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.04273066010323726</v>
+      </c>
+      <c r="W37">
+        <v>0.2490040816326531</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.1709226404129491</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2044957159395075</v>
+      </c>
+      <c r="C38">
+        <v>5.927037651814114</v>
+      </c>
+      <c r="D38">
+        <v>12.65103765181411</v>
+      </c>
+      <c r="E38">
+        <v>-7.616</v>
+      </c>
+      <c r="F38">
+        <v>10.584</v>
+      </c>
+      <c r="G38">
+        <v>3.86</v>
+      </c>
+      <c r="H38">
+        <v>11.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.66</v>
+      </c>
+      <c r="K38">
+        <v>3.08</v>
+      </c>
+      <c r="L38">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M38">
+        <v>2.5274592</v>
+      </c>
+      <c r="N38">
+        <v>-2.9474592</v>
+      </c>
+      <c r="O38">
+        <v>-0.7368648</v>
+      </c>
+      <c r="P38">
+        <v>-2.2105944</v>
+      </c>
+      <c r="Q38">
+        <v>0.8694056000000003</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1796191990126233</v>
+      </c>
+      <c r="T38">
+        <v>1.623629537540416</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.04154369732259179</v>
+      </c>
+      <c r="W38">
+        <v>0.2487206349206349</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.1661747892903671</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2064957159395075</v>
+      </c>
+      <c r="C39">
+        <v>5.482156783081873</v>
+      </c>
+      <c r="D39">
+        <v>12.50015678308187</v>
+      </c>
+      <c r="E39">
+        <v>-7.321999999999999</v>
+      </c>
+      <c r="F39">
+        <v>10.878</v>
+      </c>
+      <c r="G39">
+        <v>3.86</v>
+      </c>
+      <c r="H39">
+        <v>11.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.66</v>
+      </c>
+      <c r="K39">
+        <v>3.08</v>
+      </c>
+      <c r="L39">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M39">
+        <v>2.5976664</v>
+      </c>
+      <c r="N39">
+        <v>-3.0176664</v>
+      </c>
+      <c r="O39">
+        <v>-0.7544166</v>
+      </c>
+      <c r="P39">
+        <v>-2.2632498</v>
+      </c>
+      <c r="Q39">
+        <v>0.8167502</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1818544243937761</v>
+      </c>
+      <c r="T39">
+        <v>1.649401434961692</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.04042089469225147</v>
+      </c>
+      <c r="W39">
+        <v>0.2484525096525097</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.1616835787690059</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2084957159395075</v>
+      </c>
+      <c r="C40">
+        <v>5.040832418245957</v>
+      </c>
+      <c r="D40">
+        <v>12.35283241824596</v>
+      </c>
+      <c r="E40">
+        <v>-7.028</v>
+      </c>
+      <c r="F40">
+        <v>11.172</v>
+      </c>
+      <c r="G40">
+        <v>3.86</v>
+      </c>
+      <c r="H40">
+        <v>11.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.66</v>
+      </c>
+      <c r="K40">
+        <v>3.08</v>
+      </c>
+      <c r="L40">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M40">
+        <v>2.6678736</v>
+      </c>
+      <c r="N40">
+        <v>-3.0878736</v>
+      </c>
+      <c r="O40">
+        <v>-0.7719684</v>
+      </c>
+      <c r="P40">
+        <v>-2.3159052</v>
+      </c>
+      <c r="Q40">
+        <v>0.7640948000000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1841617538194821</v>
+      </c>
+      <c r="T40">
+        <v>1.676004683912687</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.03935718693719222</v>
+      </c>
+      <c r="W40">
+        <v>0.2481984962406015</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.1574287477487688</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2104957159395075</v>
+      </c>
+      <c r="C41">
+        <v>4.602940273347036</v>
+      </c>
+      <c r="D41">
+        <v>12.20894027334703</v>
+      </c>
+      <c r="E41">
+        <v>-6.734</v>
+      </c>
+      <c r="F41">
+        <v>11.466</v>
+      </c>
+      <c r="G41">
+        <v>3.86</v>
+      </c>
+      <c r="H41">
+        <v>11.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.66</v>
+      </c>
+      <c r="K41">
+        <v>3.08</v>
+      </c>
+      <c r="L41">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M41">
+        <v>2.7380808</v>
+      </c>
+      <c r="N41">
+        <v>-3.1580808</v>
+      </c>
+      <c r="O41">
+        <v>-0.7895202</v>
+      </c>
+      <c r="P41">
+        <v>-2.3685606</v>
+      </c>
+      <c r="Q41">
+        <v>0.7114394000000002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1865447333902933</v>
+      </c>
+      <c r="T41">
+        <v>1.703480170534206</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.03834802829777703</v>
+      </c>
+      <c r="W41">
+        <v>0.2479575091575092</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.1533921131911082</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2124957159395075</v>
+      </c>
+      <c r="C42">
+        <v>4.168361788641068</v>
+      </c>
+      <c r="D42">
+        <v>12.06836178864107</v>
+      </c>
+      <c r="E42">
+        <v>-6.44</v>
+      </c>
+      <c r="F42">
+        <v>11.76</v>
+      </c>
+      <c r="G42">
+        <v>3.86</v>
+      </c>
+      <c r="H42">
+        <v>11.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.66</v>
+      </c>
+      <c r="K42">
+        <v>3.08</v>
+      </c>
+      <c r="L42">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M42">
+        <v>2.808288</v>
+      </c>
+      <c r="N42">
+        <v>-3.228288</v>
+      </c>
+      <c r="O42">
+        <v>-0.807072</v>
+      </c>
+      <c r="P42">
+        <v>-2.421216</v>
+      </c>
+      <c r="Q42">
+        <v>0.6587839999999998</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1890071456134648</v>
+      </c>
+      <c r="T42">
+        <v>1.731871506709777</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.03738932759033261</v>
+      </c>
+      <c r="W42">
+        <v>0.2477285714285714</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.1495573103613304</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2144957159395075</v>
+      </c>
+      <c r="C43">
+        <v>3.736983802796537</v>
+      </c>
+      <c r="D43">
+        <v>11.93098380279654</v>
+      </c>
+      <c r="E43">
+        <v>-6.145999999999999</v>
+      </c>
+      <c r="F43">
+        <v>12.054</v>
+      </c>
+      <c r="G43">
+        <v>3.86</v>
+      </c>
+      <c r="H43">
+        <v>11.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.66</v>
+      </c>
+      <c r="K43">
+        <v>3.08</v>
+      </c>
+      <c r="L43">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M43">
+        <v>2.8784952</v>
+      </c>
+      <c r="N43">
+        <v>-3.2984952</v>
+      </c>
+      <c r="O43">
+        <v>-0.8246238</v>
+      </c>
+      <c r="P43">
+        <v>-2.4738714</v>
+      </c>
+      <c r="Q43">
+        <v>0.6061285999999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1915530294374219</v>
+      </c>
+      <c r="T43">
+        <v>1.76122526106079</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.0364773927710562</v>
+      </c>
+      <c r="W43">
+        <v>0.2475108013937282</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.1459095710842249</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2164957159395075</v>
+      </c>
+      <c r="C44">
+        <v>3.308698249093506</v>
+      </c>
+      <c r="D44">
+        <v>11.79669824909351</v>
+      </c>
+      <c r="E44">
+        <v>-5.852</v>
+      </c>
+      <c r="F44">
+        <v>12.348</v>
+      </c>
+      <c r="G44">
+        <v>3.86</v>
+      </c>
+      <c r="H44">
+        <v>11.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.66</v>
+      </c>
+      <c r="K44">
+        <v>3.08</v>
+      </c>
+      <c r="L44">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M44">
+        <v>2.9487024</v>
+      </c>
+      <c r="N44">
+        <v>-3.3687024</v>
+      </c>
+      <c r="O44">
+        <v>-0.8421755999999999</v>
+      </c>
+      <c r="P44">
+        <v>-2.5265268</v>
+      </c>
+      <c r="Q44">
+        <v>0.5534732000000004</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1941867023587567</v>
+      </c>
+      <c r="T44">
+        <v>1.7915912138377</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.03560888341936439</v>
+      </c>
+      <c r="W44">
+        <v>0.2473034013605442</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.1424355336774576</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2184957159395075</v>
+      </c>
+      <c r="C45">
+        <v>2.883401871910374</v>
+      </c>
+      <c r="D45">
+        <v>11.66540187191037</v>
+      </c>
+      <c r="E45">
+        <v>-5.558</v>
+      </c>
+      <c r="F45">
+        <v>12.642</v>
+      </c>
+      <c r="G45">
+        <v>3.86</v>
+      </c>
+      <c r="H45">
+        <v>11.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.66</v>
+      </c>
+      <c r="K45">
+        <v>3.08</v>
+      </c>
+      <c r="L45">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M45">
+        <v>3.0189096</v>
+      </c>
+      <c r="N45">
+        <v>-3.4389096</v>
+      </c>
+      <c r="O45">
+        <v>-0.8597274</v>
+      </c>
+      <c r="P45">
+        <v>-2.5791822</v>
+      </c>
+      <c r="Q45">
+        <v>0.5008178000000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1969127848562788</v>
+      </c>
+      <c r="T45">
+        <v>1.82302263864187</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.03478076985147219</v>
+      </c>
+      <c r="W45">
+        <v>0.2471056478405316</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.1391230794058889</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2204957159395075</v>
+      </c>
+      <c r="C46">
+        <v>2.460995961935101</v>
+      </c>
+      <c r="D46">
+        <v>11.5369959619351</v>
+      </c>
+      <c r="E46">
+        <v>-5.263999999999999</v>
+      </c>
+      <c r="F46">
+        <v>12.936</v>
+      </c>
+      <c r="G46">
+        <v>3.86</v>
+      </c>
+      <c r="H46">
+        <v>11.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.66</v>
+      </c>
+      <c r="K46">
+        <v>3.08</v>
+      </c>
+      <c r="L46">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M46">
+        <v>3.0891168</v>
+      </c>
+      <c r="N46">
+        <v>-3.5091168</v>
+      </c>
+      <c r="O46">
+        <v>-0.8772792</v>
+      </c>
+      <c r="P46">
+        <v>-2.6318376</v>
+      </c>
+      <c r="Q46">
+        <v>0.4481624000000002</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1997362274429981</v>
+      </c>
+      <c r="T46">
+        <v>1.855576614331904</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.03399029780939328</v>
+      </c>
+      <c r="W46">
+        <v>0.2469168831168831</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.1359611912375731</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2224957159395075</v>
+      </c>
+      <c r="C47">
+        <v>2.041386108673912</v>
+      </c>
+      <c r="D47">
+        <v>11.41138610867391</v>
+      </c>
+      <c r="E47">
+        <v>-4.969999999999999</v>
+      </c>
+      <c r="F47">
+        <v>13.23</v>
+      </c>
+      <c r="G47">
+        <v>3.86</v>
+      </c>
+      <c r="H47">
+        <v>11.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.66</v>
+      </c>
+      <c r="K47">
+        <v>3.08</v>
+      </c>
+      <c r="L47">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M47">
+        <v>3.159324</v>
+      </c>
+      <c r="N47">
+        <v>-3.579324</v>
+      </c>
+      <c r="O47">
+        <v>-0.894831</v>
+      </c>
+      <c r="P47">
+        <v>-2.684493</v>
+      </c>
+      <c r="Q47">
+        <v>0.3955069999999998</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2026623406692344</v>
+      </c>
+      <c r="T47">
+        <v>1.88931437095612</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.03323495785807343</v>
+      </c>
+      <c r="W47">
+        <v>0.246736507936508</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.1329398314322938</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2244957159395075</v>
+      </c>
+      <c r="C48">
+        <v>1.624481968953305</v>
+      </c>
+      <c r="D48">
+        <v>11.2884819689533</v>
+      </c>
+      <c r="E48">
+        <v>-4.676</v>
+      </c>
+      <c r="F48">
+        <v>13.524</v>
+      </c>
+      <c r="G48">
+        <v>3.86</v>
+      </c>
+      <c r="H48">
+        <v>11.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.66</v>
+      </c>
+      <c r="K48">
+        <v>3.08</v>
+      </c>
+      <c r="L48">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M48">
+        <v>3.2295312</v>
+      </c>
+      <c r="N48">
+        <v>-3.6495312</v>
+      </c>
+      <c r="O48">
+        <v>-0.9123827999999999</v>
+      </c>
+      <c r="P48">
+        <v>-2.7371484</v>
+      </c>
+      <c r="Q48">
+        <v>0.3428516000000004</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2056968284594054</v>
+      </c>
+      <c r="T48">
+        <v>1.924301674121974</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.03251245877420227</v>
+      </c>
+      <c r="W48">
+        <v>0.2465639751552795</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.1300498350968091</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2264957159395075</v>
+      </c>
+      <c r="C49">
+        <v>1.210197050222487</v>
+      </c>
+      <c r="D49">
+        <v>11.16819705022249</v>
+      </c>
+      <c r="E49">
+        <v>-4.382</v>
+      </c>
+      <c r="F49">
+        <v>13.818</v>
+      </c>
+      <c r="G49">
+        <v>3.86</v>
+      </c>
+      <c r="H49">
+        <v>11.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.66</v>
+      </c>
+      <c r="K49">
+        <v>3.08</v>
+      </c>
+      <c r="L49">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M49">
+        <v>3.2997384</v>
+      </c>
+      <c r="N49">
+        <v>-3.7197384</v>
+      </c>
+      <c r="O49">
+        <v>-0.9299346000000001</v>
+      </c>
+      <c r="P49">
+        <v>-2.7898038</v>
+      </c>
+      <c r="Q49">
+        <v>0.2901962</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2088458252227904</v>
+      </c>
+      <c r="T49">
+        <v>1.960609252878992</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.03182070433219796</v>
+      </c>
+      <c r="W49">
+        <v>0.2463987841945289</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.1272828173287919</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2284957159395075</v>
+      </c>
+      <c r="C50">
+        <v>0.7984485075639522</v>
+      </c>
+      <c r="D50">
+        <v>11.05044850756395</v>
+      </c>
+      <c r="E50">
+        <v>-4.088000000000001</v>
+      </c>
+      <c r="F50">
+        <v>14.112</v>
+      </c>
+      <c r="G50">
+        <v>3.86</v>
+      </c>
+      <c r="H50">
+        <v>11.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.66</v>
+      </c>
+      <c r="K50">
+        <v>3.08</v>
+      </c>
+      <c r="L50">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M50">
+        <v>3.3699456</v>
+      </c>
+      <c r="N50">
+        <v>-3.7899456</v>
+      </c>
+      <c r="O50">
+        <v>-0.9474864</v>
+      </c>
+      <c r="P50">
+        <v>-2.8424592</v>
+      </c>
+      <c r="Q50">
+        <v>0.2375408000000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2121159372463056</v>
+      </c>
+      <c r="T50">
+        <v>1.998313276972819</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.03115777299194384</v>
+      </c>
+      <c r="W50">
+        <v>0.2462404761904762</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.1246310919677753</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2304957159395075</v>
+      </c>
+      <c r="C51">
+        <v>0.3891569534110033</v>
+      </c>
+      <c r="D51">
+        <v>10.935156953411</v>
+      </c>
+      <c r="E51">
+        <v>-3.794</v>
+      </c>
+      <c r="F51">
+        <v>14.406</v>
+      </c>
+      <c r="G51">
+        <v>3.86</v>
+      </c>
+      <c r="H51">
+        <v>11.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.66</v>
+      </c>
+      <c r="K51">
+        <v>3.08</v>
+      </c>
+      <c r="L51">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M51">
+        <v>3.4401528</v>
+      </c>
+      <c r="N51">
+        <v>-3.8601528</v>
+      </c>
+      <c r="O51">
+        <v>-0.9650382</v>
+      </c>
+      <c r="P51">
+        <v>-2.8951146</v>
+      </c>
+      <c r="Q51">
+        <v>0.1848854000000002</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2155142889570174</v>
+      </c>
+      <c r="T51">
+        <v>2.037495890246796</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.03052190007374091</v>
+      </c>
+      <c r="W51">
+        <v>0.2460886297376093</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.1220876002949636</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2324957159395075</v>
+      </c>
+      <c r="C52">
+        <v>-0.01775372094615335</v>
+      </c>
+      <c r="D52">
+        <v>10.82224627905385</v>
+      </c>
+      <c r="E52">
+        <v>-3.5</v>
+      </c>
+      <c r="F52">
+        <v>14.7</v>
+      </c>
+      <c r="G52">
+        <v>3.86</v>
+      </c>
+      <c r="H52">
+        <v>11.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.66</v>
+      </c>
+      <c r="K52">
+        <v>3.08</v>
+      </c>
+      <c r="L52">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M52">
+        <v>3.51036</v>
+      </c>
+      <c r="N52">
+        <v>-3.93036</v>
+      </c>
+      <c r="O52">
+        <v>-0.98259</v>
+      </c>
+      <c r="P52">
+        <v>-2.94777</v>
+      </c>
+      <c r="Q52">
+        <v>0.1322300000000003</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2190485747361578</v>
+      </c>
+      <c r="T52">
+        <v>2.078245808051732</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.02991146207226609</v>
+      </c>
+      <c r="W52">
+        <v>0.2459428571428571</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.1196458482890643</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2344957159395075</v>
+      </c>
+      <c r="C53">
+        <v>-0.422356512909154</v>
+      </c>
+      <c r="D53">
+        <v>10.71164348709085</v>
+      </c>
+      <c r="E53">
+        <v>-3.206</v>
+      </c>
+      <c r="F53">
+        <v>14.994</v>
+      </c>
+      <c r="G53">
+        <v>3.86</v>
+      </c>
+      <c r="H53">
+        <v>11.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.66</v>
+      </c>
+      <c r="K53">
+        <v>3.08</v>
+      </c>
+      <c r="L53">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M53">
+        <v>3.5805672</v>
+      </c>
+      <c r="N53">
+        <v>-4.0005672</v>
+      </c>
+      <c r="O53">
+        <v>-1.0001418</v>
+      </c>
+      <c r="P53">
+        <v>-3.0004254</v>
+      </c>
+      <c r="Q53">
+        <v>0.07957459999999994</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.222727117077712</v>
+      </c>
+      <c r="T53">
+        <v>2.120658987807889</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.02932496281594715</v>
+      </c>
+      <c r="W53">
+        <v>0.2458028011204482</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.1172998512637886</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2364957159395075</v>
+      </c>
+      <c r="C54">
+        <v>-0.8247214659501036</v>
+      </c>
+      <c r="D54">
+        <v>10.6032785340499</v>
+      </c>
+      <c r="E54">
+        <v>-2.911999999999999</v>
+      </c>
+      <c r="F54">
+        <v>15.288</v>
+      </c>
+      <c r="G54">
+        <v>3.86</v>
+      </c>
+      <c r="H54">
+        <v>11.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.66</v>
+      </c>
+      <c r="K54">
+        <v>3.08</v>
+      </c>
+      <c r="L54">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M54">
+        <v>3.6507744</v>
+      </c>
+      <c r="N54">
+        <v>-4.0707744</v>
+      </c>
+      <c r="O54">
+        <v>-1.0176936</v>
+      </c>
+      <c r="P54">
+        <v>-3.0530808</v>
+      </c>
+      <c r="Q54">
+        <v>0.02691920000000003</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2265589320168311</v>
+      </c>
+      <c r="T54">
+        <v>2.164839383387221</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.02876102122333277</v>
+      </c>
+      <c r="W54">
+        <v>0.2456681318681319</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.1150440848933312</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2384957159395075</v>
+      </c>
+      <c r="C55">
+        <v>-1.224915817533111</v>
+      </c>
+      <c r="D55">
+        <v>10.49708418246689</v>
+      </c>
+      <c r="E55">
+        <v>-2.617999999999999</v>
+      </c>
+      <c r="F55">
+        <v>15.582</v>
+      </c>
+      <c r="G55">
+        <v>3.86</v>
+      </c>
+      <c r="H55">
+        <v>11.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.66</v>
+      </c>
+      <c r="K55">
+        <v>3.08</v>
+      </c>
+      <c r="L55">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M55">
+        <v>3.7209816</v>
+      </c>
+      <c r="N55">
+        <v>-4.1409816</v>
+      </c>
+      <c r="O55">
+        <v>-1.0352454</v>
+      </c>
+      <c r="P55">
+        <v>-3.1057362</v>
+      </c>
+      <c r="Q55">
+        <v>-0.02573619999999988</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2305538029108062</v>
+      </c>
+      <c r="T55">
+        <v>2.210899795799715</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.02821836044553404</v>
+      </c>
+      <c r="W55">
+        <v>0.2455385444743935</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.112873441782136</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2404957159395075</v>
+      </c>
+      <c r="C56">
+        <v>-1.623004138235123</v>
+      </c>
+      <c r="D56">
+        <v>10.39299586176488</v>
+      </c>
+      <c r="E56">
+        <v>-2.324</v>
+      </c>
+      <c r="F56">
+        <v>15.876</v>
+      </c>
+      <c r="G56">
+        <v>3.86</v>
+      </c>
+      <c r="H56">
+        <v>11.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.66</v>
+      </c>
+      <c r="K56">
+        <v>3.08</v>
+      </c>
+      <c r="L56">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M56">
+        <v>3.7911888</v>
+      </c>
+      <c r="N56">
+        <v>-4.2111888</v>
+      </c>
+      <c r="O56">
+        <v>-1.0527972</v>
+      </c>
+      <c r="P56">
+        <v>-3.1583916</v>
+      </c>
+      <c r="Q56">
+        <v>-0.07839160000000023</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2347223638436498</v>
+      </c>
+      <c r="T56">
+        <v>2.258962834838839</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.02769579821506119</v>
+      </c>
+      <c r="W56">
+        <v>0.2454137566137566</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.110783192860245</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2424957159395075</v>
+      </c>
+      <c r="C57">
+        <v>-2.019048462671005</v>
+      </c>
+      <c r="D57">
+        <v>10.290951537329</v>
+      </c>
+      <c r="E57">
+        <v>-2.029999999999998</v>
+      </c>
+      <c r="F57">
+        <v>16.17</v>
+      </c>
+      <c r="G57">
+        <v>3.86</v>
+      </c>
+      <c r="H57">
+        <v>11.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.66</v>
+      </c>
+      <c r="K57">
+        <v>3.08</v>
+      </c>
+      <c r="L57">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M57">
+        <v>3.861396</v>
+      </c>
+      <c r="N57">
+        <v>-4.281396000000001</v>
+      </c>
+      <c r="O57">
+        <v>-1.070349</v>
+      </c>
+      <c r="P57">
+        <v>-3.211047000000001</v>
+      </c>
+      <c r="Q57">
+        <v>-0.1310470000000006</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2390761941512865</v>
+      </c>
+      <c r="T57">
+        <v>2.309162008946369</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.02719223824751462</v>
+      </c>
+      <c r="W57">
+        <v>0.2452935064935065</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.1087689529900586</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2444957159395075</v>
+      </c>
+      <c r="C58">
+        <v>-2.41310841278057</v>
+      </c>
+      <c r="D58">
+        <v>10.19089158721943</v>
+      </c>
+      <c r="E58">
+        <v>-1.735999999999997</v>
+      </c>
+      <c r="F58">
+        <v>16.464</v>
+      </c>
+      <c r="G58">
+        <v>3.86</v>
+      </c>
+      <c r="H58">
+        <v>11.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.66</v>
+      </c>
+      <c r="K58">
+        <v>3.08</v>
+      </c>
+      <c r="L58">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M58">
+        <v>3.931603200000001</v>
+      </c>
+      <c r="N58">
+        <v>-4.3516032</v>
+      </c>
+      <c r="O58">
+        <v>-1.0879008</v>
+      </c>
+      <c r="P58">
+        <v>-3.263702400000001</v>
+      </c>
+      <c r="Q58">
+        <v>-0.1837024000000005</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.243627925836543</v>
+      </c>
+      <c r="T58">
+        <v>2.36164296369515</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.02670666256452329</v>
+      </c>
+      <c r="W58">
+        <v>0.2451775510204082</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.1068266502580932</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2464957159395075</v>
+      </c>
+      <c r="C59">
+        <v>-2.805241313992529</v>
+      </c>
+      <c r="D59">
+        <v>10.09275868600747</v>
+      </c>
+      <c r="E59">
+        <v>-1.441999999999997</v>
+      </c>
+      <c r="F59">
+        <v>16.758</v>
+      </c>
+      <c r="G59">
+        <v>3.86</v>
+      </c>
+      <c r="H59">
+        <v>11.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.66</v>
+      </c>
+      <c r="K59">
+        <v>3.08</v>
+      </c>
+      <c r="L59">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M59">
+        <v>4.001810400000001</v>
+      </c>
+      <c r="N59">
+        <v>-4.421810400000001</v>
+      </c>
+      <c r="O59">
+        <v>-1.1054526</v>
+      </c>
+      <c r="P59">
+        <v>-3.3163578</v>
+      </c>
+      <c r="Q59">
+        <v>-0.2363578000000004</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2483913659722766</v>
+      </c>
+      <c r="T59">
+        <v>2.41656489308341</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.02623812462479481</v>
+      </c>
+      <c r="W59">
+        <v>0.245065664160401</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.1049524984991792</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2484957159395075</v>
+      </c>
+      <c r="C60">
+        <v>-3.195502304740844</v>
+      </c>
+      <c r="D60">
+        <v>9.996497695259157</v>
+      </c>
+      <c r="E60">
+        <v>-1.148</v>
+      </c>
+      <c r="F60">
+        <v>17.052</v>
+      </c>
+      <c r="G60">
+        <v>3.86</v>
+      </c>
+      <c r="H60">
+        <v>11.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.66</v>
+      </c>
+      <c r="K60">
+        <v>3.08</v>
+      </c>
+      <c r="L60">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M60">
+        <v>4.0720176</v>
+      </c>
+      <c r="N60">
+        <v>-4.4920176</v>
+      </c>
+      <c r="O60">
+        <v>-1.1230044</v>
+      </c>
+      <c r="P60">
+        <v>-3.369013199999999</v>
+      </c>
+      <c r="Q60">
+        <v>-0.2890131999999994</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.253381636590664</v>
+      </c>
+      <c r="T60">
+        <v>2.474102152442538</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.02578574316574663</v>
+      </c>
+      <c r="W60">
+        <v>0.2449576354679803</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.1031429726629864</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2504957159395075</v>
+      </c>
+      <c r="C61">
+        <v>-3.583944439773143</v>
+      </c>
+      <c r="D61">
+        <v>9.902055560226854</v>
+      </c>
+      <c r="E61">
+        <v>-0.8540000000000028</v>
+      </c>
+      <c r="F61">
+        <v>17.346</v>
+      </c>
+      <c r="G61">
+        <v>3.86</v>
+      </c>
+      <c r="H61">
+        <v>11.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.66</v>
+      </c>
+      <c r="K61">
+        <v>3.08</v>
+      </c>
+      <c r="L61">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M61">
+        <v>4.142224799999999</v>
+      </c>
+      <c r="N61">
+        <v>-4.562224799999999</v>
+      </c>
+      <c r="O61">
+        <v>-1.1405562</v>
+      </c>
+      <c r="P61">
+        <v>-3.421668599999999</v>
+      </c>
+      <c r="Q61">
+        <v>-0.3416685999999993</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2586153350440949</v>
+      </c>
+      <c r="T61">
+        <v>2.534446107380161</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.02534869667141194</v>
+      </c>
+      <c r="W61">
+        <v>0.2448532687651332</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.1013947866856477</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2524957159395075</v>
+      </c>
+      <c r="C62">
+        <v>-3.970618787657866</v>
+      </c>
+      <c r="D62">
+        <v>9.809381212342132</v>
+      </c>
+      <c r="E62">
+        <v>-0.5600000000000023</v>
+      </c>
+      <c r="F62">
+        <v>17.64</v>
+      </c>
+      <c r="G62">
+        <v>3.86</v>
+      </c>
+      <c r="H62">
+        <v>11.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.66</v>
+      </c>
+      <c r="K62">
+        <v>3.08</v>
+      </c>
+      <c r="L62">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M62">
+        <v>4.212432</v>
+      </c>
+      <c r="N62">
+        <v>-4.632432</v>
+      </c>
+      <c r="O62">
+        <v>-1.158108</v>
+      </c>
+      <c r="P62">
+        <v>-3.474324</v>
+      </c>
+      <c r="Q62">
+        <v>-0.3943239999999997</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2641107184201972</v>
+      </c>
+      <c r="T62">
+        <v>2.597807260064664</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.02492621839355507</v>
+      </c>
+      <c r="W62">
+        <v>0.2447523809523809</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.09970487357422031</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2544957159395075</v>
+      </c>
+      <c r="C63">
+        <v>-4.35557452286675</v>
+      </c>
+      <c r="D63">
+        <v>9.718425477133248</v>
+      </c>
+      <c r="E63">
+        <v>-0.2660000000000018</v>
+      </c>
+      <c r="F63">
+        <v>17.934</v>
+      </c>
+      <c r="G63">
+        <v>3.86</v>
+      </c>
+      <c r="H63">
+        <v>11.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.66</v>
+      </c>
+      <c r="K63">
+        <v>3.08</v>
+      </c>
+      <c r="L63">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M63">
+        <v>4.282639199999999</v>
+      </c>
+      <c r="N63">
+        <v>-4.702639199999999</v>
+      </c>
+      <c r="O63">
+        <v>-1.1756598</v>
+      </c>
+      <c r="P63">
+        <v>-3.526979399999999</v>
+      </c>
+      <c r="Q63">
+        <v>-0.4469793999999991</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2698879163284075</v>
+      </c>
+      <c r="T63">
+        <v>2.664417702630425</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.02451759186251319</v>
+      </c>
+      <c r="W63">
+        <v>0.2446548009367681</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.09807036745005271</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2564957159395075</v>
+      </c>
+      <c r="C64">
+        <v>-4.738859012781415</v>
+      </c>
+      <c r="D64">
+        <v>9.629140987218584</v>
+      </c>
+      <c r="E64">
+        <v>0.02799999999999869</v>
+      </c>
+      <c r="F64">
+        <v>18.228</v>
+      </c>
+      <c r="G64">
+        <v>3.86</v>
+      </c>
+      <c r="H64">
+        <v>11.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.66</v>
+      </c>
+      <c r="K64">
+        <v>3.08</v>
+      </c>
+      <c r="L64">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M64">
+        <v>4.3528464</v>
+      </c>
+      <c r="N64">
+        <v>-4.7728464</v>
+      </c>
+      <c r="O64">
+        <v>-1.1932116</v>
+      </c>
+      <c r="P64">
+        <v>-3.5796348</v>
+      </c>
+      <c r="Q64">
+        <v>-0.4996347999999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2759691772844182</v>
+      </c>
+      <c r="T64">
+        <v>2.734533957962805</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.02412214683247265</v>
+      </c>
+      <c r="W64">
+        <v>0.2445603686635945</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.09648858732989063</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2584957159395075</v>
+      </c>
+      <c r="C65">
+        <v>-5.120517899947608</v>
+      </c>
+      <c r="D65">
+        <v>9.541482100052392</v>
+      </c>
+      <c r="E65">
+        <v>0.3219999999999992</v>
+      </c>
+      <c r="F65">
+        <v>18.522</v>
+      </c>
+      <c r="G65">
+        <v>3.86</v>
+      </c>
+      <c r="H65">
+        <v>11.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.66</v>
+      </c>
+      <c r="K65">
+        <v>3.08</v>
+      </c>
+      <c r="L65">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M65">
+        <v>4.4230536</v>
+      </c>
+      <c r="N65">
+        <v>-4.8430536</v>
+      </c>
+      <c r="O65">
+        <v>-1.2107634</v>
+      </c>
+      <c r="P65">
+        <v>-3.6322902</v>
+      </c>
+      <c r="Q65">
+        <v>-0.5522901999999998</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2823791550488619</v>
+      </c>
+      <c r="T65">
+        <v>2.808440281150989</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.02373925561290959</v>
+      </c>
+      <c r="W65">
+        <v>0.2444689342403628</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.09495702245163828</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2604957159395075</v>
+      </c>
+      <c r="C66">
+        <v>-5.50059517987715</v>
+      </c>
+      <c r="D66">
+        <v>9.455404820122849</v>
+      </c>
+      <c r="E66">
+        <v>0.6159999999999997</v>
+      </c>
+      <c r="F66">
+        <v>18.816</v>
+      </c>
+      <c r="G66">
+        <v>3.86</v>
+      </c>
+      <c r="H66">
+        <v>11.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.66</v>
+      </c>
+      <c r="K66">
+        <v>3.08</v>
+      </c>
+      <c r="L66">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M66">
+        <v>4.4932608</v>
+      </c>
+      <c r="N66">
+        <v>-4.9132608</v>
+      </c>
+      <c r="O66">
+        <v>-1.2283152</v>
+      </c>
+      <c r="P66">
+        <v>-3.6849456</v>
+      </c>
+      <c r="Q66">
+        <v>-0.6049455999999998</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2891452426891081</v>
+      </c>
+      <c r="T66">
+        <v>2.886452511182962</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.02336832974395788</v>
+      </c>
+      <c r="W66">
+        <v>0.2443803571428572</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.09347331897583144</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2624957159395075</v>
+      </c>
+      <c r="C67">
+        <v>-5.879133274676244</v>
+      </c>
+      <c r="D67">
+        <v>9.370866725323756</v>
+      </c>
+      <c r="E67">
+        <v>0.9100000000000001</v>
+      </c>
+      <c r="F67">
+        <v>19.11</v>
+      </c>
+      <c r="G67">
+        <v>3.86</v>
+      </c>
+      <c r="H67">
+        <v>11.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.66</v>
+      </c>
+      <c r="K67">
+        <v>3.08</v>
+      </c>
+      <c r="L67">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M67">
+        <v>4.563468</v>
+      </c>
+      <c r="N67">
+        <v>-4.983468</v>
+      </c>
+      <c r="O67">
+        <v>-1.245867</v>
+      </c>
+      <c r="P67">
+        <v>-3.737601</v>
+      </c>
+      <c r="Q67">
+        <v>-0.6576010000000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2962979639087969</v>
+      </c>
+      <c r="T67">
+        <v>2.968922582931045</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.02300881697866622</v>
+      </c>
+      <c r="W67">
+        <v>0.2442945054945055</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.09203526791466499</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2644957159395075</v>
+      </c>
+      <c r="C68">
+        <v>-6.256173102759073</v>
+      </c>
+      <c r="D68">
+        <v>9.287826897240928</v>
+      </c>
+      <c r="E68">
+        <v>1.204000000000001</v>
+      </c>
+      <c r="F68">
+        <v>19.404</v>
+      </c>
+      <c r="G68">
+        <v>3.86</v>
+      </c>
+      <c r="H68">
+        <v>11.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.66</v>
+      </c>
+      <c r="K68">
+        <v>3.08</v>
+      </c>
+      <c r="L68">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M68">
+        <v>4.6336752</v>
+      </c>
+      <c r="N68">
+        <v>-5.0536752</v>
+      </c>
+      <c r="O68">
+        <v>-1.2634188</v>
+      </c>
+      <c r="P68">
+        <v>-3.7902564</v>
+      </c>
+      <c r="Q68">
+        <v>-0.7102563999999996</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3038714334355263</v>
+      </c>
+      <c r="T68">
+        <v>3.056243835370194</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.02266019853959552</v>
+      </c>
+      <c r="W68">
+        <v>0.2442112554112554</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.090640794158382</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2664957159395075</v>
+      </c>
+      <c r="C69">
+        <v>-6.631754144887321</v>
+      </c>
+      <c r="D69">
+        <v>9.20624585511268</v>
+      </c>
+      <c r="E69">
+        <v>1.498000000000001</v>
+      </c>
+      <c r="F69">
+        <v>19.698</v>
+      </c>
+      <c r="G69">
+        <v>3.86</v>
+      </c>
+      <c r="H69">
+        <v>11.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.66</v>
+      </c>
+      <c r="K69">
+        <v>3.08</v>
+      </c>
+      <c r="L69">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M69">
+        <v>4.7038824</v>
+      </c>
+      <c r="N69">
+        <v>-5.1238824</v>
+      </c>
+      <c r="O69">
+        <v>-1.2809706</v>
+      </c>
+      <c r="P69">
+        <v>-3.8429118</v>
+      </c>
+      <c r="Q69">
+        <v>-0.7629118000000004</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3119039011153907</v>
+      </c>
+      <c r="T69">
+        <v>3.148857284926867</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.02232198662109409</v>
+      </c>
+      <c r="W69">
+        <v>0.2441304904051173</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.08928794648437632</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2684957159395075</v>
+      </c>
+      <c r="C70">
+        <v>-7.005914506759607</v>
+      </c>
+      <c r="D70">
+        <v>9.126085493240394</v>
+      </c>
+      <c r="E70">
+        <v>1.792000000000002</v>
+      </c>
+      <c r="F70">
+        <v>19.992</v>
+      </c>
+      <c r="G70">
+        <v>3.86</v>
+      </c>
+      <c r="H70">
+        <v>11.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.66</v>
+      </c>
+      <c r="K70">
+        <v>3.08</v>
+      </c>
+      <c r="L70">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M70">
+        <v>4.774089600000001</v>
+      </c>
+      <c r="N70">
+        <v>-5.194089600000001</v>
+      </c>
+      <c r="O70">
+        <v>-1.2985224</v>
+      </c>
+      <c r="P70">
+        <v>-3.8955672</v>
+      </c>
+      <c r="Q70">
+        <v>-0.8155672000000003</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3204383980252467</v>
+      </c>
+      <c r="T70">
+        <v>3.247259075080831</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.02199372211196035</v>
+      </c>
+      <c r="W70">
+        <v>0.2440521008403362</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.08797488844784151</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2704957159395076</v>
+      </c>
+      <c r="C71">
+        <v>-7.378690978359312</v>
+      </c>
+      <c r="D71">
+        <v>9.04730902164069</v>
+      </c>
+      <c r="E71">
+        <v>2.086000000000002</v>
+      </c>
+      <c r="F71">
+        <v>20.286</v>
+      </c>
+      <c r="G71">
+        <v>3.86</v>
+      </c>
+      <c r="H71">
+        <v>11.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.66</v>
+      </c>
+      <c r="K71">
+        <v>3.08</v>
+      </c>
+      <c r="L71">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M71">
+        <v>4.8442968</v>
+      </c>
+      <c r="N71">
+        <v>-5.2642968</v>
+      </c>
+      <c r="O71">
+        <v>-1.3160742</v>
+      </c>
+      <c r="P71">
+        <v>-3.9482226</v>
+      </c>
+      <c r="Q71">
+        <v>-0.8682226000000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3295235076389643</v>
+      </c>
+      <c r="T71">
+        <v>3.352009367825375</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.02167497251613484</v>
+      </c>
+      <c r="W71">
+        <v>0.243975983436853</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.08669989006453949</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2724957159395075</v>
+      </c>
+      <c r="C72">
+        <v>-7.750119090254888</v>
+      </c>
+      <c r="D72">
+        <v>8.969880909745115</v>
+      </c>
+      <c r="E72">
+        <v>2.380000000000003</v>
+      </c>
+      <c r="F72">
+        <v>20.58</v>
+      </c>
+      <c r="G72">
+        <v>3.86</v>
+      </c>
+      <c r="H72">
+        <v>11.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.66</v>
+      </c>
+      <c r="K72">
+        <v>3.08</v>
+      </c>
+      <c r="L72">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M72">
+        <v>4.914504000000001</v>
+      </c>
+      <c r="N72">
+        <v>-5.334504000000001</v>
+      </c>
+      <c r="O72">
+        <v>-1.333626</v>
+      </c>
+      <c r="P72">
+        <v>-4.000878</v>
+      </c>
+      <c r="Q72">
+        <v>-0.9208780000000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3392142912269298</v>
+      </c>
+      <c r="T72">
+        <v>3.463743013419553</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.02136533005161863</v>
+      </c>
+      <c r="W72">
+        <v>0.2439020408163265</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.08546132020647446</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2744957159395075</v>
+      </c>
+      <c r="C73">
+        <v>-8.12023316703384</v>
+      </c>
+      <c r="D73">
+        <v>8.893766832966159</v>
+      </c>
+      <c r="E73">
+        <v>2.673999999999999</v>
+      </c>
+      <c r="F73">
+        <v>20.874</v>
+      </c>
+      <c r="G73">
+        <v>3.86</v>
+      </c>
+      <c r="H73">
+        <v>11.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.66</v>
+      </c>
+      <c r="K73">
+        <v>3.08</v>
+      </c>
+      <c r="L73">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M73">
+        <v>4.9847112</v>
+      </c>
+      <c r="N73">
+        <v>-5.404711199999999</v>
+      </c>
+      <c r="O73">
+        <v>-1.3511778</v>
+      </c>
+      <c r="P73">
+        <v>-4.053533399999999</v>
+      </c>
+      <c r="Q73">
+        <v>-0.9735333999999991</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3495734047175135</v>
+      </c>
+      <c r="T73">
+        <v>3.583182427675399</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.02106440991004654</v>
+      </c>
+      <c r="W73">
+        <v>0.2438301810865191</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.08425763964018618</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2764957159395075</v>
+      </c>
+      <c r="C74">
+        <v>-8.489066378039034</v>
+      </c>
+      <c r="D74">
+        <v>8.818933621960966</v>
+      </c>
+      <c r="E74">
+        <v>2.968</v>
+      </c>
+      <c r="F74">
+        <v>21.168</v>
+      </c>
+      <c r="G74">
+        <v>3.86</v>
+      </c>
+      <c r="H74">
+        <v>11.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.66</v>
+      </c>
+      <c r="K74">
+        <v>3.08</v>
+      </c>
+      <c r="L74">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M74">
+        <v>5.0549184</v>
+      </c>
+      <c r="N74">
+        <v>-5.4749184</v>
+      </c>
+      <c r="O74">
+        <v>-1.3687296</v>
+      </c>
+      <c r="P74">
+        <v>-4.1061888</v>
+      </c>
+      <c r="Q74">
+        <v>-1.0261888</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3606724548859961</v>
+      </c>
+      <c r="T74">
+        <v>3.711153228663807</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.0207718486612959</v>
+      </c>
+      <c r="W74">
+        <v>0.2437603174603175</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.08308739464518355</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2784957159395074</v>
+      </c>
+      <c r="C75">
+        <v>-8.856650785565005</v>
+      </c>
+      <c r="D75">
+        <v>8.745349214434995</v>
+      </c>
+      <c r="E75">
+        <v>3.262</v>
+      </c>
+      <c r="F75">
+        <v>21.462</v>
+      </c>
+      <c r="G75">
+        <v>3.86</v>
+      </c>
+      <c r="H75">
+        <v>11.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.66</v>
+      </c>
+      <c r="K75">
+        <v>3.08</v>
+      </c>
+      <c r="L75">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M75">
+        <v>5.125125600000001</v>
+      </c>
+      <c r="N75">
+        <v>-5.5451256</v>
+      </c>
+      <c r="O75">
+        <v>-1.3862814</v>
+      </c>
+      <c r="P75">
+        <v>-4.158844200000001</v>
+      </c>
+      <c r="Q75">
+        <v>-1.078844200000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3725936569188107</v>
+      </c>
+      <c r="T75">
+        <v>3.848603348243947</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.02048730278922335</v>
+      </c>
+      <c r="W75">
+        <v>0.2436923679060665</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.08194921115689335</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2804957159395075</v>
+      </c>
+      <c r="C76">
+        <v>-9.223017390661342</v>
+      </c>
+      <c r="D76">
+        <v>8.672982609338659</v>
+      </c>
+      <c r="E76">
+        <v>3.556000000000001</v>
+      </c>
+      <c r="F76">
+        <v>21.756</v>
+      </c>
+      <c r="G76">
+        <v>3.86</v>
+      </c>
+      <c r="H76">
+        <v>11.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.66</v>
+      </c>
+      <c r="K76">
+        <v>3.08</v>
+      </c>
+      <c r="L76">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M76">
+        <v>5.1953328</v>
+      </c>
+      <c r="N76">
+        <v>-5.6153328</v>
+      </c>
+      <c r="O76">
+        <v>-1.4038332</v>
+      </c>
+      <c r="P76">
+        <v>-4.2114996</v>
+      </c>
+      <c r="Q76">
+        <v>-1.1314996</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3854318744926111</v>
+      </c>
+      <c r="T76">
+        <v>3.996626553945638</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.02021044734612574</v>
+      </c>
+      <c r="W76">
+        <v>0.2436262548262549</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.08084178938450304</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2824957159395075</v>
+      </c>
+      <c r="C77">
+        <v>-9.588196176680633</v>
+      </c>
+      <c r="D77">
+        <v>8.601803823319365</v>
+      </c>
+      <c r="E77">
+        <v>3.849999999999998</v>
+      </c>
+      <c r="F77">
+        <v>22.05</v>
+      </c>
+      <c r="G77">
+        <v>3.86</v>
+      </c>
+      <c r="H77">
+        <v>11.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.66</v>
+      </c>
+      <c r="K77">
+        <v>3.08</v>
+      </c>
+      <c r="L77">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M77">
+        <v>5.26554</v>
+      </c>
+      <c r="N77">
+        <v>-5.68554</v>
+      </c>
+      <c r="O77">
+        <v>-1.421385</v>
+      </c>
+      <c r="P77">
+        <v>-4.264155</v>
+      </c>
+      <c r="Q77">
+        <v>-1.184155</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3992971494723156</v>
+      </c>
+      <c r="T77">
+        <v>4.156491616103463</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.01994097471484406</v>
+      </c>
+      <c r="W77">
+        <v>0.2435619047619048</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.07976389885937629</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2844957159395075</v>
+      </c>
+      <c r="C78">
+        <v>-9.952216150699533</v>
+      </c>
+      <c r="D78">
+        <v>8.531783849300465</v>
+      </c>
+      <c r="E78">
+        <v>4.143999999999998</v>
+      </c>
+      <c r="F78">
+        <v>22.344</v>
+      </c>
+      <c r="G78">
+        <v>3.86</v>
+      </c>
+      <c r="H78">
+        <v>11.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.66</v>
+      </c>
+      <c r="K78">
+        <v>3.08</v>
+      </c>
+      <c r="L78">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M78">
+        <v>5.3357472</v>
+      </c>
+      <c r="N78">
+        <v>-5.7557472</v>
+      </c>
+      <c r="O78">
+        <v>-1.4389368</v>
+      </c>
+      <c r="P78">
+        <v>-4.3168104</v>
+      </c>
+      <c r="Q78">
+        <v>-1.2368104</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4143178640336622</v>
+      </c>
+      <c r="T78">
+        <v>4.329678766774443</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.01967859346859611</v>
+      </c>
+      <c r="W78">
+        <v>0.2434992481203008</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.07871437387438451</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2864957159395075</v>
+      </c>
+      <c r="C79">
+        <v>-10.31510538293304</v>
+      </c>
+      <c r="D79">
+        <v>8.462894617066963</v>
+      </c>
+      <c r="E79">
+        <v>4.437999999999999</v>
+      </c>
+      <c r="F79">
+        <v>22.638</v>
+      </c>
+      <c r="G79">
+        <v>3.86</v>
+      </c>
+      <c r="H79">
+        <v>11.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.66</v>
+      </c>
+      <c r="K79">
+        <v>3.08</v>
+      </c>
+      <c r="L79">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M79">
+        <v>5.4059544</v>
+      </c>
+      <c r="N79">
+        <v>-5.8259544</v>
+      </c>
+      <c r="O79">
+        <v>-1.4564886</v>
+      </c>
+      <c r="P79">
+        <v>-4.3694658</v>
+      </c>
+      <c r="Q79">
+        <v>-1.289465799999999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4306447276872997</v>
+      </c>
+      <c r="T79">
+        <v>4.517925669677679</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.0194230273196533</v>
+      </c>
+      <c r="W79">
+        <v>0.2434382189239332</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.07769210927861314</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2884957159395075</v>
+      </c>
+      <c r="C80">
+        <v>-10.67689104425465</v>
+      </c>
+      <c r="D80">
+        <v>8.395108955745346</v>
+      </c>
+      <c r="E80">
+        <v>4.731999999999999</v>
+      </c>
+      <c r="F80">
+        <v>22.932</v>
+      </c>
+      <c r="G80">
+        <v>3.86</v>
+      </c>
+      <c r="H80">
+        <v>11.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.66</v>
+      </c>
+      <c r="K80">
+        <v>3.08</v>
+      </c>
+      <c r="L80">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M80">
+        <v>5.4761616</v>
+      </c>
+      <c r="N80">
+        <v>-5.8961616</v>
+      </c>
+      <c r="O80">
+        <v>-1.4740404</v>
+      </c>
+      <c r="P80">
+        <v>-4.4221212</v>
+      </c>
+      <c r="Q80">
+        <v>-1.3421212</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.448455851673086</v>
+      </c>
+      <c r="T80">
+        <v>4.7232859273903</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.01917401414888852</v>
+      </c>
+      <c r="W80">
+        <v>0.2433787545787546</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.07669605659555412</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2904957159395075</v>
+      </c>
+      <c r="C81">
+        <v>-11.03759944192768</v>
+      </c>
+      <c r="D81">
+        <v>8.328400558072317</v>
+      </c>
+      <c r="E81">
+        <v>5.026</v>
+      </c>
+      <c r="F81">
+        <v>23.226</v>
+      </c>
+      <c r="G81">
+        <v>3.86</v>
+      </c>
+      <c r="H81">
+        <v>11.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.66</v>
+      </c>
+      <c r="K81">
+        <v>3.08</v>
+      </c>
+      <c r="L81">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M81">
+        <v>5.5463688</v>
+      </c>
+      <c r="N81">
+        <v>-5.9663688</v>
+      </c>
+      <c r="O81">
+        <v>-1.4915922</v>
+      </c>
+      <c r="P81">
+        <v>-4.4747766</v>
+      </c>
+      <c r="Q81">
+        <v>-1.3947766</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4679632731813281</v>
+      </c>
+      <c r="T81">
+        <v>4.948204304885076</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.01893130510902917</v>
+      </c>
+      <c r="W81">
+        <v>0.2433207956600362</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.07572522043611674</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2924957159395075</v>
+      </c>
+      <c r="C82">
+        <v>-11.39725605364641</v>
+      </c>
+      <c r="D82">
+        <v>8.26274394635359</v>
+      </c>
+      <c r="E82">
+        <v>5.32</v>
+      </c>
+      <c r="F82">
+        <v>23.52</v>
+      </c>
+      <c r="G82">
+        <v>3.86</v>
+      </c>
+      <c r="H82">
+        <v>11.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.66</v>
+      </c>
+      <c r="K82">
+        <v>3.08</v>
+      </c>
+      <c r="L82">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M82">
+        <v>5.616576</v>
+      </c>
+      <c r="N82">
+        <v>-6.036576</v>
+      </c>
+      <c r="O82">
+        <v>-1.509144</v>
+      </c>
+      <c r="P82">
+        <v>-4.527432</v>
+      </c>
+      <c r="Q82">
+        <v>-1.447432</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4894214368403946</v>
+      </c>
+      <c r="T82">
+        <v>5.195614520129331</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.0186946637951663</v>
+      </c>
+      <c r="W82">
+        <v>0.2432642857142857</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.07477865518066529</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2944957159395075</v>
+      </c>
+      <c r="C83">
+        <v>-11.7558855599797</v>
+      </c>
+      <c r="D83">
+        <v>8.1981144400203</v>
+      </c>
+      <c r="E83">
+        <v>5.614000000000001</v>
+      </c>
+      <c r="F83">
+        <v>23.814</v>
+      </c>
+      <c r="G83">
+        <v>3.86</v>
+      </c>
+      <c r="H83">
+        <v>11.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.66</v>
+      </c>
+      <c r="K83">
+        <v>3.08</v>
+      </c>
+      <c r="L83">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M83">
+        <v>5.686783200000001</v>
+      </c>
+      <c r="N83">
+        <v>-6.106783200000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.5266958</v>
+      </c>
+      <c r="P83">
+        <v>-4.5800874</v>
+      </c>
+      <c r="Q83">
+        <v>-1.5000874</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5131383545688365</v>
+      </c>
+      <c r="T83">
+        <v>5.469067915925612</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.01846386547670746</v>
+      </c>
+      <c r="W83">
+        <v>0.2432091710758378</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.0738554619068299</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2964957159395075</v>
+      </c>
+      <c r="C84">
+        <v>-12.11351187530381</v>
+      </c>
+      <c r="D84">
+        <v>8.134488124696187</v>
+      </c>
+      <c r="E84">
+        <v>5.908000000000001</v>
+      </c>
+      <c r="F84">
+        <v>24.108</v>
+      </c>
+      <c r="G84">
+        <v>3.86</v>
+      </c>
+      <c r="H84">
+        <v>11.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.66</v>
+      </c>
+      <c r="K84">
+        <v>3.08</v>
+      </c>
+      <c r="L84">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M84">
+        <v>5.7569904</v>
+      </c>
+      <c r="N84">
+        <v>-6.1769904</v>
+      </c>
+      <c r="O84">
+        <v>-1.5442476</v>
+      </c>
+      <c r="P84">
+        <v>-4.6327428</v>
+      </c>
+      <c r="Q84">
+        <v>-1.5527428</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5394904853782163</v>
+      </c>
+      <c r="T84">
+        <v>5.772905022365924</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.0182386963855281</v>
+      </c>
+      <c r="W84">
+        <v>0.2431554006968641</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.07295478554211243</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2984957159395075</v>
+      </c>
+      <c r="C85">
+        <v>-12.47015817730589</v>
+      </c>
+      <c r="D85">
+        <v>8.071841822694109</v>
+      </c>
+      <c r="E85">
+        <v>6.202000000000002</v>
+      </c>
+      <c r="F85">
+        <v>24.402</v>
+      </c>
+      <c r="G85">
+        <v>3.86</v>
+      </c>
+      <c r="H85">
+        <v>11.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.66</v>
+      </c>
+      <c r="K85">
+        <v>3.08</v>
+      </c>
+      <c r="L85">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M85">
+        <v>5.827197600000001</v>
+      </c>
+      <c r="N85">
+        <v>-6.247197600000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.5617994</v>
+      </c>
+      <c r="P85">
+        <v>-4.685398200000001</v>
+      </c>
+      <c r="Q85">
+        <v>-1.605398200000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5689428668710526</v>
+      </c>
+      <c r="T85">
+        <v>6.112487670740389</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.01801895305558198</v>
+      </c>
+      <c r="W85">
+        <v>0.243102925989673</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.07207581222232795</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3004957159395074</v>
+      </c>
+      <c r="C86">
+        <v>-12.82584693513454</v>
+      </c>
+      <c r="D86">
+        <v>8.010153064865458</v>
+      </c>
+      <c r="E86">
+        <v>6.495999999999999</v>
+      </c>
+      <c r="F86">
+        <v>24.696</v>
+      </c>
+      <c r="G86">
+        <v>3.86</v>
+      </c>
+      <c r="H86">
+        <v>11.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.66</v>
+      </c>
+      <c r="K86">
+        <v>3.08</v>
+      </c>
+      <c r="L86">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M86">
+        <v>5.897404799999999</v>
+      </c>
+      <c r="N86">
+        <v>-6.317404799999999</v>
+      </c>
+      <c r="O86">
+        <v>-1.5793512</v>
+      </c>
+      <c r="P86">
+        <v>-4.7380536</v>
+      </c>
+      <c r="Q86">
+        <v>-1.6580536</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6020767960504929</v>
+      </c>
+      <c r="T86">
+        <v>6.49451815016166</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.0178044417096822</v>
+      </c>
+      <c r="W86">
+        <v>0.2430517006802721</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.07121776683872882</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3024957159395075</v>
+      </c>
+      <c r="C87">
+        <v>-13.1805999362694</v>
+      </c>
+      <c r="D87">
+        <v>7.949400063730596</v>
+      </c>
+      <c r="E87">
+        <v>6.789999999999999</v>
+      </c>
+      <c r="F87">
+        <v>24.99</v>
+      </c>
+      <c r="G87">
+        <v>3.86</v>
+      </c>
+      <c r="H87">
+        <v>11.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.66</v>
+      </c>
+      <c r="K87">
+        <v>3.08</v>
+      </c>
+      <c r="L87">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M87">
+        <v>5.967612</v>
+      </c>
+      <c r="N87">
+        <v>-6.387612</v>
+      </c>
+      <c r="O87">
+        <v>-1.596903</v>
+      </c>
+      <c r="P87">
+        <v>-4.790709</v>
+      </c>
+      <c r="Q87">
+        <v>-1.710709</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6396285824538592</v>
+      </c>
+      <c r="T87">
+        <v>6.927486026839105</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.01759497768956829</v>
+      </c>
+      <c r="W87">
+        <v>0.2430016806722689</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.07037991075827321</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3044957159395075</v>
+      </c>
+      <c r="C88">
+        <v>-13.53443831217713</v>
+      </c>
+      <c r="D88">
+        <v>7.889561687822866</v>
+      </c>
+      <c r="E88">
+        <v>7.084</v>
+      </c>
+      <c r="F88">
+        <v>25.284</v>
+      </c>
+      <c r="G88">
+        <v>3.86</v>
+      </c>
+      <c r="H88">
+        <v>11.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.66</v>
+      </c>
+      <c r="K88">
+        <v>3.08</v>
+      </c>
+      <c r="L88">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M88">
+        <v>6.0378192</v>
+      </c>
+      <c r="N88">
+        <v>-6.4578192</v>
+      </c>
+      <c r="O88">
+        <v>-1.6144548</v>
+      </c>
+      <c r="P88">
+        <v>-4.8433644</v>
+      </c>
+      <c r="Q88">
+        <v>-1.7633644</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6825449097719922</v>
+      </c>
+      <c r="T88">
+        <v>7.422306457327614</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.0173903849257361</v>
+      </c>
+      <c r="W88">
+        <v>0.2429528239202658</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.06956153970294432</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3064957159395075</v>
+      </c>
+      <c r="C89">
+        <v>-13.88738256281733</v>
+      </c>
+      <c r="D89">
+        <v>7.830617437182667</v>
+      </c>
+      <c r="E89">
+        <v>7.378</v>
+      </c>
+      <c r="F89">
+        <v>25.578</v>
+      </c>
+      <c r="G89">
+        <v>3.86</v>
+      </c>
+      <c r="H89">
+        <v>11.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.66</v>
+      </c>
+      <c r="K89">
+        <v>3.08</v>
+      </c>
+      <c r="L89">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M89">
+        <v>6.1080264</v>
+      </c>
+      <c r="N89">
+        <v>-6.5280264</v>
+      </c>
+      <c r="O89">
+        <v>-1.6320066</v>
+      </c>
+      <c r="P89">
+        <v>-4.896019799999999</v>
+      </c>
+      <c r="Q89">
+        <v>-1.816019799999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7320637489852222</v>
+      </c>
+      <c r="T89">
+        <v>7.993253107891276</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.01719049544383108</v>
+      </c>
+      <c r="W89">
+        <v>0.2429050903119869</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.06876198177532444</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3084957159395075</v>
+      </c>
+      <c r="C90">
+        <v>-14.23945258005809</v>
+      </c>
+      <c r="D90">
+        <v>7.772547419941908</v>
+      </c>
+      <c r="E90">
+        <v>7.672000000000001</v>
+      </c>
+      <c r="F90">
+        <v>25.872</v>
+      </c>
+      <c r="G90">
+        <v>3.86</v>
+      </c>
+      <c r="H90">
+        <v>11.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.66</v>
+      </c>
+      <c r="K90">
+        <v>3.08</v>
+      </c>
+      <c r="L90">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M90">
+        <v>6.1782336</v>
+      </c>
+      <c r="N90">
+        <v>-6.5982336</v>
+      </c>
+      <c r="O90">
+        <v>-1.6495584</v>
+      </c>
+      <c r="P90">
+        <v>-4.9486752</v>
+      </c>
+      <c r="Q90">
+        <v>-1.8686752</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7898357280673245</v>
+      </c>
+      <c r="T90">
+        <v>8.659357533548885</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.01699514890469664</v>
+      </c>
+      <c r="W90">
+        <v>0.2428584415584416</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.06798059561878667</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3104957159395074</v>
+      </c>
+      <c r="C91">
+        <v>-14.59066767005732</v>
+      </c>
+      <c r="D91">
+        <v>7.715332329942683</v>
+      </c>
+      <c r="E91">
+        <v>7.966000000000001</v>
+      </c>
+      <c r="F91">
+        <v>26.166</v>
+      </c>
+      <c r="G91">
+        <v>3.86</v>
+      </c>
+      <c r="H91">
+        <v>11.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.66</v>
+      </c>
+      <c r="K91">
+        <v>3.08</v>
+      </c>
+      <c r="L91">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M91">
+        <v>6.2484408</v>
+      </c>
+      <c r="N91">
+        <v>-6.6684408</v>
+      </c>
+      <c r="O91">
+        <v>-1.6671102</v>
+      </c>
+      <c r="P91">
+        <v>-5.0013306</v>
+      </c>
+      <c r="Q91">
+        <v>-1.9213306</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8581117033461718</v>
+      </c>
+      <c r="T91">
+        <v>9.446571854780599</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.01680419217543038</v>
+      </c>
+      <c r="W91">
+        <v>0.2428128410914928</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.06721676870172155</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3124957159395075</v>
+      </c>
+      <c r="C92">
+        <v>-14.94104657466281</v>
+      </c>
+      <c r="D92">
+        <v>7.658953425337189</v>
+      </c>
+      <c r="E92">
+        <v>8.260000000000002</v>
+      </c>
+      <c r="F92">
+        <v>26.46</v>
+      </c>
+      <c r="G92">
+        <v>3.86</v>
+      </c>
+      <c r="H92">
+        <v>11.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.66</v>
+      </c>
+      <c r="K92">
+        <v>3.08</v>
+      </c>
+      <c r="L92">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M92">
+        <v>6.318648</v>
+      </c>
+      <c r="N92">
+        <v>-6.738648</v>
+      </c>
+      <c r="O92">
+        <v>-1.684662</v>
+      </c>
+      <c r="P92">
+        <v>-5.053986</v>
+      </c>
+      <c r="Q92">
+        <v>-1.973986</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9400428736807893</v>
+      </c>
+      <c r="T92">
+        <v>10.39122904025866</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.01661747892903671</v>
+      </c>
+      <c r="W92">
+        <v>0.242768253968254</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.0664699157161468</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3144957159395075</v>
+      </c>
+      <c r="C93">
+        <v>-15.29060749188082</v>
+      </c>
+      <c r="D93">
+        <v>7.603392508119182</v>
+      </c>
+      <c r="E93">
+        <v>8.554000000000002</v>
+      </c>
+      <c r="F93">
+        <v>26.754</v>
+      </c>
+      <c r="G93">
+        <v>3.86</v>
+      </c>
+      <c r="H93">
+        <v>11.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.66</v>
+      </c>
+      <c r="K93">
+        <v>3.08</v>
+      </c>
+      <c r="L93">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M93">
+        <v>6.388855200000001</v>
+      </c>
+      <c r="N93">
+        <v>-6.808855200000001</v>
+      </c>
+      <c r="O93">
+        <v>-1.7022138</v>
+      </c>
+      <c r="P93">
+        <v>-5.106641400000001</v>
+      </c>
+      <c r="Q93">
+        <v>-2.026641400000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.040180970756433</v>
+      </c>
+      <c r="T93">
+        <v>11.54581004473185</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.01643486927047587</v>
+      </c>
+      <c r="W93">
+        <v>0.2427246467817896</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.06573947708190353</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3164957159395075</v>
+      </c>
+      <c r="C94">
+        <v>-15.63936809546014</v>
+      </c>
+      <c r="D94">
+        <v>7.548631904539863</v>
+      </c>
+      <c r="E94">
+        <v>8.847999999999999</v>
+      </c>
+      <c r="F94">
+        <v>27.048</v>
+      </c>
+      <c r="G94">
+        <v>3.86</v>
+      </c>
+      <c r="H94">
+        <v>11.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.66</v>
+      </c>
+      <c r="K94">
+        <v>3.08</v>
+      </c>
+      <c r="L94">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M94">
+        <v>6.4590624</v>
+      </c>
+      <c r="N94">
+        <v>-6.8790624</v>
+      </c>
+      <c r="O94">
+        <v>-1.7197656</v>
+      </c>
+      <c r="P94">
+        <v>-5.1592968</v>
+      </c>
+      <c r="Q94">
+        <v>-2.0792968</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.165353592100987</v>
+      </c>
+      <c r="T94">
+        <v>12.98903630032333</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.01625622938710114</v>
+      </c>
+      <c r="W94">
+        <v>0.2426819875776398</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.06502491754840456</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3184957159395075</v>
+      </c>
+      <c r="C95">
+        <v>-15.98734555363595</v>
+      </c>
+      <c r="D95">
+        <v>7.494654446364048</v>
+      </c>
+      <c r="E95">
+        <v>9.141999999999999</v>
+      </c>
+      <c r="F95">
+        <v>27.342</v>
+      </c>
+      <c r="G95">
+        <v>3.86</v>
+      </c>
+      <c r="H95">
+        <v>11.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.66</v>
+      </c>
+      <c r="K95">
+        <v>3.08</v>
+      </c>
+      <c r="L95">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M95">
+        <v>6.5292696</v>
+      </c>
+      <c r="N95">
+        <v>-6.9492696</v>
+      </c>
+      <c r="O95">
+        <v>-1.7373174</v>
+      </c>
+      <c r="P95">
+        <v>-5.2119522</v>
+      </c>
+      <c r="Q95">
+        <v>-2.1319522</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.326289819543985</v>
+      </c>
+      <c r="T95">
+        <v>14.84461291465524</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.01608143122164843</v>
+      </c>
+      <c r="W95">
+        <v>0.2426402457757297</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.06432572488659383</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3204957159395075</v>
+      </c>
+      <c r="C96">
+        <v>-16.33455654707522</v>
+      </c>
+      <c r="D96">
+        <v>7.441443452924775</v>
+      </c>
+      <c r="E96">
+        <v>9.436</v>
+      </c>
+      <c r="F96">
+        <v>27.636</v>
+      </c>
+      <c r="G96">
+        <v>3.86</v>
+      </c>
+      <c r="H96">
+        <v>11.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.66</v>
+      </c>
+      <c r="K96">
+        <v>3.08</v>
+      </c>
+      <c r="L96">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M96">
+        <v>6.599476800000001</v>
+      </c>
+      <c r="N96">
+        <v>-7.019476800000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.7548692</v>
+      </c>
+      <c r="P96">
+        <v>-5.264607600000001</v>
+      </c>
+      <c r="Q96">
+        <v>-2.184607600000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.54087145613465</v>
+      </c>
+      <c r="T96">
+        <v>17.31871506709778</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.01591035216609898</v>
+      </c>
+      <c r="W96">
+        <v>0.2425993920972645</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.06364140866439594</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3224957159395075</v>
+      </c>
+      <c r="C97">
+        <v>-16.68101728606299</v>
+      </c>
+      <c r="D97">
+        <v>7.38898271393701</v>
+      </c>
+      <c r="E97">
+        <v>9.73</v>
+      </c>
+      <c r="F97">
+        <v>27.93</v>
+      </c>
+      <c r="G97">
+        <v>3.86</v>
+      </c>
+      <c r="H97">
+        <v>11.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.66</v>
+      </c>
+      <c r="K97">
+        <v>3.08</v>
+      </c>
+      <c r="L97">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M97">
+        <v>6.669684</v>
+      </c>
+      <c r="N97">
+        <v>-7.089684</v>
+      </c>
+      <c r="O97">
+        <v>-1.772421</v>
+      </c>
+      <c r="P97">
+        <v>-5.317263000000001</v>
+      </c>
+      <c r="Q97">
+        <v>-2.237263</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.841285747361581</v>
+      </c>
+      <c r="T97">
+        <v>20.78245808051735</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.01574287477487689</v>
+      </c>
+      <c r="W97">
+        <v>0.2425593984962406</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.06297149909950761</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3244957159395075</v>
+      </c>
+      <c r="C98">
+        <v>-17.0267435269668</v>
+      </c>
+      <c r="D98">
+        <v>7.337256473033199</v>
+      </c>
+      <c r="E98">
+        <v>10.024</v>
+      </c>
+      <c r="F98">
+        <v>28.224</v>
+      </c>
+      <c r="G98">
+        <v>3.86</v>
+      </c>
+      <c r="H98">
+        <v>11.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.66</v>
+      </c>
+      <c r="K98">
+        <v>3.08</v>
+      </c>
+      <c r="L98">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M98">
+        <v>6.7398912</v>
+      </c>
+      <c r="N98">
+        <v>-7.1598912</v>
+      </c>
+      <c r="O98">
+        <v>-1.7899728</v>
+      </c>
+      <c r="P98">
+        <v>-5.3699184</v>
+      </c>
+      <c r="Q98">
+        <v>-2.289918399999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.291907184201971</v>
+      </c>
+      <c r="T98">
+        <v>25.97807260064662</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.01557888649597192</v>
+      </c>
+      <c r="W98">
+        <v>0.2425202380952381</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.06231554598388778</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3264957159395075</v>
+      </c>
+      <c r="C99">
+        <v>-17.37175058801442</v>
+      </c>
+      <c r="D99">
+        <v>7.286249411985574</v>
+      </c>
+      <c r="E99">
+        <v>10.318</v>
+      </c>
+      <c r="F99">
+        <v>28.518</v>
+      </c>
+      <c r="G99">
+        <v>3.86</v>
+      </c>
+      <c r="H99">
+        <v>11.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.66</v>
+      </c>
+      <c r="K99">
+        <v>3.08</v>
+      </c>
+      <c r="L99">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M99">
+        <v>6.810098399999999</v>
+      </c>
+      <c r="N99">
+        <v>-7.230098399999999</v>
+      </c>
+      <c r="O99">
+        <v>-1.8075246</v>
+      </c>
+      <c r="P99">
+        <v>-5.422573799999999</v>
+      </c>
+      <c r="Q99">
+        <v>-2.342573799999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.042942912269294</v>
+      </c>
+      <c r="T99">
+        <v>34.6374301341955</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.01541827941869386</v>
+      </c>
+      <c r="W99">
+        <v>0.2424818851251841</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.06167311767477535</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3284957159395075</v>
+      </c>
+      <c r="C100">
+        <v>-17.71605336441797</v>
+      </c>
+      <c r="D100">
+        <v>7.235946635582025</v>
+      </c>
+      <c r="E100">
+        <v>10.612</v>
+      </c>
+      <c r="F100">
+        <v>28.812</v>
+      </c>
+      <c r="G100">
+        <v>3.86</v>
+      </c>
+      <c r="H100">
+        <v>11.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.66</v>
+      </c>
+      <c r="K100">
+        <v>3.08</v>
+      </c>
+      <c r="L100">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M100">
+        <v>6.8803056</v>
+      </c>
+      <c r="N100">
+        <v>-7.3003056</v>
+      </c>
+      <c r="O100">
+        <v>-1.8250764</v>
+      </c>
+      <c r="P100">
+        <v>-5.475229199999999</v>
+      </c>
+      <c r="Q100">
+        <v>-2.395229199999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.545014368403942</v>
+      </c>
+      <c r="T100">
+        <v>51.95614520129325</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.01526095003687045</v>
+      </c>
+      <c r="W100">
+        <v>0.2424443148688047</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.06104380014748179</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3304957159395076</v>
+      </c>
+      <c r="C101">
+        <v>-18.05966634287586</v>
+      </c>
+      <c r="D101">
+        <v>7.186333657124139</v>
+      </c>
+      <c r="E101">
+        <v>10.906</v>
+      </c>
+      <c r="F101">
+        <v>29.106</v>
+      </c>
+      <c r="G101">
+        <v>3.86</v>
+      </c>
+      <c r="H101">
+        <v>11.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.66</v>
+      </c>
+      <c r="K101">
+        <v>3.08</v>
+      </c>
+      <c r="L101">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="M101">
+        <v>6.9505128</v>
+      </c>
+      <c r="N101">
+        <v>-7.3705128</v>
+      </c>
+      <c r="O101">
+        <v>-1.8426282</v>
+      </c>
+      <c r="P101">
+        <v>-5.5278846</v>
+      </c>
+      <c r="Q101">
+        <v>-2.4478846</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.051228736807884</v>
+      </c>
+      <c r="T101">
+        <v>103.9122904025865</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.01510679902639701</v>
+      </c>
+      <c r="W101">
+        <v>0.2424075036075037</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.060427196105588</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_chemical_specialty.xlsx
@@ -1388,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1525,22 +1525,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.106256406523537</v>
+        <v>0.1060245155072281</v>
       </c>
       <c r="C2">
-        <v>26.41828177126134</v>
+        <v>26.21480376795319</v>
       </c>
       <c r="D2">
-        <v>25.12828177126134</v>
+        <v>25.19880376795319</v>
       </c>
       <c r="E2">
-        <v>-15</v>
+        <v>-14.726</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.274</v>
       </c>
       <c r="G2">
         <v>1.29</v>
@@ -1561,28 +1561,28 @@
         <v>2.23</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0137822</v>
       </c>
       <c r="N2">
-        <v>2.23</v>
+        <v>2.2162178</v>
       </c>
       <c r="O2">
-        <v>0.5575000000000001</v>
+        <v>0.5540544500000001</v>
       </c>
       <c r="P2">
-        <v>1.6725</v>
+        <v>1.66216335</v>
       </c>
       <c r="Q2">
-        <v>4.5425</v>
+        <v>4.53216335</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.106256406523537</v>
+        <v>0.1067144096032607</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.9423265434587135</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>161.8029051965579</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1607,22 +1607,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1060245155072281</v>
+        <v>0.1057926244909193</v>
       </c>
       <c r="C3">
-        <v>26.21480376795319</v>
+        <v>26.0117227156943</v>
       </c>
       <c r="D3">
-        <v>25.19880376795319</v>
+        <v>25.2697227156943</v>
       </c>
       <c r="E3">
-        <v>-14.726</v>
+        <v>-14.452</v>
       </c>
       <c r="F3">
-        <v>0.274</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="G3">
         <v>1.29</v>
@@ -1643,28 +1643,28 @@
         <v>2.23</v>
       </c>
       <c r="M3">
-        <v>0.0137822</v>
+        <v>0.0275644</v>
       </c>
       <c r="N3">
-        <v>2.2162178</v>
+        <v>2.2024356</v>
       </c>
       <c r="O3">
-        <v>0.5540544500000001</v>
+        <v>0.5506089000000001</v>
       </c>
       <c r="P3">
-        <v>1.66216335</v>
+        <v>1.6518267</v>
       </c>
       <c r="Q3">
-        <v>4.53216335</v>
+        <v>4.5218267</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1067144096032607</v>
+        <v>0.1071817596846115</v>
       </c>
       <c r="T3">
-        <v>0.9423265434587135</v>
+        <v>0.9495563005820733</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>161.8029051965579</v>
+        <v>80.90145259827896</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1689,22 +1689,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1057926244909193</v>
+        <v>0.1055607334746104</v>
       </c>
       <c r="C4">
-        <v>26.0117227156943</v>
+        <v>25.80904197545409</v>
       </c>
       <c r="D4">
-        <v>25.2697227156943</v>
+        <v>25.34104197545409</v>
       </c>
       <c r="E4">
-        <v>-14.452</v>
+        <v>-14.178</v>
       </c>
       <c r="F4">
-        <v>0.5479999999999999</v>
+        <v>0.822</v>
       </c>
       <c r="G4">
         <v>1.29</v>
@@ -1725,28 +1725,28 @@
         <v>2.23</v>
       </c>
       <c r="M4">
-        <v>0.0275644</v>
+        <v>0.0413466</v>
       </c>
       <c r="N4">
-        <v>2.2024356</v>
+        <v>2.188653400000001</v>
       </c>
       <c r="O4">
-        <v>0.5506089000000001</v>
+        <v>0.5471633500000002</v>
       </c>
       <c r="P4">
-        <v>1.6518267</v>
+        <v>1.64149005</v>
       </c>
       <c r="Q4">
-        <v>4.5218267</v>
+        <v>4.511490050000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1071817596846115</v>
+        <v>0.1076587458501139</v>
       </c>
       <c r="T4">
-        <v>0.9495563005820733</v>
+        <v>0.9569351248626156</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>80.90145259827896</v>
+        <v>53.93430173218598</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1771,22 +1771,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1055607334746104</v>
+        <v>0.1053288424583016</v>
       </c>
       <c r="C5">
-        <v>25.80904197545409</v>
+        <v>25.60676494625228</v>
       </c>
       <c r="D5">
-        <v>25.34104197545409</v>
+        <v>25.41276494625228</v>
       </c>
       <c r="E5">
-        <v>-14.178</v>
+        <v>-13.904</v>
       </c>
       <c r="F5">
-        <v>0.822</v>
+        <v>1.096</v>
       </c>
       <c r="G5">
         <v>1.29</v>
@@ -1807,28 +1807,28 @@
         <v>2.23</v>
       </c>
       <c r="M5">
-        <v>0.0413466</v>
+        <v>0.05512879999999999</v>
       </c>
       <c r="N5">
-        <v>2.188653400000001</v>
+        <v>2.174871200000001</v>
       </c>
       <c r="O5">
-        <v>0.5471633500000002</v>
+        <v>0.5437178000000001</v>
       </c>
       <c r="P5">
-        <v>1.64149005</v>
+        <v>1.631153400000001</v>
       </c>
       <c r="Q5">
-        <v>4.511490050000001</v>
+        <v>4.501153400000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1076587458501139</v>
+        <v>0.1081456692273975</v>
       </c>
       <c r="T5">
-        <v>0.9569351248626156</v>
+        <v>0.9644676746490027</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.93430173218598</v>
+        <v>40.45072629913948</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1053288424583016</v>
+        <v>0.1050969514419928</v>
       </c>
       <c r="C6">
-        <v>25.60676494625228</v>
+        <v>25.40489506569893</v>
       </c>
       <c r="D6">
-        <v>25.41276494625228</v>
+        <v>25.48489506569893</v>
       </c>
       <c r="E6">
-        <v>-13.904</v>
+        <v>-13.63</v>
       </c>
       <c r="F6">
-        <v>1.096</v>
+        <v>1.37</v>
       </c>
       <c r="G6">
         <v>1.29</v>
@@ -1889,28 +1889,28 @@
         <v>2.23</v>
       </c>
       <c r="M6">
-        <v>0.05512879999999999</v>
+        <v>0.068911</v>
       </c>
       <c r="N6">
-        <v>2.174871200000001</v>
+        <v>2.161089</v>
       </c>
       <c r="O6">
-        <v>0.5437178000000001</v>
+        <v>0.5402722500000001</v>
       </c>
       <c r="P6">
-        <v>1.631153400000001</v>
+        <v>1.62081675</v>
       </c>
       <c r="Q6">
-        <v>4.501153400000001</v>
+        <v>4.49081675</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1081456692273975</v>
+        <v>0.1086428436231503</v>
       </c>
       <c r="T6">
-        <v>0.9644676746490027</v>
+        <v>0.9721588044308928</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.45072629913948</v>
+        <v>32.36058103931158</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1935,22 +1935,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1050969514419928</v>
+        <v>0.1048650604256839</v>
       </c>
       <c r="C7">
-        <v>25.40489506569893</v>
+        <v>25.20343581054364</v>
       </c>
       <c r="D7">
-        <v>25.48489506569893</v>
+        <v>25.55743581054364</v>
       </c>
       <c r="E7">
-        <v>-13.63</v>
+        <v>-13.356</v>
       </c>
       <c r="F7">
-        <v>1.37</v>
+        <v>1.644</v>
       </c>
       <c r="G7">
         <v>1.29</v>
@@ -1971,28 +1971,28 @@
         <v>2.23</v>
       </c>
       <c r="M7">
-        <v>0.068911</v>
+        <v>0.08269320000000001</v>
       </c>
       <c r="N7">
-        <v>2.161089</v>
+        <v>2.1473068</v>
       </c>
       <c r="O7">
-        <v>0.5402722500000001</v>
+        <v>0.5368267000000001</v>
       </c>
       <c r="P7">
-        <v>1.62081675</v>
+        <v>1.6104801</v>
       </c>
       <c r="Q7">
-        <v>4.49081675</v>
+        <v>4.4804801</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1086428436231503</v>
+        <v>0.1091505961975361</v>
       </c>
       <c r="T7">
-        <v>0.9721588044308928</v>
+        <v>0.9800135752719719</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.36058103931158</v>
+        <v>26.96715086609298</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2017,22 +2017,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1048650604256839</v>
+        <v>0.1046331694093751</v>
       </c>
       <c r="C8">
-        <v>25.20343581054364</v>
+        <v>25.00239069723417</v>
       </c>
       <c r="D8">
-        <v>25.55743581054364</v>
+        <v>25.63039069723417</v>
       </c>
       <c r="E8">
-        <v>-13.356</v>
+        <v>-13.082</v>
       </c>
       <c r="F8">
-        <v>1.644</v>
+        <v>1.918</v>
       </c>
       <c r="G8">
         <v>1.29</v>
@@ -2053,28 +2053,28 @@
         <v>2.23</v>
       </c>
       <c r="M8">
-        <v>0.08269319999999999</v>
+        <v>0.09647539999999998</v>
       </c>
       <c r="N8">
-        <v>2.1473068</v>
+        <v>2.1335246</v>
       </c>
       <c r="O8">
-        <v>0.5368267000000001</v>
+        <v>0.5333811500000001</v>
       </c>
       <c r="P8">
-        <v>1.6104801</v>
+        <v>1.60014345</v>
       </c>
       <c r="Q8">
-        <v>4.4804801</v>
+        <v>4.47014345</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1091505961975361</v>
+        <v>0.1096692681821237</v>
       </c>
       <c r="T8">
-        <v>0.9800135752719719</v>
+        <v>0.9880372659160849</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.96715086609299</v>
+        <v>23.11470074236542</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2099,22 +2099,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1046331694093751</v>
+        <v>0.1044012783930663</v>
       </c>
       <c r="C9">
-        <v>25.00239069723417</v>
+        <v>24.80176328248469</v>
       </c>
       <c r="D9">
-        <v>25.63039069723417</v>
+        <v>25.70376328248469</v>
       </c>
       <c r="E9">
-        <v>-13.082</v>
+        <v>-12.808</v>
       </c>
       <c r="F9">
-        <v>1.918</v>
+        <v>2.192</v>
       </c>
       <c r="G9">
         <v>1.29</v>
@@ -2135,28 +2135,28 @@
         <v>2.23</v>
       </c>
       <c r="M9">
-        <v>0.0964754</v>
+        <v>0.1102576</v>
       </c>
       <c r="N9">
-        <v>2.1335246</v>
+        <v>2.1197424</v>
       </c>
       <c r="O9">
-        <v>0.5333811500000001</v>
+        <v>0.5299356000000001</v>
       </c>
       <c r="P9">
-        <v>1.60014345</v>
+        <v>1.5898068</v>
       </c>
       <c r="Q9">
-        <v>4.47014345</v>
+        <v>4.459806800000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1096692681821237</v>
+        <v>0.1101992156446372</v>
       </c>
       <c r="T9">
-        <v>0.9880372659160849</v>
+        <v>0.9962353846176788</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.11470074236541</v>
+        <v>20.22536314956974</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1044012783930663</v>
+        <v>0.1041693873767574</v>
       </c>
       <c r="C10">
-        <v>24.80176328248469</v>
+        <v>24.60155716385379</v>
       </c>
       <c r="D10">
-        <v>25.70376328248469</v>
+        <v>25.7775571638538</v>
       </c>
       <c r="E10">
-        <v>-12.808</v>
+        <v>-12.534</v>
       </c>
       <c r="F10">
-        <v>2.192</v>
+        <v>2.466</v>
       </c>
       <c r="G10">
         <v>1.29</v>
@@ -2217,28 +2217,28 @@
         <v>2.23</v>
       </c>
       <c r="M10">
-        <v>0.1102576</v>
+        <v>0.1240398</v>
       </c>
       <c r="N10">
-        <v>2.1197424</v>
+        <v>2.105960200000001</v>
       </c>
       <c r="O10">
-        <v>0.5299356000000001</v>
+        <v>0.5264900500000002</v>
       </c>
       <c r="P10">
-        <v>1.5898068</v>
+        <v>1.579470150000001</v>
       </c>
       <c r="Q10">
-        <v>4.459806800000001</v>
+        <v>4.449470150000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1101992156446372</v>
+        <v>0.110740810304129</v>
       </c>
       <c r="T10">
-        <v>0.9962353846176788</v>
+        <v>1.004613681752275</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.22536314956974</v>
+        <v>17.97810057739533</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1041693873767574</v>
+        <v>0.1039374963604485</v>
       </c>
       <c r="C11">
-        <v>24.60155716385379</v>
+        <v>24.40177598033243</v>
       </c>
       <c r="D11">
-        <v>25.7775571638538</v>
+        <v>25.85177598033243</v>
       </c>
       <c r="E11">
-        <v>-12.534</v>
+        <v>-12.26</v>
       </c>
       <c r="F11">
-        <v>2.466</v>
+        <v>2.74</v>
       </c>
       <c r="G11">
         <v>1.29</v>
@@ -2299,28 +2299,28 @@
         <v>2.23</v>
       </c>
       <c r="M11">
-        <v>0.1240398</v>
+        <v>0.137822</v>
       </c>
       <c r="N11">
-        <v>2.105960200000001</v>
+        <v>2.092178000000001</v>
       </c>
       <c r="O11">
-        <v>0.5264900500000002</v>
+        <v>0.5230445000000001</v>
       </c>
       <c r="P11">
-        <v>1.579470150000001</v>
+        <v>1.5691335</v>
       </c>
       <c r="Q11">
-        <v>4.449470150000001</v>
+        <v>4.439133500000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.110740810304129</v>
+        <v>0.1112944404004984</v>
       </c>
       <c r="T11">
-        <v>1.004613681752275</v>
+        <v>1.013178163267639</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.97810057739533</v>
+        <v>16.1802905196558</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2345,22 +2345,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1039374963604485</v>
+        <v>0.1037056053441397</v>
       </c>
       <c r="C12">
-        <v>24.40177598033243</v>
+        <v>24.20242341294217</v>
       </c>
       <c r="D12">
-        <v>25.85177598033243</v>
+        <v>25.92642341294217</v>
       </c>
       <c r="E12">
-        <v>-12.26</v>
+        <v>-11.986</v>
       </c>
       <c r="F12">
-        <v>2.74</v>
+        <v>3.014</v>
       </c>
       <c r="G12">
         <v>1.29</v>
@@ -2381,28 +2381,28 @@
         <v>2.23</v>
       </c>
       <c r="M12">
-        <v>0.137822</v>
+        <v>0.1516042</v>
       </c>
       <c r="N12">
-        <v>2.092178000000001</v>
+        <v>2.0783958</v>
       </c>
       <c r="O12">
-        <v>0.5230445000000001</v>
+        <v>0.5195989500000001</v>
       </c>
       <c r="P12">
-        <v>1.5691335</v>
+        <v>1.55879685</v>
       </c>
       <c r="Q12">
-        <v>4.439133500000001</v>
+        <v>4.42879685</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1112944404004984</v>
+        <v>0.1118605116226289</v>
       </c>
       <c r="T12">
-        <v>1.013178163267639</v>
+        <v>1.021935105041776</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.18029051965579</v>
+        <v>14.7093550178689</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2427,22 +2427,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1037056053441397</v>
+        <v>0.1034737143278309</v>
       </c>
       <c r="C13">
-        <v>24.20242341294217</v>
+        <v>24.00350318534375</v>
       </c>
       <c r="D13">
-        <v>25.92642341294217</v>
+        <v>26.00150318534375</v>
       </c>
       <c r="E13">
-        <v>-11.986</v>
+        <v>-11.712</v>
       </c>
       <c r="F13">
-        <v>3.014</v>
+        <v>3.288</v>
       </c>
       <c r="G13">
         <v>1.29</v>
@@ -2463,28 +2463,28 @@
         <v>2.23</v>
       </c>
       <c r="M13">
-        <v>0.1516042</v>
+        <v>0.1653864</v>
       </c>
       <c r="N13">
-        <v>2.0783958</v>
+        <v>2.0646136</v>
       </c>
       <c r="O13">
-        <v>0.5195989500000001</v>
+        <v>0.5161534000000001</v>
       </c>
       <c r="P13">
-        <v>1.55879685</v>
+        <v>1.5484602</v>
       </c>
       <c r="Q13">
-        <v>4.42879685</v>
+        <v>4.4184602</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1118605116226289</v>
+        <v>0.1124394480998078</v>
       </c>
       <c r="T13">
-        <v>1.021935105041776</v>
+        <v>1.030891068219871</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.7093550178689</v>
+        <v>13.48357543304649</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2509,22 +2509,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1034737143278309</v>
+        <v>0.103388073311522</v>
       </c>
       <c r="C14">
-        <v>24.00350318534375</v>
+        <v>23.75734140172659</v>
       </c>
       <c r="D14">
-        <v>26.00150318534375</v>
+        <v>26.02934140172659</v>
       </c>
       <c r="E14">
-        <v>-11.712</v>
+        <v>-11.438</v>
       </c>
       <c r="F14">
-        <v>3.288</v>
+        <v>3.562</v>
       </c>
       <c r="G14">
         <v>1.29</v>
@@ -2545,45 +2545,45 @@
         <v>2.23</v>
       </c>
       <c r="M14">
-        <v>0.1653864</v>
+        <v>0.1845116</v>
       </c>
       <c r="N14">
-        <v>2.0646136</v>
+        <v>2.0454884</v>
       </c>
       <c r="O14">
-        <v>0.5161534000000001</v>
+        <v>0.5113721000000001</v>
       </c>
       <c r="P14">
-        <v>1.5484602</v>
+        <v>1.5341163</v>
       </c>
       <c r="Q14">
-        <v>4.4184602</v>
+        <v>4.4041163</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1124394480998078</v>
+        <v>0.1130316934615196</v>
       </c>
       <c r="T14">
-        <v>1.030891068219871</v>
+        <v>1.040052915608956</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.48357543304649</v>
+        <v>12.08596099107048</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2591,22 +2591,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.103388073311522</v>
+        <v>0.1031674322952132</v>
       </c>
       <c r="C15">
-        <v>23.75734140172659</v>
+        <v>23.55533769754145</v>
       </c>
       <c r="D15">
-        <v>26.02934140172659</v>
+        <v>26.10133769754145</v>
       </c>
       <c r="E15">
-        <v>-11.438</v>
+        <v>-11.164</v>
       </c>
       <c r="F15">
-        <v>3.562</v>
+        <v>3.836</v>
       </c>
       <c r="G15">
         <v>1.29</v>
@@ -2627,28 +2627,28 @@
         <v>2.23</v>
       </c>
       <c r="M15">
-        <v>0.1845116</v>
+        <v>0.1987048</v>
       </c>
       <c r="N15">
-        <v>2.0454884</v>
+        <v>2.031295200000001</v>
       </c>
       <c r="O15">
-        <v>0.5113721000000001</v>
+        <v>0.5078238000000002</v>
       </c>
       <c r="P15">
-        <v>1.5341163</v>
+        <v>1.5234714</v>
       </c>
       <c r="Q15">
-        <v>4.4041163</v>
+        <v>4.393471400000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1130316934615196</v>
+        <v>0.1136377119711781</v>
       </c>
       <c r="T15">
-        <v>1.040052915608956</v>
+        <v>1.049427829216392</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.08596099107048</v>
+        <v>11.22267806313688</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2673,22 +2673,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1031674322952132</v>
+        <v>0.1029467912789043</v>
       </c>
       <c r="C16">
-        <v>23.55533769754145</v>
+        <v>23.35373337677474</v>
       </c>
       <c r="D16">
-        <v>26.10133769754145</v>
+        <v>26.17373337677474</v>
       </c>
       <c r="E16">
-        <v>-11.164</v>
+        <v>-10.89</v>
       </c>
       <c r="F16">
-        <v>3.836</v>
+        <v>4.11</v>
       </c>
       <c r="G16">
         <v>1.29</v>
@@ -2709,28 +2709,28 @@
         <v>2.23</v>
       </c>
       <c r="M16">
-        <v>0.1987048</v>
+        <v>0.212898</v>
       </c>
       <c r="N16">
-        <v>2.031295200000001</v>
+        <v>2.017102</v>
       </c>
       <c r="O16">
-        <v>0.5078238000000002</v>
+        <v>0.5042755000000001</v>
       </c>
       <c r="P16">
-        <v>1.5234714</v>
+        <v>1.5128265</v>
       </c>
       <c r="Q16">
-        <v>4.393471400000001</v>
+        <v>4.3828265</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1136377119711781</v>
+        <v>0.1142579897398875</v>
       </c>
       <c r="T16">
-        <v>1.049427829216392</v>
+        <v>1.059023329026356</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.22267806313688</v>
+        <v>10.47449952559442</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2755,22 +2755,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1029467912789043</v>
+        <v>0.1027261502625955</v>
       </c>
       <c r="C17">
-        <v>23.35373337677474</v>
+        <v>23.15253177190544</v>
       </c>
       <c r="D17">
-        <v>26.17373337677474</v>
+        <v>26.24653177190544</v>
       </c>
       <c r="E17">
-        <v>-10.89</v>
+        <v>-10.616</v>
       </c>
       <c r="F17">
-        <v>4.109999999999999</v>
+        <v>4.383999999999999</v>
       </c>
       <c r="G17">
         <v>1.29</v>
@@ -2791,28 +2791,28 @@
         <v>2.23</v>
       </c>
       <c r="M17">
-        <v>0.212898</v>
+        <v>0.2270912</v>
       </c>
       <c r="N17">
-        <v>2.017102</v>
+        <v>2.002908800000001</v>
       </c>
       <c r="O17">
-        <v>0.5042755000000001</v>
+        <v>0.5007272000000001</v>
       </c>
       <c r="P17">
-        <v>1.5128265</v>
+        <v>1.502181600000001</v>
       </c>
       <c r="Q17">
-        <v>4.3828265</v>
+        <v>4.372181600000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1142579897398875</v>
+        <v>0.1148930360268994</v>
       </c>
       <c r="T17">
-        <v>1.059023329026356</v>
+        <v>1.068847293117509</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.47449952559442</v>
+        <v>9.819843305244769</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2837,22 +2837,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1027261502625955</v>
+        <v>0.1027222592462867</v>
       </c>
       <c r="C18">
-        <v>23.15253177190544</v>
+        <v>22.87981920941754</v>
       </c>
       <c r="D18">
-        <v>26.24653177190544</v>
+        <v>26.24781920941754</v>
       </c>
       <c r="E18">
-        <v>-10.616</v>
+        <v>-10.342</v>
       </c>
       <c r="F18">
-        <v>4.383999999999999</v>
+        <v>4.658</v>
       </c>
       <c r="G18">
         <v>1.29</v>
@@ -2873,45 +2873,45 @@
         <v>2.23</v>
       </c>
       <c r="M18">
-        <v>0.2270912</v>
+        <v>0.249203</v>
       </c>
       <c r="N18">
-        <v>2.002908800000001</v>
+        <v>1.980797</v>
       </c>
       <c r="O18">
-        <v>0.5007272000000001</v>
+        <v>0.4951992500000001</v>
       </c>
       <c r="P18">
-        <v>1.502181600000001</v>
+        <v>1.48559775</v>
       </c>
       <c r="Q18">
-        <v>4.372181600000001</v>
+        <v>4.35559775</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1148930360268994</v>
+        <v>0.1155433846340803</v>
       </c>
       <c r="T18">
-        <v>1.068847293117509</v>
+        <v>1.078907979234956</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.819843305244769</v>
+        <v>8.948527906967414</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2919,22 +2919,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1027222592462867</v>
+        <v>0.1025143682299778</v>
       </c>
       <c r="C19">
-        <v>22.87981920941754</v>
+        <v>22.67478914294358</v>
       </c>
       <c r="D19">
-        <v>26.24781920941754</v>
+        <v>26.31678914294358</v>
       </c>
       <c r="E19">
-        <v>-10.342</v>
+        <v>-10.068</v>
       </c>
       <c r="F19">
-        <v>4.658</v>
+        <v>4.932</v>
       </c>
       <c r="G19">
         <v>1.29</v>
@@ -2955,28 +2955,28 @@
         <v>2.23</v>
       </c>
       <c r="M19">
-        <v>0.249203</v>
+        <v>0.263862</v>
       </c>
       <c r="N19">
-        <v>1.980797</v>
+        <v>1.966138</v>
       </c>
       <c r="O19">
-        <v>0.4951992500000001</v>
+        <v>0.4915345000000001</v>
       </c>
       <c r="P19">
-        <v>1.48559775</v>
+        <v>1.4746035</v>
       </c>
       <c r="Q19">
-        <v>4.35559775</v>
+        <v>4.3446035</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1155433846340803</v>
+        <v>0.116209595402412</v>
       </c>
       <c r="T19">
-        <v>1.078907979234956</v>
+        <v>1.089214047940633</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.948527906967414</v>
+        <v>8.451387467691445</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3001,22 +3001,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1025143682299778</v>
+        <v>0.102306477213669</v>
       </c>
       <c r="C20">
-        <v>22.67478914294358</v>
+        <v>22.47012248829727</v>
       </c>
       <c r="D20">
-        <v>26.31678914294358</v>
+        <v>26.38612248829727</v>
       </c>
       <c r="E20">
-        <v>-10.068</v>
+        <v>-9.794</v>
       </c>
       <c r="F20">
-        <v>4.931999999999999</v>
+        <v>5.206</v>
       </c>
       <c r="G20">
         <v>1.29</v>
@@ -3037,28 +3037,28 @@
         <v>2.23</v>
       </c>
       <c r="M20">
-        <v>0.263862</v>
+        <v>0.278521</v>
       </c>
       <c r="N20">
-        <v>1.966138</v>
+        <v>1.951479</v>
       </c>
       <c r="O20">
-        <v>0.4915345000000001</v>
+        <v>0.4878697500000001</v>
       </c>
       <c r="P20">
-        <v>1.4746035</v>
+        <v>1.46360925</v>
       </c>
       <c r="Q20">
-        <v>4.3446035</v>
+        <v>4.33360925</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.116209595402412</v>
+        <v>0.1168922558193444</v>
       </c>
       <c r="T20">
-        <v>1.089214047940633</v>
+        <v>1.099774587478549</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.451387467691447</v>
+        <v>8.006577600970845</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3083,22 +3083,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.102306477213669</v>
+        <v>0.1022185861973601</v>
       </c>
       <c r="C21">
-        <v>22.47012248829727</v>
+        <v>22.22554485417108</v>
       </c>
       <c r="D21">
-        <v>26.38612248829727</v>
+        <v>26.41554485417108</v>
       </c>
       <c r="E21">
-        <v>-9.794</v>
+        <v>-9.52</v>
       </c>
       <c r="F21">
-        <v>5.206</v>
+        <v>5.48</v>
       </c>
       <c r="G21">
         <v>1.29</v>
@@ -3119,45 +3119,45 @@
         <v>2.23</v>
       </c>
       <c r="M21">
-        <v>0.278521</v>
+        <v>0.2975640000000001</v>
       </c>
       <c r="N21">
-        <v>1.951479</v>
+        <v>1.932436</v>
       </c>
       <c r="O21">
-        <v>0.4878697500000001</v>
+        <v>0.4831090000000001</v>
       </c>
       <c r="P21">
-        <v>1.46360925</v>
+        <v>1.449327</v>
       </c>
       <c r="Q21">
-        <v>4.33360925</v>
+        <v>4.319327</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1168922558193444</v>
+        <v>0.1175919827467002</v>
       </c>
       <c r="T21">
-        <v>1.099774587478549</v>
+        <v>1.110599140504912</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>8.006577600970845</v>
+        <v>7.494186124665618</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3165,22 +3165,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1022185861973601</v>
+        <v>0.1020166951810513</v>
       </c>
       <c r="C22">
-        <v>22.22554485417108</v>
+        <v>22.01937893116672</v>
       </c>
       <c r="D22">
-        <v>26.41554485417108</v>
+        <v>26.48337893116672</v>
       </c>
       <c r="E22">
-        <v>-9.52</v>
+        <v>-9.245999999999999</v>
       </c>
       <c r="F22">
-        <v>5.48</v>
+        <v>5.754</v>
       </c>
       <c r="G22">
         <v>1.29</v>
@@ -3201,28 +3201,28 @@
         <v>2.23</v>
       </c>
       <c r="M22">
-        <v>0.2975640000000001</v>
+        <v>0.3124422</v>
       </c>
       <c r="N22">
-        <v>1.932436</v>
+        <v>1.9175578</v>
       </c>
       <c r="O22">
-        <v>0.4831090000000001</v>
+        <v>0.4793894500000001</v>
       </c>
       <c r="P22">
-        <v>1.449327</v>
+        <v>1.43816835</v>
       </c>
       <c r="Q22">
-        <v>4.319327</v>
+        <v>4.308168350000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1175919827467002</v>
+        <v>0.1183094242798118</v>
       </c>
       <c r="T22">
-        <v>1.110599140504912</v>
+        <v>1.121697732848399</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.494186124665618</v>
+        <v>7.137320118729161</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3247,22 +3247,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1020166951810513</v>
+        <v>0.1018148041647424</v>
       </c>
       <c r="C23">
-        <v>22.01937893116672</v>
+        <v>21.81356229558554</v>
       </c>
       <c r="D23">
-        <v>26.48337893116672</v>
+        <v>26.55156229558554</v>
       </c>
       <c r="E23">
-        <v>-9.246</v>
+        <v>-8.972000000000001</v>
       </c>
       <c r="F23">
-        <v>5.754</v>
+        <v>6.028</v>
       </c>
       <c r="G23">
         <v>1.29</v>
@@ -3283,28 +3283,28 @@
         <v>2.23</v>
       </c>
       <c r="M23">
-        <v>0.3124422</v>
+        <v>0.3273204</v>
       </c>
       <c r="N23">
-        <v>1.9175578</v>
+        <v>1.9026796</v>
       </c>
       <c r="O23">
-        <v>0.4793894500000001</v>
+        <v>0.4756699000000001</v>
       </c>
       <c r="P23">
-        <v>1.43816835</v>
+        <v>1.4270097</v>
       </c>
       <c r="Q23">
-        <v>4.308168350000001</v>
+        <v>4.2970097</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1183094242798118</v>
+        <v>0.1190452617496698</v>
       </c>
       <c r="T23">
-        <v>1.121697732848399</v>
+        <v>1.133080904482744</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.137320118729161</v>
+        <v>6.812896476968746</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1018148041647424</v>
+        <v>0.1016129131484336</v>
       </c>
       <c r="C24">
-        <v>21.81356229558554</v>
+        <v>21.60809765218792</v>
       </c>
       <c r="D24">
-        <v>26.55156229558554</v>
+        <v>26.62009765218792</v>
       </c>
       <c r="E24">
-        <v>-8.972000000000001</v>
+        <v>-8.698</v>
       </c>
       <c r="F24">
-        <v>6.028</v>
+        <v>6.302</v>
       </c>
       <c r="G24">
         <v>1.29</v>
@@ -3365,28 +3365,28 @@
         <v>2.23</v>
       </c>
       <c r="M24">
-        <v>0.3273204</v>
+        <v>0.3421986</v>
       </c>
       <c r="N24">
-        <v>1.9026796</v>
+        <v>1.887801400000001</v>
       </c>
       <c r="O24">
-        <v>0.4756699000000001</v>
+        <v>0.4719503500000001</v>
       </c>
       <c r="P24">
-        <v>1.4270097</v>
+        <v>1.41585105</v>
       </c>
       <c r="Q24">
-        <v>4.2970097</v>
+        <v>4.285851050000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1190452617496698</v>
+        <v>0.1198002118810826</v>
       </c>
       <c r="T24">
-        <v>1.133080904482744</v>
+        <v>1.144759742912787</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.812896476968746</v>
+        <v>6.516683586665757</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3411,22 +3411,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1016129131484336</v>
+        <v>0.1014110221321248</v>
       </c>
       <c r="C25">
-        <v>21.60809765218792</v>
+        <v>21.40298773373284</v>
       </c>
       <c r="D25">
-        <v>26.62009765218792</v>
+        <v>26.68898773373284</v>
       </c>
       <c r="E25">
-        <v>-8.698</v>
+        <v>-8.423999999999999</v>
       </c>
       <c r="F25">
-        <v>6.302</v>
+        <v>6.576000000000001</v>
       </c>
       <c r="G25">
         <v>1.29</v>
@@ -3447,28 +3447,28 @@
         <v>2.23</v>
       </c>
       <c r="M25">
-        <v>0.3421986</v>
+        <v>0.3570768</v>
       </c>
       <c r="N25">
-        <v>1.887801400000001</v>
+        <v>1.8729232</v>
       </c>
       <c r="O25">
-        <v>0.4719503500000001</v>
+        <v>0.4682308000000001</v>
       </c>
       <c r="P25">
-        <v>1.41585105</v>
+        <v>1.4046924</v>
       </c>
       <c r="Q25">
-        <v>4.285851050000001</v>
+        <v>4.2746924</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1198002118810826</v>
+        <v>0.1205750291212168</v>
       </c>
       <c r="T25">
-        <v>1.144759742912787</v>
+        <v>1.156745919196252</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.516683586665757</v>
+        <v>6.245155103888016</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3493,22 +3493,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1014110221321248</v>
+        <v>0.1013966311158159</v>
       </c>
       <c r="C26">
-        <v>21.40298773373284</v>
+        <v>21.13391191179103</v>
       </c>
       <c r="D26">
-        <v>26.68898773373284</v>
+        <v>26.69391191179103</v>
       </c>
       <c r="E26">
-        <v>-8.423999999999999</v>
+        <v>-8.15</v>
       </c>
       <c r="F26">
-        <v>6.576</v>
+        <v>6.85</v>
       </c>
       <c r="G26">
         <v>1.29</v>
@@ -3529,45 +3529,45 @@
         <v>2.23</v>
       </c>
       <c r="M26">
-        <v>0.3570768</v>
+        <v>0.378805</v>
       </c>
       <c r="N26">
-        <v>1.8729232</v>
+        <v>1.851195</v>
       </c>
       <c r="O26">
-        <v>0.4682308000000001</v>
+        <v>0.4627987500000001</v>
       </c>
       <c r="P26">
-        <v>1.4046924</v>
+        <v>1.38839625</v>
       </c>
       <c r="Q26">
-        <v>4.2746924</v>
+        <v>4.258396250000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1205750291212168</v>
+        <v>0.1213705081544212</v>
       </c>
       <c r="T26">
-        <v>1.156745919196252</v>
+        <v>1.169051726847276</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.245155103888017</v>
+        <v>5.886933910587242</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3575,22 +3575,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1013966311158159</v>
+        <v>0.1012022400995071</v>
       </c>
       <c r="C27">
-        <v>21.13391191179103</v>
+        <v>20.92660522652356</v>
       </c>
       <c r="D27">
-        <v>26.69391191179103</v>
+        <v>26.76060522652356</v>
       </c>
       <c r="E27">
-        <v>-8.15</v>
+        <v>-7.876</v>
       </c>
       <c r="F27">
-        <v>6.85</v>
+        <v>7.124</v>
       </c>
       <c r="G27">
         <v>1.29</v>
@@ -3611,28 +3611,28 @@
         <v>2.23</v>
       </c>
       <c r="M27">
-        <v>0.378805</v>
+        <v>0.3939572</v>
       </c>
       <c r="N27">
-        <v>1.851195</v>
+        <v>1.8360428</v>
       </c>
       <c r="O27">
-        <v>0.4627987500000001</v>
+        <v>0.4590107000000001</v>
       </c>
       <c r="P27">
-        <v>1.38839625</v>
+        <v>1.3770321</v>
       </c>
       <c r="Q27">
-        <v>4.258396250000001</v>
+        <v>4.2470321</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1213705081544212</v>
+        <v>0.1221874866209555</v>
       </c>
       <c r="T27">
-        <v>1.169051726847276</v>
+        <v>1.181690123894274</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.886933910587242</v>
+        <v>5.660513375564657</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3657,22 +3657,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1012022400995071</v>
+        <v>0.1010078490831982</v>
       </c>
       <c r="C28">
-        <v>20.92660522652356</v>
+        <v>20.7196326353496</v>
       </c>
       <c r="D28">
-        <v>26.76060522652356</v>
+        <v>26.8276326353496</v>
       </c>
       <c r="E28">
-        <v>-7.876</v>
+        <v>-7.602</v>
       </c>
       <c r="F28">
-        <v>7.124</v>
+        <v>7.398</v>
       </c>
       <c r="G28">
         <v>1.29</v>
@@ -3693,28 +3693,28 @@
         <v>2.23</v>
       </c>
       <c r="M28">
-        <v>0.3939572</v>
+        <v>0.4091094</v>
       </c>
       <c r="N28">
-        <v>1.8360428</v>
+        <v>1.8208906</v>
       </c>
       <c r="O28">
-        <v>0.4590107000000001</v>
+        <v>0.4552226500000001</v>
       </c>
       <c r="P28">
-        <v>1.3770321</v>
+        <v>1.36566795</v>
       </c>
       <c r="Q28">
-        <v>4.2470321</v>
+        <v>4.235667950000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1221874866209555</v>
+        <v>0.1230268480591757</v>
       </c>
       <c r="T28">
-        <v>1.181690123894274</v>
+        <v>1.194674778394614</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.660513375564657</v>
+        <v>5.450864732025225</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3739,22 +3739,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1010078490831982</v>
+        <v>0.1008134580668894</v>
       </c>
       <c r="C29">
-        <v>20.7196326353496</v>
+        <v>20.51299665499377</v>
       </c>
       <c r="D29">
-        <v>26.8276326353496</v>
+        <v>26.89499665499378</v>
       </c>
       <c r="E29">
-        <v>-7.602</v>
+        <v>-7.327999999999999</v>
       </c>
       <c r="F29">
-        <v>7.398</v>
+        <v>7.672000000000001</v>
       </c>
       <c r="G29">
         <v>1.29</v>
@@ -3775,28 +3775,28 @@
         <v>2.23</v>
       </c>
       <c r="M29">
-        <v>0.4091094</v>
+        <v>0.4242616000000001</v>
       </c>
       <c r="N29">
-        <v>1.8208906</v>
+        <v>1.8057384</v>
       </c>
       <c r="O29">
-        <v>0.4552226500000001</v>
+        <v>0.4514346000000001</v>
       </c>
       <c r="P29">
-        <v>1.36566795</v>
+        <v>1.3543038</v>
       </c>
       <c r="Q29">
-        <v>4.235667950000001</v>
+        <v>4.2243038</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1230268480591757</v>
+        <v>0.1238895250929019</v>
       </c>
       <c r="T29">
-        <v>1.194674778394614</v>
+        <v>1.208020117742185</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.450864732025225</v>
+        <v>5.256190991595751</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3821,22 +3821,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1008134580668894</v>
+        <v>0.1006190670505805</v>
       </c>
       <c r="C30">
-        <v>20.51299665499377</v>
+        <v>20.30669982752223</v>
       </c>
       <c r="D30">
-        <v>26.89499665499378</v>
+        <v>26.96269982752224</v>
       </c>
       <c r="E30">
-        <v>-7.327999999999999</v>
+        <v>-7.053999999999999</v>
       </c>
       <c r="F30">
-        <v>7.672000000000001</v>
+        <v>7.946000000000001</v>
       </c>
       <c r="G30">
         <v>1.29</v>
@@ -3857,28 +3857,28 @@
         <v>2.23</v>
       </c>
       <c r="M30">
-        <v>0.4242616000000001</v>
+        <v>0.4394138000000001</v>
       </c>
       <c r="N30">
-        <v>1.8057384</v>
+        <v>1.7905862</v>
       </c>
       <c r="O30">
-        <v>0.4514346000000001</v>
+        <v>0.4476465500000001</v>
       </c>
       <c r="P30">
-        <v>1.3543038</v>
+        <v>1.34293965</v>
       </c>
       <c r="Q30">
-        <v>4.2243038</v>
+        <v>4.212939650000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1238895250929019</v>
+        <v>0.1247765028881416</v>
       </c>
       <c r="T30">
-        <v>1.208020117742185</v>
+        <v>1.221741382141801</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.256190991595751</v>
+        <v>5.074943026368311</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1006190670505805</v>
+        <v>0.1004246760342717</v>
       </c>
       <c r="C31">
-        <v>20.30669982752224</v>
+        <v>20.10074472066246</v>
       </c>
       <c r="D31">
-        <v>26.96269982752224</v>
+        <v>27.03074472066246</v>
       </c>
       <c r="E31">
-        <v>-7.054000000000001</v>
+        <v>-6.780000000000001</v>
       </c>
       <c r="F31">
-        <v>7.945999999999999</v>
+        <v>8.219999999999999</v>
       </c>
       <c r="G31">
         <v>1.29</v>
@@ -3939,28 +3939,28 @@
         <v>2.23</v>
       </c>
       <c r="M31">
-        <v>0.4394138</v>
+        <v>0.454566</v>
       </c>
       <c r="N31">
-        <v>1.7905862</v>
+        <v>1.775434</v>
       </c>
       <c r="O31">
-        <v>0.4476465500000001</v>
+        <v>0.4438585000000001</v>
       </c>
       <c r="P31">
-        <v>1.34293965</v>
+        <v>1.3315755</v>
       </c>
       <c r="Q31">
-        <v>4.212939650000001</v>
+        <v>4.201575500000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1247765028881416</v>
+        <v>0.1256888229061024</v>
       </c>
       <c r="T31">
-        <v>1.221741382141801</v>
+        <v>1.23585468266712</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.074943026368313</v>
+        <v>4.905778258822702</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3985,22 +3985,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1004246760342717</v>
+        <v>0.1002302850179628</v>
       </c>
       <c r="C32">
-        <v>20.10074472066246</v>
+        <v>19.89513392812787</v>
       </c>
       <c r="D32">
-        <v>27.03074472066246</v>
+        <v>27.09913392812787</v>
       </c>
       <c r="E32">
-        <v>-6.780000000000001</v>
+        <v>-6.506</v>
       </c>
       <c r="F32">
-        <v>8.219999999999999</v>
+        <v>8.494</v>
       </c>
       <c r="G32">
         <v>1.29</v>
@@ -4021,28 +4021,28 @@
         <v>2.23</v>
       </c>
       <c r="M32">
-        <v>0.454566</v>
+        <v>0.4697182</v>
       </c>
       <c r="N32">
-        <v>1.775434</v>
+        <v>1.7602818</v>
       </c>
       <c r="O32">
-        <v>0.4438585000000001</v>
+        <v>0.4400704500000001</v>
       </c>
       <c r="P32">
-        <v>1.3315755</v>
+        <v>1.32021135</v>
       </c>
       <c r="Q32">
-        <v>4.201575500000001</v>
+        <v>4.19021135</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1256888229061024</v>
+        <v>0.1266275869825549</v>
       </c>
       <c r="T32">
-        <v>1.23585468266712</v>
+        <v>1.250377064367087</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.905778258822702</v>
+        <v>4.747527347247776</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4067,22 +4067,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1002302850179628</v>
+        <v>0.100035894001654</v>
       </c>
       <c r="C33">
-        <v>19.89513392812787</v>
+        <v>19.68987006994739</v>
       </c>
       <c r="D33">
-        <v>27.09913392812787</v>
+        <v>27.16787006994739</v>
       </c>
       <c r="E33">
-        <v>-6.506</v>
+        <v>-6.232000000000001</v>
       </c>
       <c r="F33">
-        <v>8.494</v>
+        <v>8.767999999999999</v>
       </c>
       <c r="G33">
         <v>1.29</v>
@@ -4103,28 +4103,28 @@
         <v>2.23</v>
       </c>
       <c r="M33">
-        <v>0.4697182</v>
+        <v>0.4848704</v>
       </c>
       <c r="N33">
-        <v>1.7602818</v>
+        <v>1.745129600000001</v>
       </c>
       <c r="O33">
-        <v>0.4400704500000001</v>
+        <v>0.4362824000000001</v>
       </c>
       <c r="P33">
-        <v>1.32021135</v>
+        <v>1.3088472</v>
       </c>
       <c r="Q33">
-        <v>4.19021135</v>
+        <v>4.178847200000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1266275869825549</v>
+        <v>0.1275939617671383</v>
       </c>
       <c r="T33">
-        <v>1.250377064367087</v>
+        <v>1.265326574940581</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.747527347247776</v>
+        <v>4.599167117646283</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4149,22 +4149,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.100035894001654</v>
+        <v>0.1004602529853452</v>
       </c>
       <c r="C34">
-        <v>19.68987006994739</v>
+        <v>19.26626565231678</v>
       </c>
       <c r="D34">
-        <v>27.16787006994739</v>
+        <v>27.01826565231677</v>
       </c>
       <c r="E34">
-        <v>-6.232000000000001</v>
+        <v>-5.958</v>
       </c>
       <c r="F34">
-        <v>8.767999999999999</v>
+        <v>9.042</v>
       </c>
       <c r="G34">
         <v>1.29</v>
@@ -4185,45 +4185,45 @@
         <v>2.23</v>
       </c>
       <c r="M34">
-        <v>0.4848704</v>
+        <v>0.5226276000000001</v>
       </c>
       <c r="N34">
-        <v>1.745129600000001</v>
+        <v>1.7073724</v>
       </c>
       <c r="O34">
-        <v>0.4362824000000001</v>
+        <v>0.4268431000000001</v>
       </c>
       <c r="P34">
-        <v>1.3088472</v>
+        <v>1.2805293</v>
       </c>
       <c r="Q34">
-        <v>4.178847200000001</v>
+        <v>4.150529300000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1275939617671383</v>
+        <v>0.1285891835602167</v>
       </c>
       <c r="T34">
-        <v>1.265326574940581</v>
+        <v>1.280722339561046</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.599167117646283</v>
+        <v>4.266900561700147</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4231,22 +4231,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1004602529853452</v>
+        <v>0.1002846119690363</v>
       </c>
       <c r="C35">
-        <v>19.26626565231678</v>
+        <v>19.05398620493096</v>
       </c>
       <c r="D35">
-        <v>27.01826565231677</v>
+        <v>27.07998620493096</v>
       </c>
       <c r="E35">
-        <v>-5.958</v>
+        <v>-5.683999999999999</v>
       </c>
       <c r="F35">
-        <v>9.042</v>
+        <v>9.316000000000001</v>
       </c>
       <c r="G35">
         <v>1.29</v>
@@ -4267,28 +4267,28 @@
         <v>2.23</v>
       </c>
       <c r="M35">
-        <v>0.5226276000000001</v>
+        <v>0.5384648000000001</v>
       </c>
       <c r="N35">
-        <v>1.7073724</v>
+        <v>1.6915352</v>
       </c>
       <c r="O35">
-        <v>0.4268431000000001</v>
+        <v>0.4228838000000001</v>
       </c>
       <c r="P35">
-        <v>1.2805293</v>
+        <v>1.2686514</v>
       </c>
       <c r="Q35">
-        <v>4.150529300000001</v>
+        <v>4.138651400000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1285891835602167</v>
+        <v>0.129614563589449</v>
       </c>
       <c r="T35">
-        <v>1.280722339561046</v>
+        <v>1.296584642503343</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.266900561700147</v>
+        <v>4.141403486356026</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4313,22 +4313,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1002846119690363</v>
+        <v>0.1001089709527275</v>
       </c>
       <c r="C36">
-        <v>19.05398620493096</v>
+        <v>18.84198939217811</v>
       </c>
       <c r="D36">
-        <v>27.07998620493096</v>
+        <v>27.14198939217811</v>
       </c>
       <c r="E36">
-        <v>-5.683999999999999</v>
+        <v>-5.41</v>
       </c>
       <c r="F36">
-        <v>9.316000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="G36">
         <v>1.29</v>
@@ -4349,28 +4349,28 @@
         <v>2.23</v>
       </c>
       <c r="M36">
-        <v>0.5384648000000001</v>
+        <v>0.5543020000000001</v>
       </c>
       <c r="N36">
-        <v>1.6915352</v>
+        <v>1.675698</v>
       </c>
       <c r="O36">
-        <v>0.4228838000000001</v>
+        <v>0.4189245000000001</v>
       </c>
       <c r="P36">
-        <v>1.2686514</v>
+        <v>1.2567735</v>
       </c>
       <c r="Q36">
-        <v>4.138651400000001</v>
+        <v>4.126773500000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.129614563589449</v>
+        <v>0.1306714937734269</v>
       </c>
       <c r="T36">
-        <v>1.296584642503343</v>
+        <v>1.312935016305403</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.141403486356026</v>
+        <v>4.02307767246014</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1001089709527275</v>
+        <v>0.1008783299364187</v>
       </c>
       <c r="C37">
-        <v>18.84198939217811</v>
+        <v>18.29847845924019</v>
       </c>
       <c r="D37">
-        <v>27.14198939217811</v>
+        <v>26.87247845924019</v>
       </c>
       <c r="E37">
-        <v>-5.41</v>
+        <v>-5.135999999999999</v>
       </c>
       <c r="F37">
-        <v>9.59</v>
+        <v>9.864000000000001</v>
       </c>
       <c r="G37">
         <v>1.29</v>
@@ -4431,45 +4431,45 @@
         <v>2.23</v>
       </c>
       <c r="M37">
-        <v>0.5543020000000001</v>
+        <v>0.6046632000000001</v>
       </c>
       <c r="N37">
-        <v>1.675698</v>
+        <v>1.6253368</v>
       </c>
       <c r="O37">
-        <v>0.4189245000000001</v>
+        <v>0.4063342000000001</v>
       </c>
       <c r="P37">
-        <v>1.2567735</v>
+        <v>1.2190026</v>
       </c>
       <c r="Q37">
-        <v>4.126773500000001</v>
+        <v>4.089002600000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1306714937734269</v>
+        <v>0.1317614530256541</v>
       </c>
       <c r="T37">
-        <v>1.312935016305403</v>
+        <v>1.329796339288777</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.02307767246014</v>
+        <v>3.688003503437947</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4477,22 +4477,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1008783299364187</v>
+        <v>0.1007289389201098</v>
       </c>
       <c r="C38">
-        <v>18.29847845924019</v>
+        <v>18.07639145116793</v>
       </c>
       <c r="D38">
-        <v>26.87247845924019</v>
+        <v>26.92439145116793</v>
       </c>
       <c r="E38">
-        <v>-5.136000000000001</v>
+        <v>-4.862</v>
       </c>
       <c r="F38">
-        <v>9.863999999999999</v>
+        <v>10.138</v>
       </c>
       <c r="G38">
         <v>1.29</v>
@@ -4513,28 +4513,28 @@
         <v>2.23</v>
       </c>
       <c r="M38">
-        <v>0.6046632</v>
+        <v>0.6214594</v>
       </c>
       <c r="N38">
-        <v>1.6253368</v>
+        <v>1.6085406</v>
       </c>
       <c r="O38">
-        <v>0.4063342000000001</v>
+        <v>0.4021351500000001</v>
       </c>
       <c r="P38">
-        <v>1.2190026</v>
+        <v>1.20640545</v>
       </c>
       <c r="Q38">
-        <v>4.089002600000001</v>
+        <v>4.07640545</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1317614530256541</v>
+        <v>0.1328860141589044</v>
       </c>
       <c r="T38">
-        <v>1.329796339288777</v>
+        <v>1.347192942366861</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.688003503437948</v>
+        <v>3.58832773307476</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4559,22 +4559,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1007289389201098</v>
+        <v>0.101377547903801</v>
       </c>
       <c r="C39">
-        <v>18.07639145116793</v>
+        <v>17.57844442274576</v>
       </c>
       <c r="D39">
-        <v>26.92439145116793</v>
+        <v>26.70044442274576</v>
       </c>
       <c r="E39">
-        <v>-4.862</v>
+        <v>-4.588000000000001</v>
       </c>
       <c r="F39">
-        <v>10.138</v>
+        <v>10.412</v>
       </c>
       <c r="G39">
         <v>1.29</v>
@@ -4595,45 +4595,45 @@
         <v>2.23</v>
       </c>
       <c r="M39">
-        <v>0.6214594</v>
+        <v>0.6674092</v>
       </c>
       <c r="N39">
-        <v>1.6085406</v>
+        <v>1.5625908</v>
       </c>
       <c r="O39">
-        <v>0.4021351500000001</v>
+        <v>0.3906477000000001</v>
       </c>
       <c r="P39">
-        <v>1.20640545</v>
+        <v>1.1719431</v>
       </c>
       <c r="Q39">
-        <v>4.07640545</v>
+        <v>4.0419431</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1328860141589044</v>
+        <v>0.1340468514577435</v>
       </c>
       <c r="T39">
-        <v>1.347192942366861</v>
+        <v>1.3651507261894</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.58832773307476</v>
+        <v>3.341278484024494</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4641,22 +4641,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.101377547903801</v>
+        <v>0.1012491568874921</v>
       </c>
       <c r="C40">
-        <v>17.57844442274576</v>
+        <v>17.34847812614326</v>
       </c>
       <c r="D40">
-        <v>26.70044442274576</v>
+        <v>26.74447812614326</v>
       </c>
       <c r="E40">
-        <v>-4.588000000000001</v>
+        <v>-4.314</v>
       </c>
       <c r="F40">
-        <v>10.412</v>
+        <v>10.686</v>
       </c>
       <c r="G40">
         <v>1.29</v>
@@ -4677,28 +4677,28 @@
         <v>2.23</v>
       </c>
       <c r="M40">
-        <v>0.6674092</v>
+        <v>0.6849726</v>
       </c>
       <c r="N40">
-        <v>1.5625908</v>
+        <v>1.5450274</v>
       </c>
       <c r="O40">
-        <v>0.3906477000000001</v>
+        <v>0.3862568500000001</v>
       </c>
       <c r="P40">
-        <v>1.1719431</v>
+        <v>1.15877055</v>
       </c>
       <c r="Q40">
-        <v>4.0419431</v>
+        <v>4.028770550000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1340468514577435</v>
+        <v>0.1352457489958887</v>
       </c>
       <c r="T40">
-        <v>1.3651507261894</v>
+        <v>1.383697289809399</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.341278484024494</v>
+        <v>3.255604676741815</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1012491568874921</v>
+        <v>0.1011207658711833</v>
       </c>
       <c r="C41">
-        <v>17.34847812614326</v>
+        <v>17.1186573080191</v>
       </c>
       <c r="D41">
-        <v>26.74447812614326</v>
+        <v>26.7886573080191</v>
       </c>
       <c r="E41">
-        <v>-4.314</v>
+        <v>-4.039999999999999</v>
       </c>
       <c r="F41">
-        <v>10.686</v>
+        <v>10.96</v>
       </c>
       <c r="G41">
         <v>1.29</v>
@@ -4759,28 +4759,28 @@
         <v>2.23</v>
       </c>
       <c r="M41">
-        <v>0.6849726</v>
+        <v>0.702536</v>
       </c>
       <c r="N41">
-        <v>1.5450274</v>
+        <v>1.527464</v>
       </c>
       <c r="O41">
-        <v>0.3862568500000001</v>
+        <v>0.3818660000000001</v>
       </c>
       <c r="P41">
-        <v>1.15877055</v>
+        <v>1.145598</v>
       </c>
       <c r="Q41">
-        <v>4.028770550000001</v>
+        <v>4.015598000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1352457489958887</v>
+        <v>0.1364846097853055</v>
       </c>
       <c r="T41">
-        <v>1.383697289809399</v>
+        <v>1.402862072216731</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.255604676741815</v>
+        <v>3.174214559823269</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4805,22 +4805,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1011207658711833</v>
+        <v>0.1009923748548744</v>
       </c>
       <c r="C42">
-        <v>17.1186573080191</v>
+        <v>16.88898269051355</v>
       </c>
       <c r="D42">
-        <v>26.7886573080191</v>
+        <v>26.83298269051355</v>
       </c>
       <c r="E42">
-        <v>-4.039999999999999</v>
+        <v>-3.766</v>
       </c>
       <c r="F42">
-        <v>10.96</v>
+        <v>11.234</v>
       </c>
       <c r="G42">
         <v>1.29</v>
@@ -4841,28 +4841,28 @@
         <v>2.23</v>
       </c>
       <c r="M42">
-        <v>0.702536</v>
+        <v>0.7200994000000001</v>
       </c>
       <c r="N42">
-        <v>1.527464</v>
+        <v>1.5099006</v>
       </c>
       <c r="O42">
-        <v>0.3818660000000001</v>
+        <v>0.3774751500000001</v>
       </c>
       <c r="P42">
-        <v>1.145598</v>
+        <v>1.13242545</v>
       </c>
       <c r="Q42">
-        <v>4.015598000000001</v>
+        <v>4.00242545</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1364846097853055</v>
+        <v>0.1377654658557194</v>
       </c>
       <c r="T42">
-        <v>1.402862072216731</v>
+        <v>1.42267650826499</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.174214559823269</v>
+        <v>3.096794692510506</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4887,22 +4887,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1009923748548744</v>
+        <v>0.1008639838385656</v>
       </c>
       <c r="C43">
-        <v>16.88898269051355</v>
+        <v>16.65945500055427</v>
       </c>
       <c r="D43">
-        <v>26.83298269051355</v>
+        <v>26.87745500055427</v>
       </c>
       <c r="E43">
-        <v>-3.766</v>
+        <v>-3.491999999999999</v>
       </c>
       <c r="F43">
-        <v>11.234</v>
+        <v>11.508</v>
       </c>
       <c r="G43">
         <v>1.29</v>
@@ -4923,28 +4923,28 @@
         <v>2.23</v>
       </c>
       <c r="M43">
-        <v>0.7200994000000001</v>
+        <v>0.7376628000000001</v>
       </c>
       <c r="N43">
-        <v>1.5099006</v>
+        <v>1.4923372</v>
       </c>
       <c r="O43">
-        <v>0.3774751500000001</v>
+        <v>0.3730843000000001</v>
       </c>
       <c r="P43">
-        <v>1.13242545</v>
+        <v>1.1192529</v>
       </c>
       <c r="Q43">
-        <v>4.00242545</v>
+        <v>3.9892529</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1377654658557194</v>
+        <v>0.1390904893768372</v>
       </c>
       <c r="T43">
-        <v>1.42267650826499</v>
+        <v>1.443174200728706</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.096794692510506</v>
+        <v>3.023061485545971</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1008639838385656</v>
+        <v>0.1032510928222568</v>
       </c>
       <c r="C44">
-        <v>16.65945500055426</v>
+        <v>15.58199200993991</v>
       </c>
       <c r="D44">
-        <v>26.87745500055426</v>
+        <v>26.07399200993991</v>
       </c>
       <c r="E44">
-        <v>-3.492000000000001</v>
+        <v>-3.218</v>
       </c>
       <c r="F44">
-        <v>11.508</v>
+        <v>11.782</v>
       </c>
       <c r="G44">
         <v>1.29</v>
@@ -5005,45 +5005,45 @@
         <v>2.23</v>
       </c>
       <c r="M44">
-        <v>0.7376628</v>
+        <v>0.8471258</v>
       </c>
       <c r="N44">
-        <v>1.492337200000001</v>
+        <v>1.3828742</v>
       </c>
       <c r="O44">
-        <v>0.3730843000000001</v>
+        <v>0.3457185500000001</v>
       </c>
       <c r="P44">
-        <v>1.1192529</v>
+        <v>1.03715565</v>
       </c>
       <c r="Q44">
-        <v>3.9892529</v>
+        <v>3.90715565</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1390904893768372</v>
+        <v>0.1404620049513276</v>
       </c>
       <c r="T44">
-        <v>1.443174200728706</v>
+        <v>1.464391110471851</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.023061485545971</v>
+        <v>2.632430744052418</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5051,22 +5051,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1032510928222568</v>
+        <v>0.1031812018059479</v>
       </c>
       <c r="C45">
-        <v>15.58199200993991</v>
+        <v>15.33083298545358</v>
       </c>
       <c r="D45">
-        <v>26.07399200993991</v>
+        <v>26.09683298545358</v>
       </c>
       <c r="E45">
-        <v>-3.218</v>
+        <v>-2.944000000000001</v>
       </c>
       <c r="F45">
-        <v>11.782</v>
+        <v>12.056</v>
       </c>
       <c r="G45">
         <v>1.29</v>
@@ -5087,28 +5087,28 @@
         <v>2.23</v>
       </c>
       <c r="M45">
-        <v>0.8471258</v>
+        <v>0.8668264</v>
       </c>
       <c r="N45">
-        <v>1.3828742</v>
+        <v>1.363173600000001</v>
       </c>
       <c r="O45">
-        <v>0.3457185500000001</v>
+        <v>0.3407934000000001</v>
       </c>
       <c r="P45">
-        <v>1.03715565</v>
+        <v>1.0223802</v>
       </c>
       <c r="Q45">
-        <v>3.90715565</v>
+        <v>3.892380200000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1404620049513276</v>
+        <v>0.141882503224907</v>
       </c>
       <c r="T45">
-        <v>1.464391110471851</v>
+        <v>1.486365766991537</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.632430744052418</v>
+        <v>2.572602772596682</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5133,22 +5133,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1031812018059479</v>
+        <v>0.1031113107896391</v>
       </c>
       <c r="C46">
-        <v>15.33083298545358</v>
+        <v>15.07971401372051</v>
       </c>
       <c r="D46">
-        <v>26.09683298545358</v>
+        <v>26.11971401372051</v>
       </c>
       <c r="E46">
-        <v>-2.944000000000001</v>
+        <v>-2.67</v>
       </c>
       <c r="F46">
-        <v>12.056</v>
+        <v>12.33</v>
       </c>
       <c r="G46">
         <v>1.29</v>
@@ -5169,28 +5169,28 @@
         <v>2.23</v>
       </c>
       <c r="M46">
-        <v>0.8668264</v>
+        <v>0.8865270000000001</v>
       </c>
       <c r="N46">
-        <v>1.363173600000001</v>
+        <v>1.343473</v>
       </c>
       <c r="O46">
-        <v>0.3407934000000001</v>
+        <v>0.3358682500000001</v>
       </c>
       <c r="P46">
-        <v>1.0223802</v>
+        <v>1.00760475</v>
       </c>
       <c r="Q46">
-        <v>3.892380200000001</v>
+        <v>3.877604750000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.141882503224907</v>
+        <v>0.1433546559811619</v>
       </c>
       <c r="T46">
-        <v>1.486365766991537</v>
+        <v>1.50913950193012</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.572602772596682</v>
+        <v>2.515433822094533</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5215,22 +5215,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1031113107896391</v>
+        <v>0.1043869197733302</v>
       </c>
       <c r="C47">
-        <v>15.07971401372051</v>
+        <v>14.39432030387843</v>
       </c>
       <c r="D47">
-        <v>26.11971401372051</v>
+        <v>25.70832030387843</v>
       </c>
       <c r="E47">
-        <v>-2.67</v>
+        <v>-2.396000000000001</v>
       </c>
       <c r="F47">
-        <v>12.33</v>
+        <v>12.604</v>
       </c>
       <c r="G47">
         <v>1.29</v>
@@ -5251,45 +5251,45 @@
         <v>2.23</v>
       </c>
       <c r="M47">
-        <v>0.8865270000000001</v>
+        <v>0.9553832</v>
       </c>
       <c r="N47">
-        <v>1.343473</v>
+        <v>1.2746168</v>
       </c>
       <c r="O47">
-        <v>0.3358682500000001</v>
+        <v>0.3186542000000001</v>
       </c>
       <c r="P47">
-        <v>1.00760475</v>
+        <v>0.9559626000000003</v>
       </c>
       <c r="Q47">
-        <v>3.877604750000001</v>
+        <v>3.8259626</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1433546559811619</v>
+        <v>0.1448813329135745</v>
       </c>
       <c r="T47">
-        <v>1.50913950193012</v>
+        <v>1.532756708533095</v>
       </c>
       <c r="U47">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.515433822094533</v>
+        <v>2.334141944300465</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5297,22 +5297,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1043869197733302</v>
+        <v>0.1043462787570214</v>
       </c>
       <c r="C48">
-        <v>14.39432030387843</v>
+        <v>14.13322738111468</v>
       </c>
       <c r="D48">
-        <v>25.70832030387843</v>
+        <v>25.72122738111468</v>
       </c>
       <c r="E48">
-        <v>-2.396000000000001</v>
+        <v>-2.122</v>
       </c>
       <c r="F48">
-        <v>12.604</v>
+        <v>12.878</v>
       </c>
       <c r="G48">
         <v>1.29</v>
@@ -5333,28 +5333,28 @@
         <v>2.23</v>
       </c>
       <c r="M48">
-        <v>0.9553832</v>
+        <v>0.9761524000000001</v>
       </c>
       <c r="N48">
-        <v>1.2746168</v>
+        <v>1.2538476</v>
       </c>
       <c r="O48">
-        <v>0.3186542000000001</v>
+        <v>0.3134619000000001</v>
       </c>
       <c r="P48">
-        <v>0.9559626000000003</v>
+        <v>0.9403857000000002</v>
       </c>
       <c r="Q48">
-        <v>3.8259626</v>
+        <v>3.8103857</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1448813329135745</v>
+        <v>0.1464656202962668</v>
       </c>
       <c r="T48">
-        <v>1.532756708533095</v>
+        <v>1.557265130479579</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.334141944300465</v>
+        <v>2.284479349740881</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5379,22 +5379,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1043462787570214</v>
+        <v>0.1043056377407125</v>
       </c>
       <c r="C49">
-        <v>14.13322738111468</v>
+        <v>13.87214742507315</v>
       </c>
       <c r="D49">
-        <v>25.72122738111468</v>
+        <v>25.73414742507315</v>
       </c>
       <c r="E49">
-        <v>-2.122</v>
+        <v>-1.847999999999999</v>
       </c>
       <c r="F49">
-        <v>12.878</v>
+        <v>13.152</v>
       </c>
       <c r="G49">
         <v>1.29</v>
@@ -5415,28 +5415,28 @@
         <v>2.23</v>
       </c>
       <c r="M49">
-        <v>0.9761524000000001</v>
+        <v>0.9969216000000002</v>
       </c>
       <c r="N49">
-        <v>1.2538476</v>
+        <v>1.2330784</v>
       </c>
       <c r="O49">
-        <v>0.3134619000000001</v>
+        <v>0.3082696</v>
       </c>
       <c r="P49">
-        <v>0.9403857000000002</v>
+        <v>0.9248088000000001</v>
       </c>
       <c r="Q49">
-        <v>3.8103857</v>
+        <v>3.7948088</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1464656202962668</v>
+        <v>0.1481108418090626</v>
       </c>
       <c r="T49">
-        <v>1.557265130479579</v>
+        <v>1.582716184039389</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.284479349740881</v>
+        <v>2.236886029954612</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1043056377407125</v>
+        <v>0.1042649967244037</v>
       </c>
       <c r="C50">
-        <v>13.87214742507315</v>
+        <v>13.61108045530362</v>
       </c>
       <c r="D50">
-        <v>25.73414742507315</v>
+        <v>25.74708045530362</v>
       </c>
       <c r="E50">
-        <v>-1.848000000000001</v>
+        <v>-1.574000000000002</v>
       </c>
       <c r="F50">
-        <v>13.152</v>
+        <v>13.426</v>
       </c>
       <c r="G50">
         <v>1.29</v>
@@ -5497,28 +5497,28 @@
         <v>2.23</v>
       </c>
       <c r="M50">
-        <v>0.9969216000000001</v>
+        <v>1.0176908</v>
       </c>
       <c r="N50">
-        <v>1.2330784</v>
+        <v>1.2123092</v>
       </c>
       <c r="O50">
-        <v>0.3082696000000001</v>
+        <v>0.3030773000000001</v>
       </c>
       <c r="P50">
-        <v>0.9248088000000003</v>
+        <v>0.9092319000000003</v>
       </c>
       <c r="Q50">
-        <v>3.7948088</v>
+        <v>3.779231900000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1481108418090626</v>
+        <v>0.1498205818125563</v>
       </c>
       <c r="T50">
-        <v>1.582716184039389</v>
+        <v>1.609165318130956</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.236886029954612</v>
+        <v>2.191235294649417</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5543,22 +5543,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1042649967244037</v>
+        <v>0.1042243557080949</v>
       </c>
       <c r="C51">
-        <v>13.61108045530362</v>
+        <v>13.35002649139519</v>
       </c>
       <c r="D51">
-        <v>25.74708045530362</v>
+        <v>25.76002649139519</v>
       </c>
       <c r="E51">
-        <v>-1.574000000000002</v>
+        <v>-1.300000000000001</v>
       </c>
       <c r="F51">
-        <v>13.426</v>
+        <v>13.7</v>
       </c>
       <c r="G51">
         <v>1.29</v>
@@ -5579,28 +5579,28 @@
         <v>2.23</v>
       </c>
       <c r="M51">
-        <v>1.0176908</v>
+        <v>1.03846</v>
       </c>
       <c r="N51">
-        <v>1.2123092</v>
+        <v>1.19154</v>
       </c>
       <c r="O51">
-        <v>0.3030773000000001</v>
+        <v>0.2978850000000001</v>
       </c>
       <c r="P51">
-        <v>0.9092319000000003</v>
+        <v>0.8936550000000003</v>
       </c>
       <c r="Q51">
-        <v>3.779231900000001</v>
+        <v>3.763655</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1498205818125563</v>
+        <v>0.1515987114161897</v>
       </c>
       <c r="T51">
-        <v>1.609165318130956</v>
+        <v>1.636672417586186</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.191235294649417</v>
+        <v>2.147410588756428</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5625,22 +5625,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1042243557080949</v>
+        <v>0.104183714691786</v>
       </c>
       <c r="C52">
-        <v>13.35002649139519</v>
+        <v>13.08898555297639</v>
       </c>
       <c r="D52">
-        <v>25.76002649139519</v>
+        <v>25.77298555297639</v>
       </c>
       <c r="E52">
-        <v>-1.300000000000001</v>
+        <v>-1.026</v>
       </c>
       <c r="F52">
-        <v>13.7</v>
+        <v>13.974</v>
       </c>
       <c r="G52">
         <v>1.29</v>
@@ -5661,28 +5661,28 @@
         <v>2.23</v>
       </c>
       <c r="M52">
-        <v>1.03846</v>
+        <v>1.0592292</v>
       </c>
       <c r="N52">
-        <v>1.19154</v>
+        <v>1.1707708</v>
       </c>
       <c r="O52">
-        <v>0.2978850000000001</v>
+        <v>0.2926927000000001</v>
       </c>
       <c r="P52">
-        <v>0.8936550000000003</v>
+        <v>0.8780781000000002</v>
       </c>
       <c r="Q52">
-        <v>3.763655</v>
+        <v>3.7480781</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1515987114161897</v>
+        <v>0.1534494177383388</v>
       </c>
       <c r="T52">
-        <v>1.636672417586186</v>
+        <v>1.665302255794691</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.147410588756428</v>
+        <v>2.105304498780812</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5707,22 +5707,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.104183714691786</v>
+        <v>0.1041430736754772</v>
       </c>
       <c r="C53">
-        <v>13.08898555297639</v>
+        <v>12.82795765971526</v>
       </c>
       <c r="D53">
-        <v>25.77298555297639</v>
+        <v>25.78595765971526</v>
       </c>
       <c r="E53">
-        <v>-1.026</v>
+        <v>-0.7520000000000007</v>
       </c>
       <c r="F53">
-        <v>13.974</v>
+        <v>14.248</v>
       </c>
       <c r="G53">
         <v>1.29</v>
@@ -5743,28 +5743,28 @@
         <v>2.23</v>
       </c>
       <c r="M53">
-        <v>1.0592292</v>
+        <v>1.0799984</v>
       </c>
       <c r="N53">
-        <v>1.1707708</v>
+        <v>1.1500016</v>
       </c>
       <c r="O53">
-        <v>0.2926927000000001</v>
+        <v>0.2875004000000001</v>
       </c>
       <c r="P53">
-        <v>0.8780781000000002</v>
+        <v>0.8625012000000003</v>
       </c>
       <c r="Q53">
-        <v>3.7480781</v>
+        <v>3.732501200000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1534494177383388</v>
+        <v>0.1553772368239108</v>
       </c>
       <c r="T53">
-        <v>1.665302255794691</v>
+        <v>1.69512500392855</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.105304498780812</v>
+        <v>2.064817873804258</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5789,22 +5789,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1041430736754772</v>
+        <v>0.1041024326591683</v>
       </c>
       <c r="C54">
-        <v>12.82795765971526</v>
+        <v>12.56694283131946</v>
       </c>
       <c r="D54">
-        <v>25.78595765971526</v>
+        <v>25.79894283131946</v>
       </c>
       <c r="E54">
-        <v>-0.7520000000000007</v>
+        <v>-0.4779999999999998</v>
       </c>
       <c r="F54">
-        <v>14.248</v>
+        <v>14.522</v>
       </c>
       <c r="G54">
         <v>1.29</v>
@@ -5825,28 +5825,28 @@
         <v>2.23</v>
       </c>
       <c r="M54">
-        <v>1.0799984</v>
+        <v>1.1007676</v>
       </c>
       <c r="N54">
-        <v>1.1500016</v>
+        <v>1.1292324</v>
       </c>
       <c r="O54">
-        <v>0.2875004000000001</v>
+        <v>0.2823081000000001</v>
       </c>
       <c r="P54">
-        <v>0.8625012000000003</v>
+        <v>0.8469243000000002</v>
       </c>
       <c r="Q54">
-        <v>3.732501200000001</v>
+        <v>3.716924300000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1553772368239108</v>
+        <v>0.1573870907641879</v>
       </c>
       <c r="T54">
-        <v>1.69512500392855</v>
+        <v>1.726216805174489</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.064817873804258</v>
+        <v>2.02585904599663</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5871,22 +5871,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1041024326591683</v>
+        <v>0.1098127916428595</v>
       </c>
       <c r="C55">
-        <v>12.56694283131946</v>
+        <v>10.58813797981499</v>
       </c>
       <c r="D55">
-        <v>25.79894283131946</v>
+        <v>24.09413797981499</v>
       </c>
       <c r="E55">
-        <v>-0.4779999999999998</v>
+        <v>-0.2040000000000006</v>
       </c>
       <c r="F55">
-        <v>14.522</v>
+        <v>14.796</v>
       </c>
       <c r="G55">
         <v>1.29</v>
@@ -5907,45 +5907,45 @@
         <v>2.23</v>
       </c>
       <c r="M55">
-        <v>1.1007676</v>
+        <v>1.33164</v>
       </c>
       <c r="N55">
-        <v>1.1292324</v>
+        <v>0.8983600000000005</v>
       </c>
       <c r="O55">
-        <v>0.2823081000000001</v>
+        <v>0.2245900000000001</v>
       </c>
       <c r="P55">
-        <v>0.8469243000000002</v>
+        <v>0.6737700000000004</v>
       </c>
       <c r="Q55">
-        <v>3.716924300000001</v>
+        <v>3.54377</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1573870907641879</v>
+        <v>0.1594843296583902</v>
       </c>
       <c r="T55">
-        <v>1.726216805174489</v>
+        <v>1.758660423865902</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.02585904599663</v>
+        <v>1.674626776005527</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5953,22 +5953,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1098127916428595</v>
+        <v>0.1098786506265507</v>
       </c>
       <c r="C56">
-        <v>10.58813797981499</v>
+        <v>10.29578929630579</v>
       </c>
       <c r="D56">
-        <v>24.09413797981499</v>
+        <v>24.07578929630579</v>
       </c>
       <c r="E56">
-        <v>-0.2040000000000006</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="F56">
-        <v>14.796</v>
+        <v>15.07</v>
       </c>
       <c r="G56">
         <v>1.29</v>
@@ -5989,28 +5989,28 @@
         <v>2.23</v>
       </c>
       <c r="M56">
-        <v>1.33164</v>
+        <v>1.3563</v>
       </c>
       <c r="N56">
-        <v>0.8983600000000005</v>
+        <v>0.8737000000000004</v>
       </c>
       <c r="O56">
-        <v>0.2245900000000001</v>
+        <v>0.2184250000000001</v>
       </c>
       <c r="P56">
-        <v>0.6737700000000004</v>
+        <v>0.6552750000000003</v>
       </c>
       <c r="Q56">
-        <v>3.54377</v>
+        <v>3.525275000000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1594843296583902</v>
+        <v>0.1616747791701126</v>
       </c>
       <c r="T56">
-        <v>1.758660423865902</v>
+        <v>1.792545981165824</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.674626776005527</v>
+        <v>1.64417901644179</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6035,22 +6035,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1098786506265507</v>
+        <v>0.1099445096102418</v>
       </c>
       <c r="C57">
-        <v>10.29578929630579</v>
+        <v>10.00346853809448</v>
       </c>
       <c r="D57">
-        <v>24.07578929630579</v>
+        <v>24.05746853809449</v>
       </c>
       <c r="E57">
-        <v>0.07000000000000028</v>
+        <v>0.3440000000000012</v>
       </c>
       <c r="F57">
-        <v>15.07</v>
+        <v>15.344</v>
       </c>
       <c r="G57">
         <v>1.29</v>
@@ -6071,28 +6071,28 @@
         <v>2.23</v>
       </c>
       <c r="M57">
-        <v>1.3563</v>
+        <v>1.38096</v>
       </c>
       <c r="N57">
-        <v>0.8737000000000004</v>
+        <v>0.8490400000000005</v>
       </c>
       <c r="O57">
-        <v>0.2184250000000001</v>
+        <v>0.2122600000000001</v>
       </c>
       <c r="P57">
-        <v>0.6552750000000003</v>
+        <v>0.6367800000000003</v>
       </c>
       <c r="Q57">
-        <v>3.525275000000001</v>
+        <v>3.50678</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1616747791701126</v>
+        <v>0.1639647945687314</v>
       </c>
       <c r="T57">
-        <v>1.792545981165824</v>
+        <v>1.827971791070286</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6109,7 +6109,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.64417901644179</v>
+        <v>1.614818676862473</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6117,22 +6117,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1099445096102418</v>
+        <v>0.110010368593933</v>
       </c>
       <c r="C58">
-        <v>10.00346853809448</v>
+        <v>9.711175641479285</v>
       </c>
       <c r="D58">
-        <v>24.05746853809449</v>
+        <v>24.03917564147929</v>
       </c>
       <c r="E58">
-        <v>0.3440000000000012</v>
+        <v>0.6180000000000003</v>
       </c>
       <c r="F58">
-        <v>15.344</v>
+        <v>15.618</v>
       </c>
       <c r="G58">
         <v>1.29</v>
@@ -6153,28 +6153,28 @@
         <v>2.23</v>
       </c>
       <c r="M58">
-        <v>1.38096</v>
+        <v>1.40562</v>
       </c>
       <c r="N58">
-        <v>0.8490400000000005</v>
+        <v>0.8243800000000006</v>
       </c>
       <c r="O58">
-        <v>0.2122600000000001</v>
+        <v>0.2060950000000001</v>
       </c>
       <c r="P58">
-        <v>0.6367800000000003</v>
+        <v>0.6182850000000004</v>
       </c>
       <c r="Q58">
-        <v>3.50678</v>
+        <v>3.488285</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1639647945687314</v>
+        <v>0.166361322311472</v>
       </c>
       <c r="T58">
-        <v>1.827971791070286</v>
+        <v>1.865045313063329</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.614818676862473</v>
+        <v>1.586488524636815</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6199,22 +6199,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.110010368593933</v>
+        <v>0.1100762275776241</v>
       </c>
       <c r="C59">
-        <v>9.711175641479285</v>
+        <v>9.418910542952011</v>
       </c>
       <c r="D59">
-        <v>24.03917564147929</v>
+        <v>24.02091054295201</v>
       </c>
       <c r="E59">
-        <v>0.6180000000000003</v>
+        <v>0.8920000000000012</v>
       </c>
       <c r="F59">
-        <v>15.618</v>
+        <v>15.892</v>
       </c>
       <c r="G59">
         <v>1.29</v>
@@ -6235,28 +6235,28 @@
         <v>2.23</v>
       </c>
       <c r="M59">
-        <v>1.40562</v>
+        <v>1.43028</v>
       </c>
       <c r="N59">
-        <v>0.8243800000000006</v>
+        <v>0.7997200000000004</v>
       </c>
       <c r="O59">
-        <v>0.2060950000000001</v>
+        <v>0.1999300000000001</v>
       </c>
       <c r="P59">
-        <v>0.6182850000000004</v>
+        <v>0.5997900000000003</v>
       </c>
       <c r="Q59">
-        <v>3.488285</v>
+        <v>3.469790000000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.166361322311472</v>
+        <v>0.1688719704229146</v>
       </c>
       <c r="T59">
-        <v>1.865045313063329</v>
+        <v>1.903884240865564</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.586488524636815</v>
+        <v>1.559135274212043</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6281,22 +6281,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1100762275776241</v>
+        <v>0.1101420865613153</v>
       </c>
       <c r="C60">
-        <v>9.418910542952014</v>
+        <v>9.126673179197343</v>
       </c>
       <c r="D60">
-        <v>24.02091054295201</v>
+        <v>24.00267317919734</v>
       </c>
       <c r="E60">
-        <v>0.8919999999999977</v>
+        <v>1.165999999999997</v>
       </c>
       <c r="F60">
-        <v>15.892</v>
+        <v>16.166</v>
       </c>
       <c r="G60">
         <v>1.29</v>
@@ -6317,28 +6317,28 @@
         <v>2.23</v>
       </c>
       <c r="M60">
-        <v>1.43028</v>
+        <v>1.45494</v>
       </c>
       <c r="N60">
-        <v>0.7997200000000007</v>
+        <v>0.7750600000000007</v>
       </c>
       <c r="O60">
-        <v>0.1999300000000002</v>
+        <v>0.1937650000000002</v>
       </c>
       <c r="P60">
-        <v>0.5997900000000005</v>
+        <v>0.5812950000000006</v>
       </c>
       <c r="Q60">
-        <v>3.469790000000001</v>
+        <v>3.451295000000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1688719704229145</v>
+        <v>0.1715050891739397</v>
       </c>
       <c r="T60">
-        <v>1.903884240865564</v>
+        <v>1.94461775051181</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.559135274212043</v>
+        <v>1.532709252615229</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6363,22 +6363,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1101420865613153</v>
+        <v>0.1102079455450064</v>
       </c>
       <c r="C61">
-        <v>9.126673179197343</v>
+        <v>8.834463487092101</v>
       </c>
       <c r="D61">
-        <v>24.00267317919734</v>
+        <v>23.9844634870921</v>
       </c>
       <c r="E61">
-        <v>1.165999999999997</v>
+        <v>1.439999999999998</v>
       </c>
       <c r="F61">
-        <v>16.166</v>
+        <v>16.44</v>
       </c>
       <c r="G61">
         <v>1.29</v>
@@ -6399,28 +6399,28 @@
         <v>2.23</v>
       </c>
       <c r="M61">
-        <v>1.45494</v>
+        <v>1.4796</v>
       </c>
       <c r="N61">
-        <v>0.7750600000000007</v>
+        <v>0.7504000000000006</v>
       </c>
       <c r="O61">
-        <v>0.1937650000000002</v>
+        <v>0.1876000000000002</v>
       </c>
       <c r="P61">
-        <v>0.5812950000000006</v>
+        <v>0.5628000000000004</v>
       </c>
       <c r="Q61">
-        <v>3.451295000000001</v>
+        <v>3.4328</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1715050891739397</v>
+        <v>0.1742698638625161</v>
       </c>
       <c r="T61">
-        <v>1.94461775051181</v>
+        <v>1.987387935640369</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.532709252615229</v>
+        <v>1.507164098404975</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6445,22 +6445,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1102079455450064</v>
+        <v>0.1391403363359657</v>
       </c>
       <c r="C62">
-        <v>8.834463487092101</v>
+        <v>2.565035740923516</v>
       </c>
       <c r="D62">
-        <v>23.9844634870921</v>
+        <v>17.98903574092352</v>
       </c>
       <c r="E62">
-        <v>1.439999999999998</v>
+        <v>1.713999999999999</v>
       </c>
       <c r="F62">
-        <v>16.44</v>
+        <v>16.714</v>
       </c>
       <c r="G62">
         <v>1.29</v>
@@ -6481,45 +6481,45 @@
         <v>2.23</v>
       </c>
       <c r="M62">
-        <v>1.4796</v>
+        <v>2.4536152</v>
       </c>
       <c r="N62">
-        <v>0.7504000000000006</v>
+        <v>-0.2236151999999998</v>
       </c>
       <c r="O62">
-        <v>0.1876000000000002</v>
+        <v>-0.05590379999999995</v>
       </c>
       <c r="P62">
-        <v>0.5628000000000004</v>
+        <v>-0.1677113999999998</v>
       </c>
       <c r="Q62">
-        <v>3.4328</v>
+        <v>2.7022886</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1742698638625161</v>
+        <v>0.1793309017036739</v>
       </c>
       <c r="T62">
-        <v>1.987387935640369</v>
+        <v>2.065680581440168</v>
       </c>
       <c r="U62">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.25</v>
+        <v>0.2272157427130383</v>
       </c>
       <c r="W62">
-        <v>0.0675</v>
+        <v>0.113444728969726</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.507164098404975</v>
+        <v>0.9088629708521533</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1391403363359657</v>
+        <v>0.1401503363359657</v>
       </c>
       <c r="C63">
-        <v>2.565035740923516</v>
+        <v>2.13541704111579</v>
       </c>
       <c r="D63">
-        <v>17.98903574092352</v>
+        <v>17.83341704111579</v>
       </c>
       <c r="E63">
-        <v>1.713999999999999</v>
+        <v>1.988</v>
       </c>
       <c r="F63">
-        <v>16.714</v>
+        <v>16.988</v>
       </c>
       <c r="G63">
         <v>1.29</v>
@@ -6563,37 +6563,37 @@
         <v>2.23</v>
       </c>
       <c r="M63">
-        <v>2.4536152</v>
+        <v>2.4938384</v>
       </c>
       <c r="N63">
-        <v>-0.2236151999999998</v>
+        <v>-0.2638383999999996</v>
       </c>
       <c r="O63">
-        <v>-0.05590379999999995</v>
+        <v>-0.0659595999999999</v>
       </c>
       <c r="P63">
-        <v>-0.1677113999999998</v>
+        <v>-0.1978787999999997</v>
       </c>
       <c r="Q63">
-        <v>2.7022886</v>
+        <v>2.6721212</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1793309017036739</v>
+        <v>0.182844872801139</v>
       </c>
       <c r="T63">
-        <v>2.065680581440168</v>
+        <v>2.120040596741226</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2272157427130383</v>
+        <v>0.2235509726692796</v>
       </c>
       <c r="W63">
-        <v>0.113444728969726</v>
+        <v>0.1139827172121498</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9088629708521533</v>
+        <v>0.8942038906771186</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6609,22 +6609,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1401503363359657</v>
+        <v>0.1411603363359657</v>
       </c>
       <c r="C64">
-        <v>2.13541704111579</v>
+        <v>1.708467687236794</v>
       </c>
       <c r="D64">
-        <v>17.83341704111579</v>
+        <v>17.6804676872368</v>
       </c>
       <c r="E64">
-        <v>1.988</v>
+        <v>2.262</v>
       </c>
       <c r="F64">
-        <v>16.988</v>
+        <v>17.262</v>
       </c>
       <c r="G64">
         <v>1.29</v>
@@ -6645,37 +6645,37 @@
         <v>2.23</v>
       </c>
       <c r="M64">
-        <v>2.4938384</v>
+        <v>2.5340616</v>
       </c>
       <c r="N64">
-        <v>-0.2638383999999996</v>
+        <v>-0.3040615999999998</v>
       </c>
       <c r="O64">
-        <v>-0.0659595999999999</v>
+        <v>-0.07601539999999996</v>
       </c>
       <c r="P64">
-        <v>-0.1978787999999997</v>
+        <v>-0.2280461999999999</v>
       </c>
       <c r="Q64">
-        <v>2.6721212</v>
+        <v>2.6419538</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.182844872801139</v>
+        <v>0.1865487882822509</v>
       </c>
       <c r="T64">
-        <v>2.120040596741226</v>
+        <v>2.177338991247745</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2235509726692796</v>
+        <v>0.220002544531672</v>
       </c>
       <c r="W64">
-        <v>0.1139827172121498</v>
+        <v>0.1145036264627506</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8942038906771186</v>
+        <v>0.880010178126688</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6691,22 +6691,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1411603363359657</v>
+        <v>0.1421703363359657</v>
       </c>
       <c r="C65">
-        <v>1.708467687236794</v>
+        <v>1.284119581918887</v>
       </c>
       <c r="D65">
-        <v>17.6804676872368</v>
+        <v>17.53011958191889</v>
       </c>
       <c r="E65">
-        <v>2.262</v>
+        <v>2.535999999999998</v>
       </c>
       <c r="F65">
-        <v>17.262</v>
+        <v>17.536</v>
       </c>
       <c r="G65">
         <v>1.29</v>
@@ -6727,37 +6727,37 @@
         <v>2.23</v>
       </c>
       <c r="M65">
-        <v>2.5340616</v>
+        <v>2.5742848</v>
       </c>
       <c r="N65">
-        <v>-0.3040615999999998</v>
+        <v>-0.3442847999999996</v>
       </c>
       <c r="O65">
-        <v>-0.07601539999999996</v>
+        <v>-0.0860711999999999</v>
       </c>
       <c r="P65">
-        <v>-0.2280461999999999</v>
+        <v>-0.2582135999999997</v>
       </c>
       <c r="Q65">
-        <v>2.6419538</v>
+        <v>2.611786400000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1865487882822509</v>
+        <v>0.1904584768456467</v>
       </c>
       <c r="T65">
-        <v>2.177338991247745</v>
+        <v>2.237820629893516</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.220002544531672</v>
+        <v>0.2165650047733647</v>
       </c>
       <c r="W65">
-        <v>0.1145036264627506</v>
+        <v>0.1150082572992701</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.880010178126688</v>
+        <v>0.8662600190934586</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6773,22 +6773,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1421703363359657</v>
+        <v>0.1431803363359657</v>
       </c>
       <c r="C66">
-        <v>1.284119581918887</v>
+        <v>0.8623069245620343</v>
       </c>
       <c r="D66">
-        <v>17.53011958191889</v>
+        <v>17.38230692456203</v>
       </c>
       <c r="E66">
-        <v>2.535999999999998</v>
+        <v>2.809999999999999</v>
       </c>
       <c r="F66">
-        <v>17.536</v>
+        <v>17.81</v>
       </c>
       <c r="G66">
         <v>1.29</v>
@@ -6809,37 +6809,37 @@
         <v>2.23</v>
       </c>
       <c r="M66">
-        <v>2.5742848</v>
+        <v>2.614508</v>
       </c>
       <c r="N66">
-        <v>-0.3442847999999996</v>
+        <v>-0.3845079999999998</v>
       </c>
       <c r="O66">
-        <v>-0.0860711999999999</v>
+        <v>-0.09612699999999996</v>
       </c>
       <c r="P66">
-        <v>-0.2582135999999997</v>
+        <v>-0.2883809999999999</v>
       </c>
       <c r="Q66">
-        <v>2.611786400000001</v>
+        <v>2.581619</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1904584768456467</v>
+        <v>0.1945915761840938</v>
       </c>
       <c r="T66">
-        <v>2.237820629893516</v>
+        <v>2.301758362176188</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2165650047733647</v>
+        <v>0.213233235469159</v>
       </c>
       <c r="W66">
-        <v>0.1150082572992701</v>
+        <v>0.1154973610331275</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8662600190934586</v>
+        <v>0.8529329418766362</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6855,22 +6855,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1431803363359657</v>
+        <v>0.1441903363359657</v>
       </c>
       <c r="C67">
-        <v>0.8623069245620343</v>
+        <v>0.4429661153126645</v>
       </c>
       <c r="D67">
-        <v>17.38230692456203</v>
+        <v>17.23696611531266</v>
       </c>
       <c r="E67">
-        <v>2.809999999999999</v>
+        <v>3.084</v>
       </c>
       <c r="F67">
-        <v>17.81</v>
+        <v>18.084</v>
       </c>
       <c r="G67">
         <v>1.29</v>
@@ -6891,37 +6891,37 @@
         <v>2.23</v>
       </c>
       <c r="M67">
-        <v>2.614508</v>
+        <v>2.6547312</v>
       </c>
       <c r="N67">
-        <v>-0.3845079999999998</v>
+        <v>-0.4247311999999996</v>
       </c>
       <c r="O67">
-        <v>-0.09612699999999996</v>
+        <v>-0.1061827999999999</v>
       </c>
       <c r="P67">
-        <v>-0.2883809999999999</v>
+        <v>-0.3185483999999997</v>
       </c>
       <c r="Q67">
-        <v>2.581619</v>
+        <v>2.5514516</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1945915761840938</v>
+        <v>0.1989677990130377</v>
       </c>
       <c r="T67">
-        <v>2.301758362176188</v>
+        <v>2.369457137534311</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.213233235469159</v>
+        <v>0.2100024288711415</v>
       </c>
       <c r="W67">
-        <v>0.1154973610331275</v>
+        <v>0.1159716434417164</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8529329418766362</v>
+        <v>0.8400097154845659</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6937,22 +6937,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1441903363359657</v>
+        <v>0.1452003363359657</v>
       </c>
       <c r="C68">
-        <v>0.4429661153126645</v>
+        <v>0.02603566381969102</v>
       </c>
       <c r="D68">
-        <v>17.23696611531266</v>
+        <v>17.09403566381969</v>
       </c>
       <c r="E68">
-        <v>3.084</v>
+        <v>3.358000000000001</v>
       </c>
       <c r="F68">
-        <v>18.084</v>
+        <v>18.358</v>
       </c>
       <c r="G68">
         <v>1.29</v>
@@ -6973,37 +6973,37 @@
         <v>2.23</v>
       </c>
       <c r="M68">
-        <v>2.6547312</v>
+        <v>2.6949544</v>
       </c>
       <c r="N68">
-        <v>-0.4247311999999996</v>
+        <v>-0.4649543999999999</v>
       </c>
       <c r="O68">
-        <v>-0.1061827999999999</v>
+        <v>-0.1162386</v>
       </c>
       <c r="P68">
-        <v>-0.3185483999999997</v>
+        <v>-0.3487157999999999</v>
       </c>
       <c r="Q68">
-        <v>2.5514516</v>
+        <v>2.5212842</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1989677990130377</v>
+        <v>0.2036092474679782</v>
       </c>
       <c r="T68">
-        <v>2.369457137534311</v>
+        <v>2.441258868974745</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2100024288711415</v>
+        <v>0.2068680642611244</v>
       </c>
       <c r="W68">
-        <v>0.1159716434417164</v>
+        <v>0.1164317681664669</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8400097154845659</v>
+        <v>0.8274722570444977</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7019,22 +7019,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1452003363359657</v>
+        <v>0.1462103363359657</v>
       </c>
       <c r="C69">
-        <v>0.02603566381969102</v>
+        <v>-0.388543897507116</v>
       </c>
       <c r="D69">
-        <v>17.09403566381969</v>
+        <v>16.95345610249289</v>
       </c>
       <c r="E69">
-        <v>3.358000000000001</v>
+        <v>3.632000000000001</v>
       </c>
       <c r="F69">
-        <v>18.358</v>
+        <v>18.632</v>
       </c>
       <c r="G69">
         <v>1.29</v>
@@ -7055,37 +7055,37 @@
         <v>2.23</v>
       </c>
       <c r="M69">
-        <v>2.6949544</v>
+        <v>2.735177600000001</v>
       </c>
       <c r="N69">
-        <v>-0.4649543999999999</v>
+        <v>-0.5051776000000001</v>
       </c>
       <c r="O69">
-        <v>-0.1162386</v>
+        <v>-0.1262944</v>
       </c>
       <c r="P69">
-        <v>-0.3487157999999999</v>
+        <v>-0.3788832000000001</v>
       </c>
       <c r="Q69">
-        <v>2.5212842</v>
+        <v>2.4911168</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2036092474679782</v>
+        <v>0.2085407864513525</v>
       </c>
       <c r="T69">
-        <v>2.441258868974745</v>
+        <v>2.517548208630206</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2068680642611244</v>
+        <v>0.2038258868455196</v>
       </c>
       <c r="W69">
-        <v>0.1164317681664669</v>
+        <v>0.1168783598110777</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8274722570444977</v>
+        <v>0.8153035473820786</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7101,22 +7101,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1462103363359657</v>
+        <v>0.1472203363359657</v>
       </c>
       <c r="C70">
-        <v>-0.388543897507116</v>
+        <v>-0.8008300959935397</v>
       </c>
       <c r="D70">
-        <v>16.95345610249289</v>
+        <v>16.81516990400646</v>
       </c>
       <c r="E70">
-        <v>3.632000000000001</v>
+        <v>3.906000000000002</v>
       </c>
       <c r="F70">
-        <v>18.632</v>
+        <v>18.906</v>
       </c>
       <c r="G70">
         <v>1.29</v>
@@ -7137,37 +7137,37 @@
         <v>2.23</v>
       </c>
       <c r="M70">
-        <v>2.735177600000001</v>
+        <v>2.775400800000001</v>
       </c>
       <c r="N70">
-        <v>-0.5051776000000001</v>
+        <v>-0.5454008000000004</v>
       </c>
       <c r="O70">
-        <v>-0.1262944</v>
+        <v>-0.1363502000000001</v>
       </c>
       <c r="P70">
-        <v>-0.3788832000000001</v>
+        <v>-0.4090506000000003</v>
       </c>
       <c r="Q70">
-        <v>2.4911168</v>
+        <v>2.4609494</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2085407864513525</v>
+        <v>0.2137904892401059</v>
       </c>
       <c r="T70">
-        <v>2.517548208630206</v>
+        <v>2.598759441166664</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2038258868455196</v>
+        <v>0.2008718884854396</v>
       </c>
       <c r="W70">
-        <v>0.1168783598110777</v>
+        <v>0.1173120067703375</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8153035473820786</v>
+        <v>0.8034875539417585</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7183,22 +7183,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1472203363359657</v>
+        <v>0.1882837484992706</v>
       </c>
       <c r="C71">
-        <v>-0.8008300959935397</v>
+        <v>-5.262494125259433</v>
       </c>
       <c r="D71">
-        <v>16.81516990400646</v>
+        <v>12.62750587474057</v>
       </c>
       <c r="E71">
-        <v>3.906000000000002</v>
+        <v>4.18</v>
       </c>
       <c r="F71">
-        <v>18.906</v>
+        <v>19.18</v>
       </c>
       <c r="G71">
         <v>1.29</v>
@@ -7219,45 +7219,45 @@
         <v>2.23</v>
       </c>
       <c r="M71">
-        <v>2.775400800000001</v>
+        <v>3.851344</v>
       </c>
       <c r="N71">
-        <v>-0.5454008000000004</v>
+        <v>-1.621344</v>
       </c>
       <c r="O71">
-        <v>-0.1363502000000001</v>
+        <v>-0.4053359999999999</v>
       </c>
       <c r="P71">
-        <v>-0.4090506000000003</v>
+        <v>-1.216008</v>
       </c>
       <c r="Q71">
-        <v>2.4609494</v>
+        <v>1.653992</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2137904892401059</v>
+        <v>0.2269015460924591</v>
       </c>
       <c r="T71">
-        <v>2.598759441166664</v>
+        <v>2.801583320856821</v>
       </c>
       <c r="U71">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.2008718884854396</v>
+        <v>0.1447546622685484</v>
       </c>
       <c r="W71">
-        <v>0.1173120067703375</v>
+        <v>0.1717332638164755</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8034875539417585</v>
+        <v>0.5790186490741934</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7265,22 +7265,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1882837484992706</v>
+        <v>0.1898337484992706</v>
       </c>
       <c r="C72">
-        <v>-5.262494125259433</v>
+        <v>-5.654092503870508</v>
       </c>
       <c r="D72">
-        <v>12.62750587474057</v>
+        <v>12.50990749612949</v>
       </c>
       <c r="E72">
-        <v>4.18</v>
+        <v>4.454000000000001</v>
       </c>
       <c r="F72">
-        <v>19.18</v>
+        <v>19.454</v>
       </c>
       <c r="G72">
         <v>1.29</v>
@@ -7301,37 +7301,37 @@
         <v>2.23</v>
       </c>
       <c r="M72">
-        <v>3.851344</v>
+        <v>3.9063632</v>
       </c>
       <c r="N72">
-        <v>-1.621344</v>
+        <v>-1.6763632</v>
       </c>
       <c r="O72">
-        <v>-0.4053359999999999</v>
+        <v>-0.4190908</v>
       </c>
       <c r="P72">
-        <v>-1.216008</v>
+        <v>-1.2572724</v>
       </c>
       <c r="Q72">
-        <v>1.653992</v>
+        <v>1.6127276</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2269015460924591</v>
+        <v>0.2331464269921991</v>
       </c>
       <c r="T72">
-        <v>2.801583320856821</v>
+        <v>2.898189642265677</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1447546622685484</v>
+        <v>0.1427158642084279</v>
       </c>
       <c r="W72">
-        <v>0.1717332638164755</v>
+        <v>0.1721426544669477</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5790186490741934</v>
+        <v>0.5708634568337118</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7347,22 +7347,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1898337484992706</v>
+        <v>0.1913837484992706</v>
       </c>
       <c r="C73">
-        <v>-5.654092503870501</v>
+        <v>-6.043520734889682</v>
       </c>
       <c r="D73">
-        <v>12.50990749612949</v>
+        <v>12.39447926511032</v>
       </c>
       <c r="E73">
-        <v>4.453999999999997</v>
+        <v>4.727999999999998</v>
       </c>
       <c r="F73">
-        <v>19.454</v>
+        <v>19.728</v>
       </c>
       <c r="G73">
         <v>1.29</v>
@@ -7383,37 +7383,37 @@
         <v>2.23</v>
       </c>
       <c r="M73">
-        <v>3.906363199999999</v>
+        <v>3.9613824</v>
       </c>
       <c r="N73">
-        <v>-1.676363199999999</v>
+        <v>-1.731382399999999</v>
       </c>
       <c r="O73">
-        <v>-0.4190907999999998</v>
+        <v>-0.4328455999999998</v>
       </c>
       <c r="P73">
-        <v>-1.257272399999999</v>
+        <v>-1.298536799999999</v>
       </c>
       <c r="Q73">
-        <v>1.612727600000001</v>
+        <v>1.571463200000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.233146426992199</v>
+        <v>0.239837370813349</v>
       </c>
       <c r="T73">
-        <v>2.898189642265676</v>
+        <v>3.001696415203736</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.142715864208428</v>
+        <v>0.1407336994277553</v>
       </c>
       <c r="W73">
-        <v>0.1721426544669477</v>
+        <v>0.1725406731549067</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5708634568337119</v>
+        <v>0.5629347977110215</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7429,22 +7429,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1913837484992706</v>
+        <v>0.1929337484992706</v>
       </c>
       <c r="C74">
-        <v>-6.043520734889682</v>
+        <v>-6.430838340606826</v>
       </c>
       <c r="D74">
-        <v>12.39447926511032</v>
+        <v>12.28116165939317</v>
       </c>
       <c r="E74">
-        <v>4.727999999999998</v>
+        <v>5.001999999999999</v>
       </c>
       <c r="F74">
-        <v>19.728</v>
+        <v>20.002</v>
       </c>
       <c r="G74">
         <v>1.29</v>
@@ -7465,37 +7465,37 @@
         <v>2.23</v>
       </c>
       <c r="M74">
-        <v>3.9613824</v>
+        <v>4.0164016</v>
       </c>
       <c r="N74">
-        <v>-1.731382399999999</v>
+        <v>-1.7864016</v>
       </c>
       <c r="O74">
-        <v>-0.4328455999999998</v>
+        <v>-0.4466003999999999</v>
       </c>
       <c r="P74">
-        <v>-1.298536799999999</v>
+        <v>-1.3398012</v>
       </c>
       <c r="Q74">
-        <v>1.571463200000001</v>
+        <v>1.5301988</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.239837370813349</v>
+        <v>0.2470239401027323</v>
       </c>
       <c r="T74">
-        <v>3.001696415203736</v>
+        <v>3.112870356507578</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1407336994277553</v>
+        <v>0.1388058405314847</v>
       </c>
       <c r="W74">
-        <v>0.1725406731549067</v>
+        <v>0.1729277872212779</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5629347977110215</v>
+        <v>0.5552233621259389</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7511,22 +7511,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1929337484992706</v>
+        <v>0.1944837484992706</v>
       </c>
       <c r="C75">
-        <v>-6.430838340606826</v>
+        <v>-6.816102686281756</v>
       </c>
       <c r="D75">
-        <v>12.28116165939317</v>
+        <v>12.16989731371824</v>
       </c>
       <c r="E75">
-        <v>5.001999999999999</v>
+        <v>5.276</v>
       </c>
       <c r="F75">
-        <v>20.002</v>
+        <v>20.276</v>
       </c>
       <c r="G75">
         <v>1.29</v>
@@ -7547,37 +7547,37 @@
         <v>2.23</v>
       </c>
       <c r="M75">
-        <v>4.0164016</v>
+        <v>4.0714208</v>
       </c>
       <c r="N75">
-        <v>-1.7864016</v>
+        <v>-1.8414208</v>
       </c>
       <c r="O75">
-        <v>-0.4466003999999999</v>
+        <v>-0.4603552</v>
       </c>
       <c r="P75">
-        <v>-1.3398012</v>
+        <v>-1.3810656</v>
       </c>
       <c r="Q75">
-        <v>1.5301988</v>
+        <v>1.4889344</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2470239401027323</v>
+        <v>0.2547633224143758</v>
       </c>
       <c r="T75">
-        <v>3.112870356507578</v>
+        <v>3.232596139450177</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1388058405314847</v>
+        <v>0.1369300859297079</v>
       </c>
       <c r="W75">
-        <v>0.1729277872212779</v>
+        <v>0.1733044387453146</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5552233621259389</v>
+        <v>0.5477203437188316</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7593,22 +7593,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1944837484992706</v>
+        <v>0.1960337484992706</v>
       </c>
       <c r="C76">
-        <v>-6.816102686281756</v>
+        <v>-7.199369076977828</v>
       </c>
       <c r="D76">
-        <v>12.16989731371824</v>
+        <v>12.06063092302217</v>
       </c>
       <c r="E76">
-        <v>5.276</v>
+        <v>5.549999999999997</v>
       </c>
       <c r="F76">
-        <v>20.276</v>
+        <v>20.55</v>
       </c>
       <c r="G76">
         <v>1.29</v>
@@ -7629,37 +7629,37 @@
         <v>2.23</v>
       </c>
       <c r="M76">
-        <v>4.0714208</v>
+        <v>4.12644</v>
       </c>
       <c r="N76">
-        <v>-1.8414208</v>
+        <v>-1.896439999999999</v>
       </c>
       <c r="O76">
-        <v>-0.4603552</v>
+        <v>-0.4741099999999998</v>
       </c>
       <c r="P76">
-        <v>-1.3810656</v>
+        <v>-1.422329999999999</v>
       </c>
       <c r="Q76">
-        <v>1.4889344</v>
+        <v>1.447670000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2547633224143758</v>
+        <v>0.2631218553109508</v>
       </c>
       <c r="T76">
-        <v>3.232596139450177</v>
+        <v>3.361899985028184</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1369300859297079</v>
+        <v>0.1351043514506451</v>
       </c>
       <c r="W76">
-        <v>0.1733044387453146</v>
+        <v>0.1736710462287105</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5477203437188316</v>
+        <v>0.5404174058025806</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7675,22 +7675,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1960337484992706</v>
+        <v>0.1975837484992706</v>
       </c>
       <c r="C77">
-        <v>-7.199369076977828</v>
+        <v>-7.580690849225423</v>
       </c>
       <c r="D77">
-        <v>12.06063092302217</v>
+        <v>11.95330915077458</v>
       </c>
       <c r="E77">
-        <v>5.549999999999997</v>
+        <v>5.823999999999998</v>
       </c>
       <c r="F77">
-        <v>20.55</v>
+        <v>20.824</v>
       </c>
       <c r="G77">
         <v>1.29</v>
@@ -7711,37 +7711,37 @@
         <v>2.23</v>
       </c>
       <c r="M77">
-        <v>4.12644</v>
+        <v>4.1814592</v>
       </c>
       <c r="N77">
-        <v>-1.896439999999999</v>
+        <v>-1.9514592</v>
       </c>
       <c r="O77">
-        <v>-0.4741099999999998</v>
+        <v>-0.4878647999999999</v>
       </c>
       <c r="P77">
-        <v>-1.422329999999999</v>
+        <v>-1.4635944</v>
       </c>
       <c r="Q77">
-        <v>1.447670000000001</v>
+        <v>1.4064056</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2631218553109508</v>
+        <v>0.2721769326155739</v>
       </c>
       <c r="T77">
-        <v>3.361899985028184</v>
+        <v>3.501979151071026</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1351043514506451</v>
+        <v>0.1333266626157682</v>
       </c>
       <c r="W77">
-        <v>0.1736710462287105</v>
+        <v>0.1740280061467538</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5404174058025806</v>
+        <v>0.5333066504630729</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7757,22 +7757,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1975837484992706</v>
+        <v>0.1991337484992706</v>
       </c>
       <c r="C78">
-        <v>-7.580690849225423</v>
+        <v>-7.960119457834598</v>
       </c>
       <c r="D78">
-        <v>11.95330915077458</v>
+        <v>11.8478805421654</v>
       </c>
       <c r="E78">
-        <v>5.823999999999998</v>
+        <v>6.097999999999999</v>
       </c>
       <c r="F78">
-        <v>20.824</v>
+        <v>21.098</v>
       </c>
       <c r="G78">
         <v>1.29</v>
@@ -7793,37 +7793,37 @@
         <v>2.23</v>
       </c>
       <c r="M78">
-        <v>4.1814592</v>
+        <v>4.2364784</v>
       </c>
       <c r="N78">
-        <v>-1.9514592</v>
+        <v>-2.0064784</v>
       </c>
       <c r="O78">
-        <v>-0.4878647999999999</v>
+        <v>-0.5016195999999999</v>
       </c>
       <c r="P78">
-        <v>-1.4635944</v>
+        <v>-1.5048588</v>
       </c>
       <c r="Q78">
-        <v>1.4064056</v>
+        <v>1.3651412</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2721769326155739</v>
+        <v>0.2820194079466857</v>
       </c>
       <c r="T78">
-        <v>3.501979151071026</v>
+        <v>3.65423911416107</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1333266626157682</v>
+        <v>0.1315951475168621</v>
       </c>
       <c r="W78">
-        <v>0.1740280061467538</v>
+        <v>0.1743756943786141</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5333066504630729</v>
+        <v>0.5263805900674485</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7839,22 +7839,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1991337484992706</v>
+        <v>0.2006837484992706</v>
       </c>
       <c r="C79">
-        <v>-7.960119457834598</v>
+        <v>-8.337704558153757</v>
       </c>
       <c r="D79">
-        <v>11.8478805421654</v>
+        <v>11.74429544184624</v>
       </c>
       <c r="E79">
-        <v>6.097999999999999</v>
+        <v>6.372</v>
       </c>
       <c r="F79">
-        <v>21.098</v>
+        <v>21.372</v>
       </c>
       <c r="G79">
         <v>1.29</v>
@@ -7875,37 +7875,37 @@
         <v>2.23</v>
       </c>
       <c r="M79">
-        <v>4.2364784</v>
+        <v>4.2914976</v>
       </c>
       <c r="N79">
-        <v>-2.0064784</v>
+        <v>-2.0614976</v>
       </c>
       <c r="O79">
-        <v>-0.5016195999999999</v>
+        <v>-0.5153744</v>
       </c>
       <c r="P79">
-        <v>-1.5048588</v>
+        <v>-1.5461232</v>
       </c>
       <c r="Q79">
-        <v>1.3651412</v>
+        <v>1.3238768</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2820194079466857</v>
+        <v>0.2927566537624442</v>
       </c>
       <c r="T79">
-        <v>3.65423911416107</v>
+        <v>3.820340892077483</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1315951475168621</v>
+        <v>0.1299080302410049</v>
       </c>
       <c r="W79">
-        <v>0.1743756943786141</v>
+        <v>0.1747144675276062</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5263805900674485</v>
+        <v>0.5196321209640197</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7921,22 +7921,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2006837484992706</v>
+        <v>0.2022337484992706</v>
       </c>
       <c r="C80">
-        <v>-8.337704558153757</v>
+        <v>-8.713494084050648</v>
       </c>
       <c r="D80">
-        <v>11.74429544184624</v>
+        <v>11.64250591594935</v>
       </c>
       <c r="E80">
-        <v>6.372</v>
+        <v>6.646000000000001</v>
       </c>
       <c r="F80">
-        <v>21.372</v>
+        <v>21.646</v>
       </c>
       <c r="G80">
         <v>1.29</v>
@@ -7957,37 +7957,37 @@
         <v>2.23</v>
       </c>
       <c r="M80">
-        <v>4.2914976</v>
+        <v>4.346516800000001</v>
       </c>
       <c r="N80">
-        <v>-2.0614976</v>
+        <v>-2.1165168</v>
       </c>
       <c r="O80">
-        <v>-0.5153744</v>
+        <v>-0.5291292000000001</v>
       </c>
       <c r="P80">
-        <v>-1.5461232</v>
+        <v>-1.5873876</v>
       </c>
       <c r="Q80">
-        <v>1.3238768</v>
+        <v>1.2826124</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2927566537624442</v>
+        <v>0.3045164944177987</v>
       </c>
       <c r="T80">
-        <v>3.820340892077483</v>
+        <v>4.002261886938316</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1299080302410049</v>
+        <v>0.1282636247949162</v>
       </c>
       <c r="W80">
-        <v>0.1747144675276062</v>
+        <v>0.1750446641411808</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5196321209640197</v>
+        <v>0.5130544991796651</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8003,22 +8003,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2022337484992706</v>
+        <v>0.2037837484992706</v>
       </c>
       <c r="C81">
-        <v>-8.713494084050648</v>
+        <v>-9.087534321872955</v>
       </c>
       <c r="D81">
-        <v>11.64250591594935</v>
+        <v>11.54246567812705</v>
       </c>
       <c r="E81">
-        <v>6.646000000000001</v>
+        <v>6.920000000000002</v>
       </c>
       <c r="F81">
-        <v>21.646</v>
+        <v>21.92</v>
       </c>
       <c r="G81">
         <v>1.29</v>
@@ -8039,37 +8039,37 @@
         <v>2.23</v>
       </c>
       <c r="M81">
-        <v>4.346516800000001</v>
+        <v>4.401536</v>
       </c>
       <c r="N81">
-        <v>-2.1165168</v>
+        <v>-2.171536</v>
       </c>
       <c r="O81">
-        <v>-0.5291292000000001</v>
+        <v>-0.5428839999999999</v>
       </c>
       <c r="P81">
-        <v>-1.5873876</v>
+        <v>-1.628652</v>
       </c>
       <c r="Q81">
-        <v>1.2826124</v>
+        <v>1.241348</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3045164944177987</v>
+        <v>0.3174523191386887</v>
       </c>
       <c r="T81">
-        <v>4.002261886938316</v>
+        <v>4.202374981285232</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1282636247949162</v>
+        <v>0.1266603294849798</v>
       </c>
       <c r="W81">
-        <v>0.1750446641411808</v>
+        <v>0.175366605839416</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5130544991796651</v>
+        <v>0.5066413179399192</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8085,22 +8085,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2037837484992706</v>
+        <v>0.2053337484992706</v>
       </c>
       <c r="C82">
-        <v>-9.087534321872955</v>
+        <v>-9.459869980628245</v>
       </c>
       <c r="D82">
-        <v>11.54246567812705</v>
+        <v>11.44413001937175</v>
       </c>
       <c r="E82">
-        <v>6.920000000000002</v>
+        <v>7.193999999999999</v>
       </c>
       <c r="F82">
-        <v>21.92</v>
+        <v>22.194</v>
       </c>
       <c r="G82">
         <v>1.29</v>
@@ -8121,37 +8121,37 @@
         <v>2.23</v>
       </c>
       <c r="M82">
-        <v>4.401536</v>
+        <v>4.4565552</v>
       </c>
       <c r="N82">
-        <v>-2.171536</v>
+        <v>-2.2265552</v>
       </c>
       <c r="O82">
-        <v>-0.5428839999999999</v>
+        <v>-0.5566388</v>
       </c>
       <c r="P82">
-        <v>-1.628652</v>
+        <v>-1.6699164</v>
       </c>
       <c r="Q82">
-        <v>1.241348</v>
+        <v>1.2000836</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3174523191386887</v>
+        <v>0.3317498096196723</v>
       </c>
       <c r="T82">
-        <v>4.202374981285232</v>
+        <v>4.423552611879192</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1266603294849798</v>
+        <v>0.1250966217135603</v>
       </c>
       <c r="W82">
-        <v>0.175366605839416</v>
+        <v>0.1756805983599171</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5066413179399192</v>
+        <v>0.5003864868542411</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8167,22 +8167,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2053337484992706</v>
+        <v>0.2364930275253646</v>
       </c>
       <c r="C83">
-        <v>-9.459869980628245</v>
+        <v>-11.4072548160611</v>
       </c>
       <c r="D83">
-        <v>11.44413001937175</v>
+        <v>9.770745183938894</v>
       </c>
       <c r="E83">
-        <v>7.193999999999999</v>
+        <v>7.468</v>
       </c>
       <c r="F83">
-        <v>22.194</v>
+        <v>22.468</v>
       </c>
       <c r="G83">
         <v>1.29</v>
@@ -8203,45 +8203,45 @@
         <v>2.23</v>
       </c>
       <c r="M83">
-        <v>4.4565552</v>
+        <v>5.2979544</v>
       </c>
       <c r="N83">
-        <v>-2.2265552</v>
+        <v>-3.0679544</v>
       </c>
       <c r="O83">
-        <v>-0.5566388</v>
+        <v>-0.7669885999999999</v>
       </c>
       <c r="P83">
-        <v>-1.6699164</v>
+        <v>-2.3009658</v>
       </c>
       <c r="Q83">
-        <v>1.2000836</v>
+        <v>0.5690342000000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3317498096196723</v>
+        <v>0.3526874602990653</v>
       </c>
       <c r="T83">
-        <v>4.423552611879192</v>
+        <v>4.747451408918542</v>
       </c>
       <c r="U83">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1250966217135603</v>
+        <v>0.1052292937817661</v>
       </c>
       <c r="W83">
-        <v>0.1756805983599171</v>
+        <v>0.2109869325262596</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5003864868542411</v>
+        <v>0.4209171751270642</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8249,22 +8249,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2364930275253646</v>
+        <v>0.2383930275253646</v>
       </c>
       <c r="C84">
-        <v>-11.4072548160611</v>
+        <v>-11.76760272862441</v>
       </c>
       <c r="D84">
-        <v>9.770745183938894</v>
+        <v>9.684397271375587</v>
       </c>
       <c r="E84">
-        <v>7.468</v>
+        <v>7.742000000000001</v>
       </c>
       <c r="F84">
-        <v>22.468</v>
+        <v>22.742</v>
       </c>
       <c r="G84">
         <v>1.29</v>
@@ -8285,37 +8285,37 @@
         <v>2.23</v>
       </c>
       <c r="M84">
-        <v>5.2979544</v>
+        <v>5.362563600000001</v>
       </c>
       <c r="N84">
-        <v>-3.0679544</v>
+        <v>-3.1325636</v>
       </c>
       <c r="O84">
-        <v>-0.7669885999999999</v>
+        <v>-0.7831409</v>
       </c>
       <c r="P84">
-        <v>-2.3009658</v>
+        <v>-2.3494227</v>
       </c>
       <c r="Q84">
-        <v>0.5690342000000004</v>
+        <v>0.5205773000000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3526874602990653</v>
+        <v>0.3707396638460693</v>
       </c>
       <c r="T84">
-        <v>4.747451408918542</v>
+        <v>5.026713256501988</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1052292937817661</v>
+        <v>0.1039614709651183</v>
       </c>
       <c r="W84">
-        <v>0.2109869325262596</v>
+        <v>0.2112858851464251</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4209171751270642</v>
+        <v>0.4158458838604731</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8331,22 +8331,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2383930275253646</v>
+        <v>0.2402930275253646</v>
       </c>
       <c r="C85">
-        <v>-11.76760272862441</v>
+        <v>-12.1264378296659</v>
       </c>
       <c r="D85">
-        <v>9.684397271375587</v>
+        <v>9.599562170334107</v>
       </c>
       <c r="E85">
-        <v>7.742000000000001</v>
+        <v>8.016000000000002</v>
       </c>
       <c r="F85">
-        <v>22.742</v>
+        <v>23.016</v>
       </c>
       <c r="G85">
         <v>1.29</v>
@@ -8367,37 +8367,37 @@
         <v>2.23</v>
       </c>
       <c r="M85">
-        <v>5.362563600000001</v>
+        <v>5.427172800000001</v>
       </c>
       <c r="N85">
-        <v>-3.1325636</v>
+        <v>-3.197172800000001</v>
       </c>
       <c r="O85">
-        <v>-0.7831409</v>
+        <v>-0.7992932000000001</v>
       </c>
       <c r="P85">
-        <v>-2.3494227</v>
+        <v>-2.3978796</v>
       </c>
       <c r="Q85">
-        <v>0.5205773000000002</v>
+        <v>0.4721203999999997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3707396638460693</v>
+        <v>0.3910483928364487</v>
       </c>
       <c r="T85">
-        <v>5.026713256501988</v>
+        <v>5.340882835033362</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1039614709651183</v>
+        <v>0.1027238344060097</v>
       </c>
       <c r="W85">
-        <v>0.2112858851464251</v>
+        <v>0.2115777198470629</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4158458838604731</v>
+        <v>0.4108953376240388</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8413,22 +8413,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2402930275253646</v>
+        <v>0.2421930275253646</v>
       </c>
       <c r="C86">
-        <v>-12.12643782966589</v>
+        <v>-12.48379953052723</v>
       </c>
       <c r="D86">
-        <v>9.599562170334107</v>
+        <v>9.516200469472775</v>
       </c>
       <c r="E86">
-        <v>8.015999999999998</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F86">
-        <v>23.016</v>
+        <v>23.29</v>
       </c>
       <c r="G86">
         <v>1.29</v>
@@ -8449,37 +8449,37 @@
         <v>2.23</v>
       </c>
       <c r="M86">
-        <v>5.4271728</v>
+        <v>5.491782</v>
       </c>
       <c r="N86">
-        <v>-3.1971728</v>
+        <v>-3.261781999999999</v>
       </c>
       <c r="O86">
-        <v>-0.7992931999999999</v>
+        <v>-0.8154454999999998</v>
       </c>
       <c r="P86">
-        <v>-2.3978796</v>
+        <v>-2.446336499999999</v>
       </c>
       <c r="Q86">
-        <v>0.4721204000000006</v>
+        <v>0.4236635000000009</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3910483928364484</v>
+        <v>0.4140649523588784</v>
       </c>
       <c r="T86">
-        <v>5.340882835033359</v>
+        <v>5.69694169070225</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1027238344060097</v>
+        <v>0.1015153187071155</v>
       </c>
       <c r="W86">
-        <v>0.2115777198470629</v>
+        <v>0.2118626878488622</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4108953376240388</v>
+        <v>0.406061274828462</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8495,22 +8495,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2421930275253646</v>
+        <v>0.2440930275253646</v>
       </c>
       <c r="C87">
-        <v>-12.48379953052723</v>
+        <v>-12.83972588535818</v>
       </c>
       <c r="D87">
-        <v>9.516200469472775</v>
+        <v>9.43427411464182</v>
       </c>
       <c r="E87">
-        <v>8.289999999999999</v>
+        <v>8.564</v>
       </c>
       <c r="F87">
-        <v>23.29</v>
+        <v>23.564</v>
       </c>
       <c r="G87">
         <v>1.29</v>
@@ -8531,37 +8531,37 @@
         <v>2.23</v>
       </c>
       <c r="M87">
-        <v>5.491782</v>
+        <v>5.5563912</v>
       </c>
       <c r="N87">
-        <v>-3.261781999999999</v>
+        <v>-3.3263912</v>
       </c>
       <c r="O87">
-        <v>-0.8154454999999998</v>
+        <v>-0.8315977999999999</v>
       </c>
       <c r="P87">
-        <v>-2.446336499999999</v>
+        <v>-2.4947934</v>
       </c>
       <c r="Q87">
-        <v>0.4236635000000009</v>
+        <v>0.3752066000000003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4140649523588784</v>
+        <v>0.4403695918130839</v>
       </c>
       <c r="T87">
-        <v>5.69694169070225</v>
+        <v>6.103866097180981</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1015153187071155</v>
+        <v>0.1003349080244746</v>
       </c>
       <c r="W87">
-        <v>0.2118626878488622</v>
+        <v>0.2121410286878289</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.406061274828462</v>
+        <v>0.4013396320978985</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8577,22 +8577,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2440930275253646</v>
+        <v>0.2459930275253646</v>
       </c>
       <c r="C88">
-        <v>-12.83972588535818</v>
+        <v>-13.19425364903926</v>
       </c>
       <c r="D88">
-        <v>9.43427411464182</v>
+        <v>9.353746350960733</v>
       </c>
       <c r="E88">
-        <v>8.564</v>
+        <v>8.837999999999997</v>
       </c>
       <c r="F88">
-        <v>23.564</v>
+        <v>23.838</v>
       </c>
       <c r="G88">
         <v>1.29</v>
@@ -8613,37 +8613,37 @@
         <v>2.23</v>
       </c>
       <c r="M88">
-        <v>5.5563912</v>
+        <v>5.6210004</v>
       </c>
       <c r="N88">
-        <v>-3.3263912</v>
+        <v>-3.391000399999999</v>
       </c>
       <c r="O88">
-        <v>-0.8315977999999999</v>
+        <v>-0.8477500999999998</v>
       </c>
       <c r="P88">
-        <v>-2.4947934</v>
+        <v>-2.5432503</v>
       </c>
       <c r="Q88">
-        <v>0.3752066000000003</v>
+        <v>0.3267497000000006</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4403695918130839</v>
+        <v>0.4707210988756288</v>
       </c>
       <c r="T88">
-        <v>6.103866097180981</v>
+        <v>6.573394258502595</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1003349080244746</v>
+        <v>0.0991816332195956</v>
       </c>
       <c r="W88">
-        <v>0.2121410286878289</v>
+        <v>0.2124129708868194</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4013396320978985</v>
+        <v>0.3967265328783823</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8659,22 +8659,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2459930275253646</v>
+        <v>0.2478930275253646</v>
       </c>
       <c r="C89">
-        <v>-13.19425364903926</v>
+        <v>-13.54741833216305</v>
       </c>
       <c r="D89">
-        <v>9.353746350960733</v>
+        <v>9.274581667836951</v>
       </c>
       <c r="E89">
-        <v>8.837999999999997</v>
+        <v>9.111999999999998</v>
       </c>
       <c r="F89">
-        <v>23.838</v>
+        <v>24.112</v>
       </c>
       <c r="G89">
         <v>1.29</v>
@@ -8695,37 +8695,37 @@
         <v>2.23</v>
       </c>
       <c r="M89">
-        <v>5.6210004</v>
+        <v>5.6856096</v>
       </c>
       <c r="N89">
-        <v>-3.391000399999999</v>
+        <v>-3.4556096</v>
       </c>
       <c r="O89">
-        <v>-0.8477500999999998</v>
+        <v>-0.8639024</v>
       </c>
       <c r="P89">
-        <v>-2.5432503</v>
+        <v>-2.5917072</v>
       </c>
       <c r="Q89">
-        <v>0.3267497000000006</v>
+        <v>0.2782928</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4707210988756288</v>
+        <v>0.506131190448598</v>
       </c>
       <c r="T89">
-        <v>6.573394258502595</v>
+        <v>7.121177113377813</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0991816332195956</v>
+        <v>0.09805456920573655</v>
       </c>
       <c r="W89">
-        <v>0.2124129708868194</v>
+        <v>0.2126787325812873</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3967265328783823</v>
+        <v>0.3922182768229462</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8741,22 +8741,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2478930275253646</v>
+        <v>0.2497930275253646</v>
       </c>
       <c r="C90">
-        <v>-13.54741833216305</v>
+        <v>-13.89925425324689</v>
       </c>
       <c r="D90">
-        <v>9.274581667836951</v>
+        <v>9.196745746753107</v>
       </c>
       <c r="E90">
-        <v>9.111999999999998</v>
+        <v>9.385999999999999</v>
       </c>
       <c r="F90">
-        <v>24.112</v>
+        <v>24.386</v>
       </c>
       <c r="G90">
         <v>1.29</v>
@@ -8777,37 +8777,37 @@
         <v>2.23</v>
       </c>
       <c r="M90">
-        <v>5.6856096</v>
+        <v>5.7502188</v>
       </c>
       <c r="N90">
-        <v>-3.4556096</v>
+        <v>-3.520218799999999</v>
       </c>
       <c r="O90">
-        <v>-0.8639024</v>
+        <v>-0.8800546999999999</v>
       </c>
       <c r="P90">
-        <v>-2.5917072</v>
+        <v>-2.6401641</v>
       </c>
       <c r="Q90">
-        <v>0.2782928</v>
+        <v>0.2298359000000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.506131190448598</v>
+        <v>0.5479794804893796</v>
       </c>
       <c r="T90">
-        <v>7.121177113377813</v>
+        <v>7.768556850957616</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09805456920573655</v>
+        <v>0.09695283247308782</v>
       </c>
       <c r="W90">
-        <v>0.2126787325812873</v>
+        <v>0.2129385221028459</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3922182768229462</v>
+        <v>0.3878113298923513</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8823,22 +8823,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2497930275253646</v>
+        <v>0.2516930275253646</v>
       </c>
       <c r="C91">
-        <v>-13.89925425324689</v>
+        <v>-14.24979458833848</v>
       </c>
       <c r="D91">
-        <v>9.196745746753107</v>
+        <v>9.120205411661519</v>
       </c>
       <c r="E91">
-        <v>9.385999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="F91">
-        <v>24.386</v>
+        <v>24.66</v>
       </c>
       <c r="G91">
         <v>1.29</v>
@@ -8859,37 +8859,37 @@
         <v>2.23</v>
       </c>
       <c r="M91">
-        <v>5.7502188</v>
+        <v>5.814828</v>
       </c>
       <c r="N91">
-        <v>-3.520218799999999</v>
+        <v>-3.584828</v>
       </c>
       <c r="O91">
-        <v>-0.8800546999999999</v>
+        <v>-0.896207</v>
       </c>
       <c r="P91">
-        <v>-2.6401641</v>
+        <v>-2.688621</v>
       </c>
       <c r="Q91">
-        <v>0.2298359000000003</v>
+        <v>0.1813790000000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5479794804893796</v>
+        <v>0.5981974285383176</v>
       </c>
       <c r="T91">
-        <v>7.768556850957616</v>
+        <v>8.545412536053377</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09695283247308782</v>
+        <v>0.0958755787789424</v>
       </c>
       <c r="W91">
-        <v>0.2129385221028459</v>
+        <v>0.2131925385239254</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3878113298923513</v>
+        <v>0.3835023151157696</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8905,22 +8905,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2516930275253646</v>
+        <v>0.2535930275253646</v>
       </c>
       <c r="C92">
-        <v>-14.24979458833848</v>
+        <v>-14.59907141816468</v>
       </c>
       <c r="D92">
-        <v>9.120205411661519</v>
+        <v>9.044928581835318</v>
       </c>
       <c r="E92">
-        <v>9.66</v>
+        <v>9.934000000000001</v>
       </c>
       <c r="F92">
-        <v>24.66</v>
+        <v>24.934</v>
       </c>
       <c r="G92">
         <v>1.29</v>
@@ -8941,37 +8941,37 @@
         <v>2.23</v>
       </c>
       <c r="M92">
-        <v>5.814828</v>
+        <v>5.879437200000001</v>
       </c>
       <c r="N92">
-        <v>-3.584828</v>
+        <v>-3.6494372</v>
       </c>
       <c r="O92">
-        <v>-0.896207</v>
+        <v>-0.9123593000000001</v>
       </c>
       <c r="P92">
-        <v>-2.688621</v>
+        <v>-2.7370779</v>
       </c>
       <c r="Q92">
-        <v>0.1813790000000002</v>
+        <v>0.1329221</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5981974285383176</v>
+        <v>0.6595749205981306</v>
       </c>
       <c r="T92">
-        <v>8.545412536053377</v>
+        <v>9.494902817837085</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0958755787789424</v>
+        <v>0.0948220009901628</v>
       </c>
       <c r="W92">
-        <v>0.2131925385239254</v>
+        <v>0.2134409721665196</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3835023151157696</v>
+        <v>0.3792880039606512</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8987,22 +8987,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2535930275253646</v>
+        <v>0.2554930275253646</v>
       </c>
       <c r="C93">
-        <v>-14.59907141816468</v>
+        <v>-14.94711577296459</v>
       </c>
       <c r="D93">
-        <v>9.044928581835318</v>
+        <v>8.970884227035409</v>
       </c>
       <c r="E93">
-        <v>9.934000000000001</v>
+        <v>10.208</v>
       </c>
       <c r="F93">
-        <v>24.934</v>
+        <v>25.208</v>
       </c>
       <c r="G93">
         <v>1.29</v>
@@ -9023,37 +9023,37 @@
         <v>2.23</v>
       </c>
       <c r="M93">
-        <v>5.879437200000001</v>
+        <v>5.9440464</v>
       </c>
       <c r="N93">
-        <v>-3.6494372</v>
+        <v>-3.714046399999999</v>
       </c>
       <c r="O93">
-        <v>-0.9123593000000001</v>
+        <v>-0.9285115999999998</v>
       </c>
       <c r="P93">
-        <v>-2.7370779</v>
+        <v>-2.785534799999999</v>
       </c>
       <c r="Q93">
-        <v>0.1329221</v>
+        <v>0.0844652000000008</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6595749205981306</v>
+        <v>0.7362967856728972</v>
       </c>
       <c r="T93">
-        <v>9.494902817837085</v>
+        <v>10.68176567006672</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0948220009901628</v>
+        <v>0.09379132706635671</v>
       </c>
       <c r="W93">
-        <v>0.2134409721665196</v>
+        <v>0.2136840050777531</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3792880039606512</v>
+        <v>0.3751653082654268</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9069,22 +9069,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2554930275253646</v>
+        <v>0.2573930275253646</v>
       </c>
       <c r="C94">
-        <v>-14.94711577296459</v>
+        <v>-15.29395767513834</v>
       </c>
       <c r="D94">
-        <v>8.970884227035409</v>
+        <v>8.898042324861654</v>
       </c>
       <c r="E94">
-        <v>10.208</v>
+        <v>10.482</v>
       </c>
       <c r="F94">
-        <v>25.208</v>
+        <v>25.482</v>
       </c>
       <c r="G94">
         <v>1.29</v>
@@ -9105,37 +9105,37 @@
         <v>2.23</v>
       </c>
       <c r="M94">
-        <v>5.9440464</v>
+        <v>6.0086556</v>
       </c>
       <c r="N94">
-        <v>-3.714046399999999</v>
+        <v>-3.7786556</v>
       </c>
       <c r="O94">
-        <v>-0.9285115999999998</v>
+        <v>-0.9446638999999999</v>
       </c>
       <c r="P94">
-        <v>-2.785534799999999</v>
+        <v>-2.833991699999999</v>
       </c>
       <c r="Q94">
-        <v>0.0844652000000008</v>
+        <v>0.03600830000000066</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7362967856728972</v>
+        <v>0.8349391836261685</v>
       </c>
       <c r="T94">
-        <v>10.68176567006672</v>
+        <v>12.20773219436197</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09379132706635671</v>
+        <v>0.09278281817317006</v>
       </c>
       <c r="W94">
-        <v>0.2136840050777531</v>
+        <v>0.2139218114747665</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3751653082654268</v>
+        <v>0.3711312726926803</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9151,22 +9151,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2573930275253646</v>
+        <v>0.2592930275253646</v>
       </c>
       <c r="C95">
-        <v>-15.29395767513834</v>
+        <v>-15.63962617983489</v>
       </c>
       <c r="D95">
-        <v>8.898042324861654</v>
+        <v>8.826373820165111</v>
       </c>
       <c r="E95">
-        <v>10.482</v>
+        <v>10.756</v>
       </c>
       <c r="F95">
-        <v>25.482</v>
+        <v>25.756</v>
       </c>
       <c r="G95">
         <v>1.29</v>
@@ -9187,37 +9187,37 @@
         <v>2.23</v>
       </c>
       <c r="M95">
-        <v>6.0086556</v>
+        <v>6.0732648</v>
       </c>
       <c r="N95">
-        <v>-3.7786556</v>
+        <v>-3.8432648</v>
       </c>
       <c r="O95">
-        <v>-0.9446638999999999</v>
+        <v>-0.9608162</v>
       </c>
       <c r="P95">
-        <v>-2.833991699999999</v>
+        <v>-2.8824486</v>
       </c>
       <c r="Q95">
-        <v>0.03600830000000066</v>
+        <v>-0.01244859999999992</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8349391836261685</v>
+        <v>0.9664623808971967</v>
       </c>
       <c r="T95">
-        <v>12.20773219436197</v>
+        <v>14.24235422675564</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09278281817317006</v>
+        <v>0.09179576691600867</v>
       </c>
       <c r="W95">
-        <v>0.2139218114747665</v>
+        <v>0.2141545581612052</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3711312726926803</v>
+        <v>0.3671830676640347</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9233,22 +9233,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2592930275253646</v>
+        <v>0.2611930275253647</v>
       </c>
       <c r="C96">
-        <v>-15.63962617983489</v>
+        <v>-15.98414941359394</v>
       </c>
       <c r="D96">
-        <v>8.826373820165111</v>
+        <v>8.755850586406064</v>
       </c>
       <c r="E96">
-        <v>10.756</v>
+        <v>11.03</v>
       </c>
       <c r="F96">
-        <v>25.756</v>
+        <v>26.03</v>
       </c>
       <c r="G96">
         <v>1.29</v>
@@ -9269,37 +9269,37 @@
         <v>2.23</v>
       </c>
       <c r="M96">
-        <v>6.0732648</v>
+        <v>6.137874000000001</v>
       </c>
       <c r="N96">
-        <v>-3.8432648</v>
+        <v>-3.907874000000001</v>
       </c>
       <c r="O96">
-        <v>-0.9608162</v>
+        <v>-0.9769685000000001</v>
       </c>
       <c r="P96">
-        <v>-2.8824486</v>
+        <v>-2.930905500000001</v>
       </c>
       <c r="Q96">
-        <v>-0.01244859999999992</v>
+        <v>-0.0609055000000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9664623808971967</v>
+        <v>1.150594857076637</v>
       </c>
       <c r="T96">
-        <v>14.24235422675564</v>
+        <v>17.09082507210677</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09179576691600867</v>
+        <v>0.09082949568531384</v>
       </c>
       <c r="W96">
-        <v>0.2141545581612052</v>
+        <v>0.214382404917403</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3671830676640347</v>
+        <v>0.3633179827412554</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9315,22 +9315,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2611930275253647</v>
+        <v>0.2630930275253646</v>
       </c>
       <c r="C97">
-        <v>-15.98414941359394</v>
+        <v>-16.32755461115009</v>
       </c>
       <c r="D97">
-        <v>8.755850586406064</v>
+        <v>8.686445388849913</v>
       </c>
       <c r="E97">
-        <v>11.03</v>
+        <v>11.304</v>
       </c>
       <c r="F97">
-        <v>26.03</v>
+        <v>26.304</v>
       </c>
       <c r="G97">
         <v>1.29</v>
@@ -9351,37 +9351,37 @@
         <v>2.23</v>
       </c>
       <c r="M97">
-        <v>6.137874000000001</v>
+        <v>6.202483200000001</v>
       </c>
       <c r="N97">
-        <v>-3.907874000000001</v>
+        <v>-3.9724832</v>
       </c>
       <c r="O97">
-        <v>-0.9769685000000001</v>
+        <v>-0.9931208</v>
       </c>
       <c r="P97">
-        <v>-2.930905500000001</v>
+        <v>-2.9793624</v>
       </c>
       <c r="Q97">
-        <v>-0.0609055000000005</v>
+        <v>-0.1093624000000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.150594857076637</v>
+        <v>1.426793571345796</v>
       </c>
       <c r="T97">
-        <v>17.09082507210677</v>
+        <v>21.36353134013348</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09082949568531384</v>
+        <v>0.08988335510525849</v>
       </c>
       <c r="W97">
-        <v>0.214382404917403</v>
+        <v>0.2146055048661801</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3633179827412554</v>
+        <v>0.359533420421034</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9397,22 +9397,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2630930275253646</v>
+        <v>0.2649930275253646</v>
       </c>
       <c r="C98">
-        <v>-16.32755461115008</v>
+        <v>-16.66986815050035</v>
       </c>
       <c r="D98">
-        <v>8.686445388849913</v>
+        <v>8.618131849499646</v>
       </c>
       <c r="E98">
-        <v>11.304</v>
+        <v>11.578</v>
       </c>
       <c r="F98">
-        <v>26.304</v>
+        <v>26.578</v>
       </c>
       <c r="G98">
         <v>1.29</v>
@@ -9433,37 +9433,37 @@
         <v>2.23</v>
       </c>
       <c r="M98">
-        <v>6.2024832</v>
+        <v>6.2670924</v>
       </c>
       <c r="N98">
-        <v>-3.972483199999999</v>
+        <v>-4.0370924</v>
       </c>
       <c r="O98">
-        <v>-0.9931207999999998</v>
+        <v>-1.0092731</v>
       </c>
       <c r="P98">
-        <v>-2.979362399999999</v>
+        <v>-3.0278193</v>
       </c>
       <c r="Q98">
-        <v>-0.1093623999999993</v>
+        <v>-0.1578192999999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.426793571345793</v>
+        <v>1.88712476179439</v>
       </c>
       <c r="T98">
-        <v>21.36353134013342</v>
+        <v>28.48470845351123</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08988335510525851</v>
+        <v>0.08895672257840016</v>
       </c>
       <c r="W98">
-        <v>0.2146055048661801</v>
+        <v>0.2148240048160132</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3595334204210341</v>
+        <v>0.3558268903136007</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9479,22 +9479,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2649930275253646</v>
+        <v>0.2668930275253646</v>
       </c>
       <c r="C99">
-        <v>-16.66986815050035</v>
+        <v>-17.01111558632982</v>
       </c>
       <c r="D99">
-        <v>8.618131849499646</v>
+        <v>8.550884413670179</v>
       </c>
       <c r="E99">
-        <v>11.578</v>
+        <v>11.852</v>
       </c>
       <c r="F99">
-        <v>26.578</v>
+        <v>26.852</v>
       </c>
       <c r="G99">
         <v>1.29</v>
@@ -9515,37 +9515,37 @@
         <v>2.23</v>
       </c>
       <c r="M99">
-        <v>6.2670924</v>
+        <v>6.3317016</v>
       </c>
       <c r="N99">
-        <v>-4.0370924</v>
+        <v>-4.101701599999999</v>
       </c>
       <c r="O99">
-        <v>-1.0092731</v>
+        <v>-1.0254254</v>
       </c>
       <c r="P99">
-        <v>-3.0278193</v>
+        <v>-3.0762762</v>
       </c>
       <c r="Q99">
-        <v>-0.1578192999999999</v>
+        <v>-0.2062761999999996</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.88712476179439</v>
+        <v>2.807787142691585</v>
       </c>
       <c r="T99">
-        <v>28.48470845351123</v>
+        <v>42.72706268026684</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08895672257840016</v>
+        <v>0.0880490009194369</v>
       </c>
       <c r="W99">
-        <v>0.2148240048160132</v>
+        <v>0.2150380455831968</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3558268903136007</v>
+        <v>0.3521960036777476</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9561,22 +9561,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2668930275253646</v>
+        <v>0.2687930275253646</v>
       </c>
       <c r="C100">
-        <v>-17.01111558632982</v>
+        <v>-17.35132168188454</v>
       </c>
       <c r="D100">
-        <v>8.550884413670179</v>
+        <v>8.48467831811546</v>
       </c>
       <c r="E100">
-        <v>11.852</v>
+        <v>12.126</v>
       </c>
       <c r="F100">
-        <v>26.852</v>
+        <v>27.126</v>
       </c>
       <c r="G100">
         <v>1.29</v>
@@ -9597,37 +9597,37 @@
         <v>2.23</v>
       </c>
       <c r="M100">
-        <v>6.3317016</v>
+        <v>6.396310799999999</v>
       </c>
       <c r="N100">
-        <v>-4.101701599999999</v>
+        <v>-4.166310799999999</v>
       </c>
       <c r="O100">
-        <v>-1.0254254</v>
+        <v>-1.0415777</v>
       </c>
       <c r="P100">
-        <v>-3.0762762</v>
+        <v>-3.124733099999999</v>
       </c>
       <c r="Q100">
-        <v>-0.2062761999999996</v>
+        <v>-0.2547330999999993</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.807787142691585</v>
+        <v>5.56977428538317</v>
       </c>
       <c r="T100">
-        <v>42.72706268026684</v>
+        <v>85.45412536053368</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0880490009194369</v>
+        <v>0.08715961707176584</v>
       </c>
       <c r="W100">
-        <v>0.2150380455831968</v>
+        <v>0.2152477622944776</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9635,91 +9635,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3521960036777476</v>
+        <v>0.3486384682870634</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2687930275253646</v>
-      </c>
-      <c r="C101">
-        <v>-17.35132168188454</v>
-      </c>
-      <c r="D101">
-        <v>8.48467831811546</v>
-      </c>
-      <c r="E101">
-        <v>12.126</v>
-      </c>
-      <c r="F101">
-        <v>27.126</v>
-      </c>
-      <c r="G101">
-        <v>1.29</v>
-      </c>
-      <c r="H101">
-        <v>12.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.100000000000001</v>
-      </c>
-      <c r="K101">
-        <v>2.87</v>
-      </c>
-      <c r="L101">
-        <v>2.23</v>
-      </c>
-      <c r="M101">
-        <v>6.396310799999999</v>
-      </c>
-      <c r="N101">
-        <v>-4.166310799999999</v>
-      </c>
-      <c r="O101">
-        <v>-1.0415777</v>
-      </c>
-      <c r="P101">
-        <v>-3.124733099999999</v>
-      </c>
-      <c r="Q101">
-        <v>-0.2547330999999993</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.56977428538317</v>
-      </c>
-      <c r="T101">
-        <v>85.45412536053368</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08715961707176584</v>
-      </c>
-      <c r="W101">
-        <v>0.2152477622944776</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3486384682870634</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
